--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1048B40-C63F-479D-8043-E98C187E6990}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C482383-A482-4187-850B-6B301E916091}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="132">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -15404,6 +15404,175 @@
   <si>
     <t>[달러/원 환율] 위험회피 vs. 일본 엔화 강세 동조에 1,430원대 등락 전일 달러/원 환율은 미국 재무부의 환시 개입 부인에 따른 달러 강세에 7.1원 상승 개장. 장중 저가 매수세 유입에 1,431원까지 상승하기도 했으나, 일본 엔화 강세와 미 달러화 지수 하락에 연동해 상승 폭이 점진적으로 축소. 오후장에서 1,422원까지 저점 낮춘 이후 20원대에서 등락, 전일 종가 대비 3.8원 상승한 1,426.3원에 정규장 마감. 야간장에서는 미국 기술주 급락에 따른 위험회피심리에 1,434.0원으로 상승 마감. 역외 NDF 환율은 5.40원 상승한 1,430.20원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 상승 개장 예상. 미 달러의 전방위적 약세에도 불구, 기술주 급락에 위험회피 분위기가 지배적. 이로 인한 국내 증시 부진 및 외국인 자금 순유출이 원화 약세 자극. 이에 달러/원은 1,430원 부근 개장 뒤, 상승 폭 확대될 가능성. 하지만 일본 엔화의 강세는 엔화 프록시인 원화에도 강세 요인. 금일 환율은 위험회피 및 엔화 강세 등에 주로 1,430원대 등락 전망 [글로벌 동향] 미국 무역수지 적자 폭 확대, 기술주 급락 여파에 약 달러 전일 미 달러화는 미국 경제지표 부진과 기술주 급락 등에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.20% 하락한 96.20pt 기록. 미국 신규 실업수당 청구건수는 20.9만건으로 집계되며 예상치 20.5만건 상회. 11월 무역수지는 568억 달러 적자로, 10월 적자 폭 대비 95% 급증. 애틀랜다 연은 GDPNow의 4분기 성장률 추정치는 4.2%로 기존 대비 1.2%p 하향 조정. 순수출 성장 기여도는 무역적자 반영해 기존 1.88%p에서 0.65%p로 대폭 하향 조정. 반면, 일본 엔화는 외환당국 개입 경계가 지속되는 가운데, 미 경기둔화 우려 반영해 강세. 뉴욕증시는 마이크로소프트發 기술주 급락에 나스닥 지수 위주로 부진. 마이크로소프트의 작년 4분기 실적 실망과 과잉 투자 우려가 부상. 소프트웨어주는 AI의 기존 사업모델 대체 우려를 반영하며 부진. 한편 미 재무부는 한국을 기존과 같은 '환율 관찰대상국'으로 지정 [마켓 이슈] 트럼프 대통령 지지율이 내려가면, 달러화가 약해지는 이유는? 최근 미 달러화의 약세는 단순 금리 변수 만으로 설명하긴 어려움. 그보다는 트럼프의 국정수행 지지율과 미 달러화 지수 간의 연관성에 주목할 필요. 트럼프 지지율 하락 시 달러화 지수도 동반 하락하는 패턴은 1기와 2기 모두에서 관찰. 특히 2기 들어서 변수 간 연관성이 더욱 강화. 1기 상관계수는 0.38에 그쳤으나, 2기 1년 간은 0.70 내외로 크게 상승. 1기 및 2기 전체 기간의 상관계수도 약 0.60 수준. 최근의 달러 약세 역시 같은 맥락에서 해석 가능. 11월 중간선거 앞두고 트럼프 지지율 하락 흐름이 지속 중. 이에 따라 지지층 결집 위한 정책적 무리수도 이어지는 모습. 이민자 강경 단속, 대외 군사 압박, 그린란드 편입 시도 등이 대표적. 하지만 이는 셧다운 리스크와 국제사회 내 미국 정부 신뢰도 훼손 등으로 연결. 결과적으로 미국 자산 프리미엄이 약화하며 약 달러 압력이 가중. 향후에도 지지율 하락 국면에서는 달러 약세가 지속될 가능성 존재</t>
   </si>
+  <si>
+    <t>UTC+9</t>
+  </si>
+  <si>
+    <t>문정희</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중동 긴장과 국제유가 등락에 민감한 환율 [금일 달러/원 환율 1,485~1,495원 전망]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 여전히 중동 소식과 장중 유가 등락에 반응할 외환시장 전일 달러/원 환율은 중동 전쟁 지속과 국제유가 상승에 개장부터 7.3원 상승한 1,501원으로 출발, 이후 1,491원까지 하락하기도 했으나, 종가는 3.8원 상승한 1,497.5원에 마감함. 야간장에서는 중동 긴장 완화 및 국제유가 하락, 달러화 약세에 1,491.9원으로 하락했으며, NDF 역외환율은 1,488.3원으로 전장보다 7.85원 더 하락하여 호가됨 금일 달러/원 환율은 국제유가 하락에 따른 역외환율 하락을 반영하여 1,490원 전후에서 등락할 것으로 예상됨. 중동 지역의 긴장은 전일보다 다소 완화된 것으로 판단되나, 여전히 전쟁에 대한 불안심리는 남아있고, 장중에도 국제유가 등락에 따라 달러/원 환율이 민감하게 반응하고 있음. 미국과 이란의 협상 재개 또는 호르무즈 해협의 운송 재개 등이 필요하나, 아직은 구체적 언급이 없음. 금일 정오에는 호주 RBA 통화정책회의 예정, 호주의 금리인상과 호주 달러 강세는 원화에도 강세 요인임 [글로벌 동향] 중동의 긴장 완화로 국제유가 5% 이상 하락, 달러도 반락 전일 미 달러화 지수는 중동 사태 진정 및 국제유가 반락에 0.69% 하락함. 국제에너지 기구 (IEA)는 비축유 추가 방출 가능성을 시사했고, 트럼프 대통령은 한국 등 주요국에 호르무즈 해협 선박 호위 작전에 동참해줄 것을 요청함. 한편으로 트럼프 대통령은 이란과 대화할 용의가 있다고도 밝힘. 전일 호르무즈 해협에서는 중국과 이란의 원유 수송선이 통과한 것으로도 알려져 해협 운송 재개 기대도 높아짐. 이러한 중동 지역의 분위기 선회에 국제유가는 5% 이상 하락, 다시 배럴당 90달러 초반으로 낮아졌고, 중동 불안 완화로 미국 국채 장단기 금리는 소폭 하락, 뉴욕증시는 3대 지수 모두 반등함. 시장의 위험회피심리가 완화됨에 따라 미 달러화 지수는 다시 100pt를 하회했으며, 달러화의 약세에 유로화와 일본 엔화, 영국 파운드화 등이 일제히 강세를 보였음 [마켓 이슈] 호주 RBA의 2회 연속 금리인상 전망에 호주 달러 (AUD) 강세 금일 정오 (12시 30분)에 호주 RBA의 통화정책 결정이 발표됨. 컨센서스는 이번 회의에서 RBA가 지난 2월에 이어 정책금리를 0.25%p 인상할 것으로 전망함. RBA의 금리인상 전망은 높은 물가상승압력에 기인, 최근 3월 조사된 기대 인플레이션율은 5.2%로 물가상승률 3.8%를 크게 상회. 원유 및 원자재 가격 상승으로 소비자들의 기대 인플레이션율이 더욱 높아지고 있음. RBA 금리인상 전망에 호주 달러 (AUD)도 강세, 더욱이 호주 달러는 중국 위안화 (CNY)와 높은 상관성을 보임. 문제는 이렇게 금리를 계속 인상하게 될 경우 실물 경제에 부정적 영향을 끼침. 실질 경제성장률은 2.0~2.2% 수준이나, 물가상승률이 4%에 근접하고, 기준금리 역시 물가에 부합할 경우 호주의 실물 경제를 위축시킬 수 있음. 이에 호주 RBA의 추가 인상은 지연될 가능성이 큼. 과거와 다르게 호주 달러와 한국 원화의 환율 상관관계는 크게 떨어짐</t>
+  </si>
+  <si>
+    <t>이민혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이민혁</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>달러/원 1,500원 공방전 [금일 달러/원 환율 1,493~1,505원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 중동 불안과 강 달러에 상방 압력, 당국은 1,500원 사수 전일 달러/원 환율은 중동 지역 불확실성 및 국제유가 상승 등에 따른 달러화 강세에 1,490원대로 개장. 이후에는 고점 인식에 따른 달러 매도에 1,485원까지 상승 폭을 줄이기도 했으나, 외국인의 국내 주식 순매도 등 커스터디 매수가 하단을 지지. 이후 수급상 매수 우위 이어지며 전일 종가 대비 12.5원 상승한 1,493.7원에 정규장 마감. 야간장에서는 달러화 강세 및 위험회피심리에 1,497.5원으로 상승 마감. 역외 NDF 환율은 10.05원 상승한 1,502.50원에 최종 호가 금일 달러/원 환율은 주말간 강 달러와 역외 거래 감안해 1,490원대 개장 예상. 중동 불안과 고유가 등 대외적으로 환율 상방 압력 지속 중. 이에 빅 피겨 진입도 가능하나, 외환당국이 1,500원 사수 위해 미세조정에 나설 듯. 이에 따라 1,500원 부근에서는 수출업체 등 시장 참여자의 달러 매도 유인 증가. 다만 위험회피 장세 이어지고 있어 유의미한 하락 전환은 어려움. 금일 환율은 1,490원대에서 혼조세 보일 것으로 예상 [글로벌 동향] 트럼프의 이란 전쟁 장기화 시사, 유가 상승에 달러화 강세 전일 미 달러화는 중동 지역 불확실성과 국제유가 상승에 연동하며 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.75% 상승한 100.50pt 기록. 뉴욕장에서 미 달러화 지수는 4분기 GDP 부진 영향에 일시적으로 100pt 하회. 미국의 4분기 실질GDP는 전기대비 연율 0.7% 증가로 수정. 이는 예비치인 1.7%의 절반 수준에 해당, 3분기의 4.4%를 큰 폭으로 하회. 하지만 이내 양호한 경제지표가 발표되며 달러화 지수 반등. 미시간대 3월 소비자신뢰지수는 55.5pt로 예상치인 54.8pt 상회. 2월 구인건수는 694.6만건으로 집계되며 예상치인 675.0만건을 상회. 미국·이란 갈등 격화 우려 및 국제유가 상승 역시 달러 강세에 기여. 트럼프 대통령은 다음 주에 이란을 매우 강하게 공격할 것이라고 발언. 그는 미국이 무제한에 가까운 탄약을 보유하고 있다며 전쟁 장기화 시사. WTI 국제유가는 전장 대비 3.11% 상승한 배럴당 98.71달러에 거래 [마켓 이슈] 전쟁과 고유가 장기화 조짐, 그리고 약화한 연준 금리인하 기대 트럼프 대통령의 추가 공격 가능성 발언이 이어지며 미국·이란 전쟁의 장기화 조짐. 중동 긴장 완화 기대 약화되며 국제유가 역시 상승세 지속. 글로벌 시장에서는 점차 고유가 부담 확대되는 분위기. 아직 경제지표에서는 이러한 충격이 확인되지는 않은 상황. 현재 발표되는 주요 경제지표 대부분이 전쟁 이전인 2월 데이터까지만 발표된 상태. 다만 금융시장은 이미 고유가가 가져올 경제 및 정책 환경 변화를 가격에 빠르게 반영 중. 특히 연준 금리인하 기대 축소가 두드러짐. 금리선물시장 기준 올해 연준의 25bp 금리인하 기대는 연초 약 2회에서 최근 1회 미만으로 축소. 이에 달러화 역시 강세 보이며, 달러화 지수는 100pt 상회. 결국 이번 중동 사태의 핵심 변수는 유가. 고유가가 장기화할 경우 인플레이션 압력이 가중, 연준의 인하 시점은 더욱 지연될 가능성. 즉 금주 FOMC에서 연준 위원들의 전쟁 및 고유가 관련 평가에 주목할 필요</t>
+  </si>
+  <si>
+    <t>이란의 강경 대응에 국제유가 다시 급등 [금일 달러/원 환율 1,485~1,496원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 국제유가 급등과 위험회피 심화에 다시 1,490원대 등락 전일 달러/원 환율은 중동 불안과 국제유가 상승에 13.6원 상승 출발한 가운데 장중 원유 선물 가격이 100달러를 상회하며 환율은 1,485원까지도 상승, 이후 유가가 조정을 보임에 따라 종가는 14.7원 상승한 1,481.2원에 마감함. 야간장에서는 이란의 강경 대응 소식과 그에 따른 국제유가 추가 상승, 뉴욕증시 하락 등 불안 심리에 7원 이상 추가 상승, NDF 역외 환율은 1,491.8원에 호가됨 금일 달러/원 환율은 국제유가 상승 및 역외 환율 급등을 반영하여 1,490원 수준에서 출발, 이후 국내 증시 조정과 최근 이어지고 있는 외국인 투자자의 주식 순매도, 국채 선물 매도 등의 강도에 따라 등락이 이어질 것으로 예상됨. 이란의 호르무즈 해협 봉쇄로 원유 수입 차질이 우려되고, 유가 상승과 환율 상승은 국내 물가상승에도 영향, 뉴욕증시 조정에 국내 증시에도 투자심리 위축 등이 불가피함. 정부의 유가 상한제, 시장 안정 조치 등이 예상되나, 변동성 장세는 당분간 이어질 것으로 예상됨 [글로벌 동향] 이란의 강경 대응에 국제유가 100달러 상회, 달러도 강세 전일 미 달러화 지수는 중동 전쟁이 고조되고 국제유가가 급등함에 따라 위험회피 및 국채 금리 상승 영향에 0.49% 상승함. 이란의 차기 지도자인 무즈타파 하메네이의 성명문이 공개된 가운데 이란은 호르무즈 해협을 봉쇄할 것이며, 전선은 확대될 것이라고 알려짐. 이란 차기 정부의 강경 대응에 국제유가는 더욱 상승, Brent 유가는 배럴당 100달러를 상회함. 유가 상승으로 전세계적인 물가 상승도 우려됨. 미국 국채 금리는 단기와 장기 모두에서 상승, 대표적인 10년물 국채 금리는 3.3bp 상승한 4.265%를 기록, 이란 전쟁 이후 장기금리는 20bp 이상 급등함. 유가 상승으로 가장 큰 타격을 받을 아시아 국가는 물론 유럽 경제 역시 과거 2022년 러우 전쟁처럼 유가 상승이 경제를 타격할 것으로 우려됨. 이란의 강경 대응으로 전쟁이 장기화될 위험과 유가 상승에 대한 불안감에 뉴욕증시는 3대 지수 모두 하락함 [마켓 이슈] 2022년과 2026년, 동유럽과 중동의 전쟁 및 국제유가 급등 미국과 이란의 전쟁이 발발한 지 2주일이 도래했고, 시장 개장 이후로는 10일째가 되고 있음. 양측의 포격과 공습 등으로 전세계 금융시장은 더욱 불안해지고 있고, 국제유가는 배럴당 100달러까지 상승, 전쟁 전 65달러 수준에서 약 50% 가까이 상승함. 미국 트럼프 대통령은 전쟁에서 한 발 빼려는 모습을 보이나, 이란에서는 차기 정부 수립과 강경 정권 유지, 추종 세력과 무장 세력 등이 반격과 보복에 나설 것이라고 주장하며 중동 전쟁은 좀처럼 진정되지 못하고 있음. 다만, 지난 2022년 2월 24일 러시아와 우크라이나의 전쟁 발발, 그리고 거래일 기준으로 10여일이 지난 이후에는 국제유가도 다소 진정, 하지만 이후 3개월 이상은 고유가 수준이 이어짐. 이번 2026년 미국-이란 전쟁에서도 유가 급등, 다음 주면 3주째가 되며, 유가의 변동성이 줄어들 수 있을지가 관건임</t>
+  </si>
+  <si>
+    <t>중동 불안 속, 기로에 선 원화 [금일 달러/원 환율 1,477~1,488원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 중동발 유가 불안 및 위험회피심리에 1,480원대로 상승 전일 달러/원 환율은 중동 호르무즈 해협을 둘러싼 불확실성에 상승 개장. 이후 당국 개입 경계에 추가 상승은 제한된 가운데, 장중 국제유가가 안정되고 미 달러화 지수가 하락한 것에 달러/원도 연동. 국내 증시 또한 호조를 보임에 따라 1,470원 선을 하회. 오후장에서는 1,460원대 등락, 전일 종가 대비 2.7원 하락한 1,466.5원에 정규장 마감. 야간장에서는 국제유가 상승에 연동하며 1,477.0원으로 상승 마감. 역외 NDF 환율은 13.10원 상승한 1,478.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 소폭 상승 개장 예상. 금일 장 역시 중동 전황 등 지정학적 리스크에 민감하게 반응하며 등락. 트럼프 대통령의 종전 시사에도 이란의 강경 대응에 종전 여부는 불확실. 국제유가 역시 각국 대응에도 불구하고 여전히 불안정. 글로벌 증시도 위험회피심리를 고스란히 반영하는 모습. 즉, 대내외 여건 상 원화 약세 자극 재료 산적. 금일 환율은 1,480원대로 상방 우세 전망 [글로벌 동향] 美 물가 예상 부합에도 이란 위협, 유가 불안에 달러 강세 전일 미 달러화는 예상에 부합한 미국 소비자물가에도 불구, 국제유가 불안에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.34% 상승한 99.26pt 기록. 미국의 2월 소비자물가지수는 전월 대비 0.3% 상승하며 예상에 부합. 2월 근원 소비자물가는 0.2% 상승하며 역시 예상에 부합. 이번 물가지표 결과에 특이할 만한 사항은 없었고, 국제유가 상승 등 전쟁 영향도 반영되지 않아 시장 영향은 제한적. 한편 국제유가는 중동 지역 불확실성이 지속되며 여전히 불안정한 흐름. WTI 국제유가는 전일 대비 5.98% 상승해 배럴당 88.44달러에 거래. 국제에너지기구 IEA는 이란 전쟁 대응의 일환으로 전략 비축유 4억 배럴 방출 결정. 이는 우크라이나 전쟁 이후 4년 만이며, 규모로는 역대 최대 방출량. 하지만 유가는 해당 소식에도 상승 흐름 지속. 이란은 해협을 지나는 모든 유조선이 공격 대상이이고 위협하며 유가 상승을 자극 [마켓 이슈] 변화하는 환경, 기로에 선 원화: 장기 약세 지속 vs. 추세 반전 최근 달러/원 환율은 장기간 이어진 상승 추세 속, 점차 1,500원이라는 레벨에 근접 중. 그동안 환율 상승을 이끌었던 요인들은 비교적 명확. 대외적으로는 달러화 강세와 엔화 약세, 지정학 리스크가 주요 배경. 대내적으로는 해외투자 확대에 따른 달러 수요 증가, 그리고 한미 금리 역전 등이 원화 약세 압력으로 작용. 다만 최근 들어 일부 여건 변화 조짐 포착. 미 달러화 지수는 2025년을 기점으로 하락 흐름. 한미 금리 역전 폭 역시 점차 축소. 국민연금 달러 수요는 투자 비중 조정과 환 헤지 확대, 외채 발행 계획 등에 둔화될 전망. 물론 서학개미 해외투자는 여전히 거세지만, 향후 RIA 계좌 도입 등 제도 변화가 매수세에 영향 줄 가능성. 여기에 역대급 실적을 기록 중인 반도체 수출 역시 외환 수급 여건 변화의 핵심 변수 중 하나. 반면 엔화 장기 약세와 이란 전쟁으로 인한 지정학 리스크 등 기존의 원화 약세 요인은 잔존</t>
+  </si>
+  <si>
+    <t>FOMC 이후 숨 고르기, 弱달러 국면은 유지 [금일 달러/원 환율 1,425~1,435원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 미 재무부 개입 부인에 반등, 이후 상승 폭 완만하게 축소 전일 달러/원 환율은 미국 소비심리 악화 및 트럼프 대통령의 약 달러 용인 발언에 갭 하락 개장. 이후 미 달러화 지수 반등에도 불구하고 국내 증시 호조 등 위험선호심리, 저가 매수보다 추격 매도가 우위를 보이며 1,420원까지 낙폭 확대. 오후장에서도 1,420원대 초반에서 등락, 전일 종가 대비 23.7원 하락한 1,422.5원애 정규장 마감. 야간장에서는 미 재무부의 엔화 개입 부인에 따른 엔화 약세 동조에 1,436.1원으로 반등 마감. 역외 NDF 환율은 8.35원 상승한 1,429.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래를 감안해 1,430원 부근 상승 개장 예상. 미국 환시 개입 부인 소식에 엔화 약세 되돌림, 원화도 일부 동조 예상. 더불어 전날 급락 분에 대한 저가 매수세 유입 역시 하단 지지 요소. 다만 여전히 글로벌 약 달러 국면은 유지되는 상황. 이에 따라 역내외 달러 매수 심리도 기대보다는 강하지 않을 가능성. 금일 환율은 개장 이후 상승 폭을 점차 줄여 나갈 것으로 예상 [글로벌 동향] 미 재무부 엔화 개입 부인에 달러 반등, FOMC는 동결 전일 미 달러화는 미국 재무부의 엔화 개입 부인 소식에 강세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.57% 상승한 96.39pt 기록. 스콧 베센트 재무장관은 엔화 매수 개입에 대해 '결코 그런 일은 없다'며 강하게 부인. 그는 '레이트 체크' 여부에도 답하지 않으면서 '강 달러 정책 고수'를 언급. 이에 달러당 엔화 환율은 152엔에서 단숨에 154엔 부근까지 급등. 미 달러화 지수 역시 96.2pt에서 96.7pt까지 상승. 하지만 이후 FOMC 회의 결과를 소화하며 강세 폭을 일부 반납. 금리는 예상대로 동결되었으나 인하 소수 의견이 두 명으로 확인. 스티븐 마이런 이사와 크리스토퍼 월러 이사가 금리 동결에 반대. 성명서에서는 성장과 고용에 대한 평가가 이전 대비 다소 개선. 인플레이션에 대해서는 '다소 높다'는 평가를 그대로 유지. FOMC에 대한 시장 반응은 다소 중립적. 미 국채금리 장단기물과 뉴욕증시 3대 지수는 모두 혼조 [마켓 이슈] FOMC 리뷰 - 평이했던 회의 결과, 달러화에는 중립적인 영향 29일 새벽 연준은 FOMC 회의에서 예상대로 금리를 3.50~3.75%로 유지. 동결의 배경은 지난 12월 금리 인하 이후 나온 경제지표들이 예상보다 양호했던 것에 있음. 성명서 문구에서 성장과 고용에 대한 평가는 개선, 인플레이션 상방 경계는 유지됨. 특이 사항으로는 금리 인하 소수 의견이 두 명이었다는 점. 스티븐 마이런 이사 외에 크리스토퍼 월러 이사가 반대표 행사. 이는 트럼프의 차기 의장 지명을 앞두고 월러 이사의 전략적 움직임이었던 것으로 해석. 기자회견에서 파월 의장 발언은 다소 평이. 연준 독립성 관련해서는 원론적인 입장을 반복. 미 달러화는 연준 금리 동결에도 불구, FOMC 이후 오히려 약세 전환 흐름. 현재 달러화에는 펀더멘털이나 통화정책보다는 트럼프 정책 리스크가 관건. 최근 들어 미 국채 2년물 금리와 미 달러화 지수 간의 관계는 '無 상관'. 이는 트럼프 정책 리스크가 불거질 때마다 나타나는 전형적 패턴</t>
+  </si>
+  <si>
+    <t>가속 붙는 달러/원 하락세(트럼프를 곁들인) [금일 달러/원 환율 1,422~1,437원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 미 달러화의 급격한 약세, 역내외 매도 우위에 하방 가속 전일 달러/원 환율은 트럼프의 한국 상호관세율 인상 발표에 따른 위험회피심리에 1,450원으로 상승 개장. 하지만 정부가 대응에 나섰다는 소식에 추가 상방은 제한적, 이후 글로벌 약 달러에 동조하며 상승 폭 축소. 오후장에서는 국내 증시 호조, 외국인 주식 순매수 등 위험선호심리 회복에 1,440원대 등락, 전일 종가 대비 5.6원 상승한 1,446.2원에 정규장 마감. 야간장에서는 미국 소비심리 악화에 1,437.5원으로 하락 마감. 역외 NDF 환율은 17.15원 하락한 1,427.40원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 10원 이상 급락 개장 예상. 트럼프 관세 충격은 제한적인 반면, 글로벌 달러의 급격한 약세가 달러/원에 직접적 영향. 특히 트럼프의 약 달러 용인 발언이 비달러 통화 강세를 유발하는 상황. 이에 달러/원 역시 롱 심리가 거의 소멸되며 하방에 가속이 붙을 전망. 수급적으로도 저가 매수를 뛰어넘는 추격 매도 물량이 나올 것으로 예상 [글로벌 동향] 미 달러화 지수 95pt로 급락-소비심리 악화, 트럼프 발언 전일 미 달러화는 미국 소비심리 악화 및 트럼프의 약 달러 용인 발언에 약세. 주요 6개국 통화로 구성된 달러화 지수는 1.21% 급락한 95.84pt 기록. 전날 환시에시도 미일 공조 개입에 대한 경계는 여전히 잔존. 일본 재무상은 필요시 미국과 긴밀하게 공조하겠다고 언급. 달러당 엔화 환율은 낙폭을 더 확대해 2025년 2월 이후 최저인 152.37엔 기록. 미국의 급격한 소비심리 악화가 달러화 약세를 유발. 컨퍼런스보드 1월 소비자신뢰지수는 84.5pt로 예상치인 91.0pt를 큰 폭 하회. 이는 2014년 5월 이후 최저이며, 팬데믹 발발 당시보다도 낮은 수준. 기대 지수는 65.1pt로 전월대비 9.5pt 급락 (침체 임계 레벨 80pt). 이에 선물시장에서 기대하는 연준 인하 횟수는 기존 1.8회에서 1.9회로 증가. 트럼프는 달러화가 제자리 (fair value)를 찾아가고 있다며 약 달러 용인 시사. 발언 직후 달러화 지수 낙폭 더욱 확대하며 95pt대 진입 [마켓 이슈] 1월 FOMC 프리뷰 - 소문도 안 난 잔치에 진짜 먹을 게 없다. 29일 새벽 미국 연준의 FOMC 결과가 발표될 예정. 하지만 이번 회의 자체가 시장에 의미 있는 변수가 될 가능성은 낮음. 금리 동결은 확실시되며, 선물시장의 동결 확률은 사실상 100%. 12월 FOMC 금리 인하 이후 나온 미국 경제지표들은 예상보다 양호. 씨티의 미국 경제지표 서프라이즈 지수는 약 5개월 만에 최고치로 상승. 연준이 추가 인하를 서둘러야 할 명분은 약화된 상황. 마이런 이사의 금리 인하 소수의견이 나올 수 있지만, 시장은 이를 '디폴트'로 인식. 파월 의장 기자회견 역시 '데이터 디펜던트'라는 원론적 입장 반복에 그칠 전망. 연준 독립성 훼손 관련 질문이 나와도, 시장에 새로울 메시지는 없을 것으로 보임. 현재 시장 관심은 FOMC 바깥에 있으며, 특히 트럼프發 정책 리스크가 관건. 현재 시장은 ① 트럼프의 차기 연준 의장 지명 ② 미국 연방정부 셧다운 우려 ③ 미일 재무당국의 외환시장 공조 개입 가능성에 초점</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 트럼프 관세 소식 vs. 대외적 약 달러에 상하방 변동성 전일 달러/원 환율은 미일 공조 개입 가능성에 대한 경계 심리에 약 20원 급락 개장. 이후 저가 매수에 낙폭 일부 축소했으나, 장중 추가적인 일본 엔화의 강세, 미 달러화 지수 하락에 연동하며 낙폭 확대. 오후장에서는 1,440원 부근에서 등락하다가, 장중 일시적으로 1,430원대 진입. 이후에도 매도 우위 이어지며 전일 종가 대비 25.2원 하락한 1,440.6원에 정규장 마감. 야간장에서는 저가 매수에 1,443.9원으로 반등 마감. 역외 NDF 환율은 8.05원 상승한 1,447.00원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,440원대 개장 예상. 개장 직전 트럼프의 한국 상호관세 25% 인상 소식에 1,450원 상회 예상. 이에 더해 역내 매수세 유입 시 상승 폭 더욱 확대될 가능성. 반면 미일 공조 경계, 미 셧다운 리스크 등 대외적으로는 약 달러 여건 유지. 더불어 국민연금 투자 비중 조정 등 국내 정책발 원화 가치 지지 요인도 상존. 금일 환율은 대내외 재료 혼재에 상하방 변동성 클 전망 [글로벌 동향] 미일 공조 개입 경계 잔존, 셧다운 가능성 부상에 약 달러 전일 미 달러화는 미일 공조 개입 경계와 미국 정책 리스크에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.51% 하락한 97.02pt 기록. 주말부터 불거진 미일 재무당국 공조 개입에 대한 경계가 시장에 여전히 잔존. 달러당 엔화 환율은 장중 153엔대까지 하락하며 강세 지속. 이에 유로화도 강세 동조하며 유로/달러는 1.188달러까지 급등. 미국에서는 트럼프 행정부의 정책 리스크가 부각되며 달러화에 약세 압력으로 작용. 미네소타주에서 이민단속국 (ICE) 총격 사건에 정부 셧다운 가능성 부상. 해당 사건에 민주당은 2026년 예산안 패키지 통과에 반대 입장 선언. 베팅사이트에서 금주 토요일 셧다운 돌입 확률은 70%대 급상승. 한편 트럼프 대통령은 한국의 상호관세율을 기존 15%에서 25%로 인상하겠다고 긴급 발표. 트럼프는 한국 국회가 한미 무역합의 비준 지연으로 미국과의 거래를 이행하지 않고 있다며 비난 [마켓 이슈] 차기 연준 의장에 릭 리더 부상, 물가보다 성장 및 고용에 초점 트럼프 대통령의 차기 연준 의장 지명이 임박. 이런 가운데 블랙록 글로벌 채권 CIO인 릭 리더 (Rick Rieder) 지명 가능성이 빠르게 부상. 외신에 따르면, 미 재무부는 최근 주요 채권 투자자들을 대상으로 릭 리더에 대한 의견을 타진. 베팅 시장 기준으로도 릭 리더 지명 확률이 1위로 급상승. 릭 리더는 이념보다는 시장을 더 중시하는 실용주의 성향으로 분류. 최근 주목할 발언으로는 '인플레이션은 이미 어제의 문제', '주택시장 차입 비용이 여전히 높다' 등. 이는 릭 리더 정책 초점이 물가보다는 성장과 고용 하방 리스크에 무게를 두고 있음을 시사. 즉, 릭 리더가 차기 의장으로 지명될 경우, 시장은 정책금리 경로의 하향 조정을 가격에 반영할 가능성. 이 경우 미 금리 하락으로 인해 달러도 완만한 약세가 예상. 다만 그는 '연준 독립성이 중요하다'고 언급한 만큼, 의장 지명 시 정책 신뢰 회복으로 인해 달러 하방 압력이 다소 완화될 여지도 존재</t>
+  </si>
+  <si>
+    <t>깜짝 관세 변수, 브레이크 걸린 달러/원 하락세 [금일 달러/원 환율 1,440~1,455원 전망]</t>
+  </si>
+  <si>
+    <t>떨어지는 칼날은 붙잡지 않는 법 [금일 달러/원 환율 1,437~1,452원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 1,440원대 갭 하락 개장, 이후 수급에 따라 큰 폭 변동 전일 달러/원 환율은 러우 종전 기대로 인한 달러 약세에 1,465원으로 하락 개장한 뒤, 미 달러화 지수 반등 및 저가 매수에 낙폭 일부 되돌림. 이후 일본 BOJ 금정위를 경계하며 박스권 등락하다가, BOJ의 매파적 기조 확인하며 1,464원까지 낙폭 확대. 이후 다시 하단 지지되며 전일 종가 대비 4.1원 하락한 1,465.8원에 정규장 마감. 야간장에서는 큰 이벤트 없이 등락하며 1,462.5원으로 하락 마감. 역외 NDF 환율은 미일 공조 개입 가능성에 19.55원 급락한 1,444.60원에 최종 호가 금일 달러/원 환율은 주말간 달러 약세와 역외 거래 감안해 1,440원대 갭 하락 개장 예상. 장중 저가 매수 유입에 일시 반등하며 낙폭 일부 축소 예상. 하지만 미일 공조 등 개입 경계 이어지는 가운데, 엔화 강세에 반등 여력은 제한적. 더불어 수출업체 추격 네고 가세할 경우 하락 폭 도리어 확대될 소지. 금일 환율은 대외적 하방 압력 이어지는 가운데, 수급에 따라 큰 폭의 변동성 예상 [글로벌 동향] 미일 환시 공조 개입 가능성에 달러/엔 급락, 미 달러 약세 전일 미 달러화는 미국과 일본 재무당국의 환율 공조 개입 가능성에 급격한 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.83% 하락한 97.52pt 기록. 전날 일본 BOJ의 통화정책회의 이후, 유럽장에서부터 엔화 환율이 하락하기 시작. BOJ 총재 기자회견 직후 당국 개입 추정 움직임에 일시 급락. 이후 다시 반등했으나, 이내 다시 하락하기 시작. 미국 뉴욕 연은이 런던 외환시장에 달러/엔 레이트 체크 (rate check)를 했다는 소식이 전해짐. 이에 따라 시장 내에서 미일 공조 개입 가능성이 불거지며 엔화 환율은 1.65% 급락. 달러/엔 환율은 155엔으로 급락하며 2025년 12월 이후 최저치 기록. 엔화 강세에 동조해 유로화 역시 급격한 강세 시현. 유로/달러 환율은 0.62% 상승한 1.182달러로 2025년 9월 이후 최고치 기록. 영국 파운드화도 1% 이상 미 달러화 대비 절상. 그 외 미 달러화 지수 구성 통화 (CAD, SEK, CHF) 모두 강세로 마감 [마켓 이슈] 미일 공조 개입에 환시 변동성 확대, 원화와 엔화 변곡점인가? 미일 재무당국의 환시 공조 개입 가능성이 불거지며, 달러/엔과 달러/원 NDF 환율이 급락. 최근 들어 미일 공조 개입에 대한 시그널은 지속적으로 확인된 상황. 달러/엔이 현재 160엔 빅 피겨 근처에 근접, 과거 2024년에도 빅 피겨에 근접할 때마다 당국의 달러 매도 개입이 있었던 사례. 또한 스콧 베센트 재무장관의 이례적인 구두 개입 역시 공조 개입의 시그널로 해석 가능. 마지막으로는 트럼프 행정부가 만성적인 무역적자를 문제 삼고 있는 상황에서, 주요 교역국 통화 가치 절하를 더 이상 용인할 수 없었던 것도 개입의 배경. 금일 달러/원은 NDF 급락을 반영해 갭 하락 개장할 것으로 예상. 관건은 우선 추격 네고가 가세하며 환율 레벨을 더욱 낮출지, 아니면 저가 매수가 대거 유입되며 기술적 반등이 나타날지 여부. 그 외 고려할 변수로는 달러 급락에 따른 대만 생보사의 프록시 헤지 개시 여부. 이 경우 달러/원 하락 쏠림이 더욱 강화될 가능성</t>
+  </si>
+  <si>
+    <t>매운맛 BOJ가 원화 강세 자극할까? [금일 달러/원 환율 1,459~1,469원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 금일 BOJ의 매파적 시그널 경계, 엔화에 원화도 동조 전일 달러/원 환율은 전날 대통령 환율 발언 및 국민연금 국내 비중 축소 소식 등에 하락 개장. 이후 추가로 하락하며 1,464원까지 저점 낮췄으나, 저가 매수세에 하단 지지되며 반등 시도. 오후 장중 엔화 약세 전환에 원화도 동조하며 낙폭을 상당 부분 되돌림. 1,470원 부근에서 등락하다가 전일 종가 대비 1.4원 하락한 1,469.9원에 정규장 마감. 야간장에서는 러우 종전 기대 등 유로화 강세 동조하며 1,464.5원으로 하락 마감. 역외 NDF 환율은 5.65원 하락한 1,462.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 하락 개장 예상. 미국 PCE 등 주요 매크로 이벤트 끝난 가운데, 금일은 BOJ 회의 등 정책 변수에 주목. BOJ의 금리동결이 유력하나 '조기 인상 필요' 등 매파적 시그널 기대. 이 경우 엔화 강세에 원화가 동조하며 달러/원 추가 하락 예상. 다만 여전히 탄탄한 역내 달러 매수 등 수급 불균형은 하단 지지 요소. 금일 환율은 BOJ 주시하며 하방이 우세한 흐름 보일 전망 [글로벌 동향] 미국 경제지표는 대체로 호조, 러우 종전 기대에 약 달러 전일 미 달러화는 미국 경제지표 소화하는 가운데, 러우 종전 기대에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.46% 하락한 98.33pt 기록. 미국 11월 개인소비지출 (PCE) 가격지수는 시장 예상에 부합. 전품목과 근원 PCE 물가는 모두 전월대비 0.2% 상승. 명목PCE는 0.5% 증가, 개인소득은 0.3% 증가하며 양호한 흐름. 반면 저축률은 7개월 연속 하락, 11월 3.5% 기록. 이처럼 낮은 저축률은 가계 소비 여력이 줄어들고 있음을 시사. 3분기 실질 성장률 수정치는 기존 4.3%에서 4.4%로 소폭 상향 조정. 이 같은 성장 실적은 2023년 3분기 이후 2년 만에 최고치. 경제지표 호조에도 불구하고, 러우 종전 기대가 약 달러 촉발. 미국 트럼프 및 우크라 젤렌스키 대통령은 스위스에서 1시간 동안 회담. 트럼프는 이번 회담이 좋았다고 평가하며 종전 기대를 자극. 종전 수혜 지역인 유럽의 유로화가 달러 대비 0.53% 절상, 유로/달러는 1.17달러 상회 [마켓 이슈] 日 장기금리 급등이 엔 캐리 트레이드 청산 유발? 과도한 우려 최근 일본 장기물 국채금리 급등을 계기로 엔 캐리 트레이드 청산 우려가 고개를 드는 모습. 하지만 이를 곧바로 캐리 청산으로 연결하는 것은 다소 과도한 해석이라는 판단. 가장 최근 캐리 청산 사례였던 2024년 7~8월을 보면, 금리차라는 표면 아래 복합적 배경이 존재. 당시에는 미국 실업률 상승에 따른 경기침체 우려로 미 국채금리가 급락. 동시에 BOJ의 깜짝 인상으로 일본 단·중기 국채금리가 상승하며, 캐리의 핵심인 단기 금리차가 급격히 축소. 즉 미 경기 불안, 정책 서프라이즈, 단기 금리차 축소가 동시에 작동한 국면. 반면 현재 미국 경기는 실업률 하락 등 양호한 지표, 미 국채금리는 상승. 금일 BOJ의 깜짝 금리인상 가능성도 매우 제한적. 캐리 트레이드가 단기 조달금리에 기반한다는 점을 감안하면, 현 국면에서 청산 압력은 약해 보임. 금일 BOJ가 매파적 시그널을 낸다면 일부 포지션 조정 가능하나, 시장에 충격을 줄 정도는 아니라는 판단</t>
+  </si>
+  <si>
+    <t>서서히 열리는 달러/원 하단 [금일 달러/원 환율 1,460~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 정부 의지 확인, 위험선호심리 회복에 1,460원대 하락 전일 달러/원 환율은 그린란드 갈등과 셀 아메리카에 따른 위험회피심리에 1,480원 상승 개장. 이후 대통령의 환율 하락 예측 발언에 급락한 뒤, 곧 이어 국민연금의 국내 투자 비중 확대 소식에 낙폭 더욱 확대. 장중 저가 매수세 유입되며 낙폭 일부 되돌림, 전일 종가 대비 6.8원 하락한 1,471.3원에 정규장 마감. 야간장에서는 외신 보도에서 올해 대미투자 200억 달러 연기 가능성 소식에 재차 하락하며 1,465.9원으로 마감. 역외 NDF 환율은 6.40원 하락한 1,463.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 반등에도 역외 거래를 감안해 1,460원대 개장 예상. 전날 대통령 환율 발언과 국민연금 국내 비중 확대 소식, 대미투자 연기 가능성 등이 환율 하방에 영향. 정부의 전방위적인 환율 안정 의지 확인되며 금일에도 하락 흐름 유지 예상. 트럼프의 그린란드 관세 철회에 회복된 위험선호심리 역시 원화에 긍정적 영향. 일부 저가 매수 유입에도 불구, 대내외 하방 압력에 반등 여력은 제한적일 전망 [글로벌 동향] 그린란드 관세 전격 철회, TACO 트레이드에 달러 반등 전일 미 달러화는 트럼프의 그린란드 관세 철회 등으로 인해 반등. 주요 6개국 통화로 구성된 달러화 지수는 0.20% 상승한 98.79pt 기록. 트럼프는 최근 그린란드 사태로 불거진 '셀 아메리카'에 부담 느끼고 한 발 물러선 상황. 그는 다보스 포럼 연설에서 그린란드 관련해 무력 사용은 없을 것이라고 약속. 이후에는 유럽 8개국에 예고한 관세 조치도 취소하기로 결정. 금융시장은 그린란드 철회 소식에 긍정적인 반응. 우선 뉴욕증시 3대 지수 모두 장중 상승 폭 확대하며 마감. 미 국채금리도 국채 매도 재료 소멸되며 장단기물 대체로 하락. 미 달러화 역시 그간의 약세를 되돌리며 반등에 성공. 유로/달러 환율은 0.28% 하락해 기존 1.17달러 선을 하회. 한편 트럼프 대통령은 차기 연준 의장 지명이 가까워졌음을 시사. 현재 시장에서는 케빈 워시, 릭라이더를 유력 후보로 여기는 상황. 트럼프는 라이더와의 면담이 인상적이었다고 밝힘 [마켓 이슈] 해외주식투자 둔화, 국내투자는 가속... 수급 변화의 초기 신호 거주자의 해외주식 순매수 흐름은 유지되고 있으나, 보관금액 (예탁금)의 증가 속도는 둔화. 1월 현재 해외주식 보관금액은 1,777억 달러 (작년 말 대비 2.4% 증가). 절대 규모는 크지만 증가 탄력은 다소 약화된 모습. 반면, 국내주식 예탁금은 빠르게 증가 (+8.8%, 금액 95.5조원, 사상 최대치). 이는 단순 유동성 확대라기보다 자산 배분의 전략 변화로도 해석 가능. 이 같은 변화는 최근 미국 대비 한국 증시의 상대 매력도가 부각된 것에 기인. 여기에 작년 말 정부의 달러 수급 개선 조치, 특히 해외주식 매각 후 국내 투자시 양도소득세 감면 (RIA)의 효과가 완만하게 반영되는 국면. 핵심은 그간 역내 수급 불균형을 키웠던 해외투자發 달러 수요가 이제는 정점을 통과했을 가능성. 아직 급격한 변화는 아니나, 수급 변화의 초기 신호는 포착되는 상황. 여기에 글로벌 달러 약세까지 가세한다면, 달러/원에는 상방보다는 하방이 더욱 열려있다는 판단</t>
+  </si>
+  <si>
+    <t>상하방 리스크가 공존하는 달러/원 [금일 달러/원 환율 1,475~1,483원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험회피에 막한 하방, 당국 경계에 상단 역시 제한적 전일 달러/원 환율은 미국-유럽 그린란드 갈등에 따른 달러 약세에도 상승 개장한 뒤 장중 미 달러화 지수 반등에 연동해 1,479원까지 추가 상승. 하지만 1,480원 부근 당국 개입 경계 및 고점 매도에 상승 폭 줄였으나, 외국인의 국내 주식 순매도 등 역내 매수 우위의 수급 불균형에 하방도 제한적 전일 종가 대비 4.4원 상승한 1,478.1원에 정규장 마감. 야간장에서는 달러 약세 및 고점 매도에 소폭 하락하며 1,476.7원으로 마감. 역외 NDF 환율은 2.65원 상승한 1,479.10원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 1,480원 부근 개장 예상. 셀 아메리카 분위기로 글로벌 달러 약세지만, 동시에 위험자산에도 부정적 국면. 이에 따라 유로화 등 선진국 통화는 강세, 반면 위험통화인 원화는 혼조 예상. 위험회피에 따른 국내증시 조정도 달러/원 하단 지지 요소. 다만 1,480원대 당국 개입 경계에 추가 상방은 제한적. 금일 환율은 위험회피 속 상단 경계에 박스권 등락 예상 [글로벌 동향] 덴마크 연기금의 미 국채 전량 매도 계획 등 '셀 아메리카' 전일 미 달러화는 그린란드 갈등 여파 속, 미 국채 등 달러 자산 매도 분위기에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.45% 하락한 98.59pt 기록. 미국의 유럽 8개국 관세 위협, 이에 대한 상대국의 보복 조짐 등 갈등 심화 양상. 트럼프는 프랑스 와인 및 샴페인에 200% 관세 예고. 덴마크는 그린란드 추가 병력 투입에 이어 연기금 동원까지 계획. 덴마크 연기금 아카데메커펜션은 이달 말까지 1억 달러 규모 미 국채 전량 매도 예정. 연기금 CIO는 국채 매도 배경으로 미국 정부의 재정 불안정성 지목. 이에 시장에서는 '셀 아메리카' 분위기 불거지며 미 국채금리는 급등. 10년물 금리는 6.8bp 급등해 4.3%에 근접. 한편 달러 약세에도 상대적으로 엔화 퍼포먼스는 부진. 일본 정부의 감세 조치가 재정 우려 자극하며 장기 국채금리가 급등. 이에 달러/엔은 0.05% 상승해 158엔 부근 등락. 유로/달러는 미 자산 신뢰 약화에 1.17달러 상회 [마켓 이슈] '구매력평가'와 '재귀성 이론' 관점에서 본 달러/원 하방 리스크 장기적인 환율 수준은 각국의 물가 수준, 즉 구매력 차이에 의해 결정. 구매력평가설 (PPP)에 따르면, 상대적으로 물가가 낮은 국가의 통화가 강세를 보이는 경향. 한미 CPI로 추정한 달러/원 장기 적정환율 (PPP환율)은 2010년대부터 점진적으로 하락. 그러나 달러/원의 명목환율은 2020년대 들어 PPP환율의 역사적 평균 범위를 상회. 이러한 괴리는 해외투자 등 구조적 달러 수요 요인 외에, 시장 '가격'이 시장 '여건'을 왜곡하는 현상에도 기인. '환율 상승→추가 상승 기대→달러 보유 성향 강화→수급 왜곡→추가 상승'의 경로가 작동. 이는 조지 소로스가 주장한 '재귀성 이론'의 전형적 모습. 하지만 해당 이론의 중요한 결론은 '일방향적인 가격 형성 과정'보다는 '끝나는 방식'에 있음. 재귀적으로 형성된 가격은 반드시 조정 국면을 겪으며, 그 과정은 매우 급격히 나타난다는 것. 이를 감안하면, 현재 달러/원에는 하방 리스크가 크다는 판단</t>
+  </si>
+  <si>
+    <t>그린란드 사태, 원화 반전의 트리거인가? [금일 달러/원 환율 1,469~1,477원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 역내 수급 불균형, 당국 경계에 1,470원대 박스권 등락 전일 달러/원 환율은 미국 그린란드 갈등에 따른 위험회피에 1,474원으로 상승 개장 이후 미 달러화 지수 하락 연동 및 고점 매도에 1,470원까지 하락. 하지만 이내 저가 매수세 유입에 반등한 가운데, 1,475원에서는 상단 인식. 오후장에서는 1,470원대 초중반 좁은 박스권 레인지 등락하며, 전일 종가 대비 0.1원 상승한 1,473.7원에 정규장 마감. 야간장에서는 미국 휴장으로 한산한 가운데, 보합권에서 등락하며 1,473.1원으로 마감. 역외 NDF 환율은 0.10원 하락한 1,471.90원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 보합권 개장 예상. 미국 휴장으로 특별한 이벤트 없는 가운데, 역내 환시는 주로 수급에 의해 주도. 수급 여건은 여전히 달러 수요 우위인 장세로 1,470원대 고환율 구간 유지 예상. 반면, 당국의 안정 의지 및 고점 인식에 1,480원이 상단으로 작용. 금일 환율 역시 수급 불균형과 당국 경계에 상하단 모두 막힌 박스권 등락 예상 [글로벌 동향] 미국 마틴 루터 킹의 날로 휴장, 그린란드 여파에 약 달러 전일 미 달러화는 미국 금융시장 휴장인 가운데, 그린란드 이슈 소화하며 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.33% 하락한 99.04pt 기록. 19일 미국 마틴 루터 킹의 날로 인해 주식 및 채권 시장이 휴장. 미국과 덴마크 등 유럽 국가들의 그린란드 관련 갈등은 지속 중. 주말 트럼프 대통령은 그린란드에 군을 투입한 유럽 8개국에 관세 부과 위협. 이에 유럽연합은 긴급 정상회의를 소집하며 보복 조치 등을 논의. 덴마크는 그린란드에 100여명의 병력을 추가 투입하며 사태 격화. 일각에서는 이번 사태로 지난해 4월의 '셀 아메리카'가 재현될 수 있다고 경고. 지난해 4월 미국 트럼프의 고율 관세 충격으로 미 국채금리 급등, 달러 급락 현상 발생. 이번에도 그린란드 사태 발생 직후 국채금리는 장단기물 상승, 달러화 지수는 하락으로 반응. 다만 미국 경제의 견고한 성장세를 근거로 과거 현상이 재현되지 않을 가능성도 상존 [마켓 이슈] 달러/원 방향 전환의 필요조건: 글로벌 미 달러의 급격한 약세 최근 달러/원 환율은 뚜렷한 조정 없이 상승 흐름 이어가는 중. 이는 역내 시장 전반에 형성된 달러 매수 우위의 쏠림 구조 탓. 외환당국의 각종 시장안정 조치에도 불구하고, '달러 매수'로 치우쳐진 심리는 여전히 지속. 이는 현재 환율 레벨이 '국내 변수'만으로 조정될 수 있는 국면이 아님을 시사. 쏠림 국면 반전을 위해서는 역외, 즉 해외에서의 충격이 필요하다는 판단. 실제 2025년 상반기 관세 충격으로 미 달러화 지수가 급락, 달러/원도 하락 동조. 이 과정에서 대만 생보사들의 원화 프록시 헤지 물량까지 가세, 하락 쏠림 더욱 심화. 반면, 2025년 하반기에는 미 달러화 지수가 대체로 보합권 등락. 이 시기 달러/원은 대외 충격이 부재한 상태에서 주로 역내 수급과 심리에 의해 등락. 향후 달러/원 방향 전환의 출발점은 글로벌 달러의 급격한 약세. 이번 그린란트 사태 등으로 인한 미국 정책 신뢰 훼손 등이 급격한 약 달러의 트리거가 될 가능성</t>
+  </si>
+  <si>
+    <t>美·日 '정책 리스크' 주시하는 달러/원 [금일 달러/원 환율 1,470~1,478원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 유럽 관세 등 대외 불확실성, 역내 달러 수요에 혼조 예상 전일 달러/원 환율은 미국 경제지표 호조로 인한 달러 강세에 1,470원에서 개장한 이후, 일본 재무당국의 구두 개입에 따른 엔화 강세와 외국인의 국내 주식 순매수에도 불구하고, 역내에서 달러 매수가 우위를 보이며 1,475원까지 상승. 오후장에서는 특별한 재료 없이 박스권 등락하며 전일 종가 대비 3.9원 상승한 1,473.6원에 정규장 마감. 야간장에서는 당국 경고에도 꾸준한 매수세에 상승하며 1,474.5원으로 마감. 역외 NDF 환율은 0.35원 상승한 1,472.50원에 최종 호가 금일 달러/원 환율은 주말간 달러와 역외 거래 감안해 보합권 개장 예상. 미국 트럼프 행정부의 유럽 관세 부과와 해당국들의 보복 검토 소식이 금일 환시의 주 재료. 이에 따른 유로화 약세 및 위험회피가 원화에는 부정적 영향. 반면, 일본 당국의 환시 개입 관련 발언 시, 엔화 강세에 원화도 일부 동조 예상. 여전히 꾸준한 역내 달러 수요는 하방 제약 요인. 금일 환율은 대외 불확실성과 수급 불균형에 1,470원대 등락 예상 [글로벌 동향] 日 당국 환시 개입 가능성 대두, 트럼프 對유럽 관세 조치 전일 미 달러화는 일본 외환당국의 개입 가능성에 약세 보이다가, 차기 연준 의장 이슈 소화하며 반등하며 약 보합. 주요 6개국 통화로 구성된 달러화 지수는 0.02% 하락한 99.37pt 기록. 가타야마 사쓰키 일본 재무상은 당국의 시장 개입이 미국과의 합의에 포함된 내용이라고 언급. 그는 미국과의 공조 가능성에 대해서 어떤 옵션도 배재하지 않을 것이라고 첨언. 이에 엔화가 강세 압력을 받으며, 달러/엔 환율은 0.35% 하락해 158엔 초반에 근접. 이후 달러화 지수는 뉴욕장 들어 트럼프 대통령의 차기 연준 의장 관련 발언 소화하며 반등. 트럼프 대통령은 연준 의장 유력 후보인 케빈 해싯 위원장을 현직에 두고 싶다고 언급. 한편 트럼프는 미국의 그린란드 합병에 반하는 유럽 8개국 대상으로 관세 부과 발표. 2월 1일부터 10%, 6월 1일부터 25%의 관세 부과 방침. 이에 프랑스 등 대상 국가들은 트럼프의 관세 조치에 반발하며 보복 등 맞대응 예고 [마켓 이슈] 금주 한국 GDP 영향력은 제한적, 그보다는 '정책 변수'가 관건 지난해 12월 달러/원 환율은 단기간 약 50원 급락한 뒤, 연초부터 연이은 상승 흐름에 현재는 1,470원대 진입. 이 같은 변동성의 근저에는 일본 엔화 약세와의 연동, 그리고 여전히 지속 중인 역내 달러 수급 불균형이 있음. 한편 지난주 미국 CPI 지표를 끝으로 당분간 매크로 이벤트는 종료. 최근 환율은 국내 펀더멘털 변수에 둔감하게 반응하기 때문에 금주 한국 GDP의 영향력은 제한적. 그보다는 최근 베센트 미 재무장관의 구두 개입 등으로 부각된 한미일 정책 공조가 관건. 3국 재무당국의 강한 구두 개입이나 일본 당국의 환시 직접 개입 등이 나타난다면, 달러/원이 일시적으로 강한 하방 압력을 받을 전망. 이 경우 달러/원은 단기적으로 50일 이동평균선인 1,460원대 초반까지는 하락이 가능. 하지만 상기의 정책 이벤트가 발생하지 않는다면, 역내 달러 수요 우위의 수급 불균형으로, 달러/원은 1,470원대 고환율 구간에서 등락할 전망</t>
+  </si>
+  <si>
+    <t>환율 안정 위한 三國 공조 나올까? [금일 달러/원 환율 1,467~1,475원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대내외 상방 압력에 1,470원대 복귀, 한미일 공조 변수 전일 달러/원 환율은 미국 재무부의 구두 개입에 급락하며 1,465원으로 개장. 하지만 곧 바로 저가 매수세가 유입되며 낙폭 줄여 나간 가운데, 한국은행의 매파적 금통위 결과에도 불구하고 달러 매수 지속되며 1,470원 부근에서 등락. 오후장 내내 하방이 제한된 움직임을 보이며, 전일 종가 대비 7.8원 하락한 1,469.7원에 정규장 마감. 야간장에서는 한은 금리동결 여파 이어지는 가운데, 강 달러에 1,469.2원으로 보합권 마감. 역외 NDF 환율은 0.60원 상승한 1,468.80원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,470원 부근 개장 예상. 미 경제지표 호조에 따른 달러 강세가 달러/원 상방 자극. 일본 엔화 역시 원화에 여전히 부정적 영향. 더불어 역내 꾸준한 달러 매수세가 환율 하단을 지지하는 형국. 다만 한미일 환율 관련 정책 공조 경계가 상방을 일부 억제하는 요소. 금일 환율은 정책 변수 경계 속, 대내외 상방 압력에 1,470원대 복귀 예상 [글로벌 동향] 미 고용 및 제조업 지표 호조, 연준 인사 발언에 달러 강세 전일 미 달러화는 미국 경제지표 호조와 연준 인사들 발언 소화하며 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.28% 상승한 99.39pt 기록. 미 실업수당 청구건수는 19.8만명으로 예상치 (21.5만명)와 전주치 (20.7만명) 모두 하회. 이처럼 고용지표가 양호한 가운데, 지역 제조업 경기업황도 개선. 뉴욕 연은 1월 제조업 지수는 7.7pt로 예상치 (1.0pt)와 전월치 (-3.7pt) 모두 상회. 뉴욕 연은 관계자는 제조기업들이 여건 개선을 기대하며 낙관적 태도를 유지하고 있다고 언급. 이 같은 경제지표 실적에 미국 국채금리는 장단기 대체로 상승. 연준 위원들은 양호한 성장전망을 바탕으로 금리인하 신중론 시사. 메리 데일리 총재는 노동시장이 안정적이라며, 이중 책무 달성을 위해선 신중할 필요가 있다고 언급. 제프리 슈미드는 현 시점에서 추가 금리인하 근거를 찾지 못했다고 발언. 애나 폴슨은 물가 안정을 위해 당분간 현 금리를 유지해야 한다고 언급 [마켓 이슈] 단기 환율의 초점, 매크로 변수에서 '한미일 정책 공조'로 이동 지난 14일 스콧 베센트 미국 재무장관의 환율 관련 발언은 외환시장에서 주목할 만한 정책 신호로 평가. 특히 이번 발언에서는 원화가 명시적으로 언급, 과거보다 한 단계 수위 높은 구두 개입으로 해석. 전주 미국 고용과 금주 물가 등 주요 매크로 이벤트가 일단락. 즉 앞으로 당분간은 경제지표보다 외교적 공조 등 환율 정책 변수가 환시를 주도할 가능성. 과거 사례에서도 한미일 재무당국의 환율 관련 발언이나 협의 소식은 단기 변동성을 유발. 2024년 4월 한미일 재무장관 및 6월 한일 재무장관 공동 발언, 2025년 5월 한미 재무당국 간 환율 협의 보도 직후 달러/원은 단기 하락 압력에 노출. 여기에 더해 일본 외환당국의 환시 개입 가능성도 여전히 유효한 변수. 특히 다음 주 월요일 (19일)은 미국 휴장으로 인해 글로벌 외환시장 유동성이 얇아지는 시점. 이는 일본 외환당국이 선호할 '효과적인 환시 개입 타이밍'과도 부합한다는 판단</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 미국 구두 개입에 급락, 추격 네고 등에 하락 쏠림 주의 전일 달러/원 환율은 일본 확장 재정 우려에 따른 엔화 약세 영향에 상승 개장한 이후 1,479원까지 추가 상승. 이후 당국 개입 경계와 고점 매도에 장중 1,475원까지 하락. 하지만 외국인의 차익 실현성 국내주식 매도세와 수입 결제 등 달러 수요 우위에 재차 반등, 전일 종가 대비 3.8원 상승한 1,477.5원에 정규장 마감. 야간장에서는 미국 재무부의 과도한 원화 약세 발언 등 환시 구두 개입에 급락하며 1,464.0원으로 마감. 역외 NDF 환율은 14.75원 하락한 1,461.20원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,460원대 급락 개장 예상. 미국 재무부의 원화 구두 개입에 역내 달러 롱 심리 완화 예상. 이에 추격 네고나 금일 금통위 환시 관련 발언까지 가세할 경우 하락 쏠림 더욱 심화. 이 경우 달러/원은 장중 1,450원대 진입도 가능. 다만 급락에 따른 저가 매수는 하단을 지지하는 요인. 금일 환율은 강한 하방 압력 속, 반발 매수에 계단식 하락 패턴 보일 전망 [글로벌 동향] 미 재무부 구두 개입, 한국 원화 및 일본 엔화의 강세 전환 전일 미 달러화는 미국 소비 호조에도 재무부의 환시 구두 개입에 약 보합. 주요 6개국 통화로 구성된 달러화 지수는 0.04% 하락한 99.11pt 기록. 미국의 11월 소매판매는 전월비 0.6% 증가하며 예상치 (+0.5%) 및 전월치 (0.0%) 상회. 11월 생산자물가는 전월비 0.2% 상승하며 예상치에 부합. 같이 발표된 10월 생산자물가는 0.1% 상승에 그침. 한편 연준 위원들의 다소 완화적 발언에 국채금리는 장단기 대체로 하락. 애나 폴슨 총재는 물가가 안정되면 추가 금리인하에 나설 수 있다고 언급. 스티븐 마이런 이사는 트럼프 행정부의 규제 완화로, 완화적인 정책이 필요하다고 주장. 스콧 베센트 재무장관은 최근 원화 약세가 바람직하지 않다고 언급. 그는 원화 가치가 펀더멘털에 부합하지 않으며, 과도한 변동성은 바람직하지 않다고 밝힘. 이에 야간장에서 달러/원 환율은 10원 이상 급락. 원화와 동조하는 엔화 환율 역시 하락하며 158엔대에 진입 [마켓 이슈] 고환율 대응을 위한 금리인상? 편익보다는 비용이 더 큰 선택 금일 금통위를 앞두고 최근 고환율이 통화정책 판단에 어떤 영향 미칠지에 관심 증대. 최근 한국은행은 금융불안을 경계하며 정책 스탠스를 '인하'에서 '동결'로 선회. 다만 고환율 만을 이유로, 향후 금리인상 가능성은 제한적이라는 판단. 작금의 환율 상승은 단순 금리 수준보다는 한미 잠재성장률 격차 확대, 해외투자 증가에 따른 구조적 달러 수요가 주 원인. 또한 한국은행이 추정한 환율→물가 전이 효과도 제한적 (환율 10% 상승→물가 0.3%p 상승). 즉 현재 물가상승률이 2%대에 머물러 있다는 점에서 긴축 전환 명분은 충분치 않음. 더욱이 내수 여건은 여전히 금리인상에 취약한 상황. 수출은 양호하나, 소비 회복은 더디고 건설경기 침체가 지속되고 있기 때문. 이 같은 상황에서 금리인상은 환율 안정이라는 편익보다 경기하방 압력이라는 비용이 더 크다는 판단. 고환율 대응의 핵심은 수급 쏠림 완화 등 단기 변동성 관리와 성장 잠재력 확충에 있음</t>
+  </si>
+  <si>
+    <t>베센트 가라사대 "원화 약세가 과도하구나" [금일 달러/원 환율 1,457~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>아무도 원화에 웃어주지 않는다 [금일 달러/원 환율 1,470~1,479원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 엔화-원화의 약세 동조, 당국 경계에 1,470원대 등락 전일 달러/원 환율은 연준 독립성 훼손 우려에 따른 달러 약세에도 1,460원대 후반 보합권 개장. 장중 달러 매수 우위 흐름 이어지는 가운데, 일본 엔화 약세에 동조하며 장중 1,470원 상회. 이후 당국 개입 경계에도 불구하고 외국인의 국내주식 순매도 등 수급 부담에 1,470원대에서 등락, 전일 종가 대비 5.3원 상승한 1,473.7원에 정규장 마감. 야간장에서는 일본 엔화 약세에 영향 받으며 1,478.8원으로 상승 마감. 역외 NDF 환율은 3.95원 상승한 1,476.00원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,470원대 중반 개장 예상. 미국 소비자물가는 예상 하회했지만, 글로벌 환시 영향력은 제한적. 그보다는 엔저가 원화에 영향 미칠 재료. 엔화 프록시인 원화가 일부 약세 동조하며 달러/원 하단 지지. 한편 외국인 순매수와 환율 하락의 연계성 약화로, 증시 측면에서도 원화에는 긍정적 재료가 부재. 금일 환율은 대외적 상방 압력 속, 당국 경계에 제한적 상승 시도 예상 [글로벌 동향] 美 근원 소비자물가 예상 하회, 日 확장 재정 우려에 엔저 전일 미 달러화는 미국 인플레이션 압력 둔화에도 불구, 엔저 영향에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.24% 상승한 99.15pt 기록. 미국 12월 소비자물가는 대체로 시장 예상치 하회. 전품목 물가지수는 예상에 부합했지만, 근원 물가는 예상치 하회. 근원 물가는 전월비 0.2%, 전년비 2.6% 상승하며 예상치를 각각 0.1%p 상회. 이에 미 국채금리 장단기물도 소폭 하락하며, 달러에 일부 약세 압력 제공. 하지만 시장 관심이 고용에 집중되어 있어, 이번 CPI의 영향력은 제한적. 그보다는 일본 엔화의 초 약세가 달러화 지수 상방에 기여. 달러당 엔화 환율은 159엔을 상회하며 2024년 7월 이후 최고치 기록. 일본 BOJ 추가 인상 기대에도 불구, 정부 확장 재정에 대한 우려가 엔저에 영향. 현지 언론에 따르면, 다카이치 사나에 총리는 1월에 중의원 해산을 계획. 조기 총선 일자는 2월 8일 또는 15일, 두 날짜가 유력한 것으로 보도 [마켓 이슈] 외국인의 주식 순매수가 환율 하락으로 이어지지 않는 이유는? 최근 외국인의 국내 주식 순매수에도 불구, 달러/원 환율은 뚜렷한 하락 반응을 보이지 않는 모습. 과거 10년간 일별 데이터 기준으로 보면, 외국인 순매수일 중 환율 하락이 동반된 비율은 평균 58.3%. 특히 2020~2023년에는 해당 비율이 60%를 상회하며 비교적 명확한 연결 고리. 그러나 2024년 들어, 이 비율이 50%대 초반까지 낮아지며 외국인 순매수와 환율 하락 간의 관계가 약화. 이는 최근 외국인의 주식 매수 방식이 환오픈에서 환헤지 방식으로 전환되었을 가능성 시사. 이 경우 외국인 주식 순매수는 발생하지만, 현물환 시장에서의 달러 매도는 동반되지 않아 환율에 미치는 직접적인 영향도 제한적. 이 같은 환헤지 비중의 확대는 외국인 투자자들이 원화 약세 리스크를 경계하고 있음을 의미. 따라서 향후 외국인의 주식 순매수가 환율 하락으로 연결되기 위해서는 외국인의 환헤지 비중 축소, 즉 원화 약세에 대한 기대가 완화될 필요</t>
+  </si>
+  <si>
+    <t>어김없이 작동하는 수요와 공급의 법칙 [금일 달러/원 환율 1,462~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 글로벌 약 달러 vs. 역내 수급 불균형에 박스권 등락 예상 전일 달러/원 환율은 장초반 미 연방검찰의 파월 연준 의장 수사 소식에 따른 글로벌 약 달러에 1,460원 하회. 하지만 일본 엔화 약세가 이어지는 가운데, 역내 지속적으로 유입되는 달러 매수에 재차 1,460원 상회. 이후 숏 포지션 청산으로 추정되는 물량에 오후장부터 급등하며 1,470원에 근접, 전일 종가 대비 10.8원 상승한 1,468.4원에 정규장 마감. 야간장에서는 약 달러에도 매수 우위로 인해 1,468.8원에 보합권 마감. 역외 NDF 환율은 1.00원 하락한 1,465.90원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,460원대 중후반에서 개장 예상. 연준 독립성 우려에 따른 약 달러에 대외적 환율 상방 압력은 완화. 더불어 환율 레벨이 단기간 빠르게 높아짐에 따라, 당국 개입 경계도 상존. 다만 역내 달러 수요 우위의 수급 불균형이 하단 지지. 거주자 해외투자 환전 수요와 기업 달러 보유 성향 등 공급 병목이 불균형 야기. 금일 환율은 상하방이 모두 제한적인 박스권 등락 예상 [글로벌 동향] 미 검찰의 파월 의장 수사, 연준 독립성 우려에 달러 약세 전일 미 달러화는 주목할 지표가 부재한 가운데, 연준 독립성 우려 불거지며 약세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.23% 하락한 98.91pt 기록. 12일 오전 9시 무렵, 미 연방검찰의 파월 연준 의장 수사 소식 발표. 검찰은 연준 본부 개보수 관련 파월 의장의 의회 위증 여부에 대한 수사를 개시. 이에 대해 파월 의장은 이번 수사가 통화정책에 대한 정치적 압박이라며 즉각 반발. 그는 그간 금리인하에 반대해 온 자산에 대한 백악관의 보복이라고 발언. 역대 연준 의장들은 파월 의장 수사 건을 두고 연준 독립성 훼손 우려를 제기. 그들은 이번 사태가 인플레이션과 경제 전반에 부정적 결과를 초래할 수 있다고 경고. 한편 백악관은 트럼프 대통령이 파월 의장 수사를 직접 지시하지 않았다고 발표. 대변인은 대통령이 연준 독립성을 존중하지만, 파월 의장 범죄 여부에 대해서는 법무부가 판단할 일이라고 밝힘 [마켓 이슈] 빠르게 올라가는 달러/원, 연초 특유의 달러 수요 우위 환경 탓 12일 시황 마켓이슈에서 최근 달러/원 상승의 주된 배경이 글로벌 강 달러에 있음을 언급한 바 있음. 다만 달러/원 상승 폭이 미 달러화 지수 상승 폭보다 더 컸다는 점에서 다른 요인도 점검. 특히 역내 달러 수급 불균형이 달러/원 상방에 일부 기여한 것으로 판단. 1월 1일~10일 무역수지는 26억 달러 적자 기록. 같은 기간, 거주자의 해외주식 순매수액은 19.8억 달러, 외국인 국내 주식 순매수액은 4.3억 달러에 그침. 종합하면, 1월 현재 달러 순 유출 규모는 약 41.5억 달러로 추정. 무역수지는 연초에 계절적으로 적자 보이는 패턴. 해외주식 투자 역시 지난해 말 양도소득세 납부 위한 일시적 매도 이후 다시 순매수 복귀 흐름. 반면, 지난해 말 정부가 추진했던 각종 달러 수급 개선 조치의 효과는 아직 제한적인 것으로 추정. 따라서 1월 중에는 연초 특유의 달러 수요 우위 환경으로 인해 달러/원 상방 압력이 지속될 가능성</t>
+  </si>
+  <si>
+    <t>强달러가 멈추지 않는 탓일까? [금일 달러/원 환율 1,455~1,462원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 1,460원 부근 개장, 당국 경계·네고 출회에 제한적 하락 전일 달러/원 환율은 미국 성장 호조 기대에 따른 달러 강세에 1,450원대에서 상승 개장. 이후에도 글로벌 강 달러 흐름이 이어지는 가운데, 외국인의 국내주식 순매도, 역내 달러 수요 우위에 상단을 높여 갔으며 장 막판에는 1,460원 부근까지 상승 폭 확대, 전일 종가 대비 7.0원 상승한 1,457.6원에 정규장 마감. 야간장에서는 엔저 및 미국 실업률 하락에 따른 달러 강세에 상승하며 1,459.0원에 마감. 역외 NDF 환율은 2.20원 상승한 1,458.45원에 최종 호가 금일 달러/원 환율은 주말간 달러 강세와 역외 거래 감안해 1,460원 부근 개장 예상. 미국 실업률 호조와 일본 조기 총선 이슈에 글로벌 강 달러 흐름. 이란의 반정부 시위 격화에 따른 미국 개입 가능성도 불안 요소. 더불어 역내 주체들의 달러 보유 성향 등 수급 불균형도 일부 잔존. 하지만 1,460원 부근 당국 개입 경계가 상방 압력을 일부 억제. 금일 환율은 레벨 부담에 따른 네고 물량 출회 등에 제한적 하방 전환 예상 [글로벌 동향] 일본의 조기 총선 가능성, 미국 실업률 하락에 달러 강세 전일 미 달러화는 엔화 약세 속, 미국 실업률 하락으로 인해 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.22% 상승한 99.14pt 기록. 일본 엔화는 다카이치 총리의 조기 총선 추진 소식에 약세. 다카이치는 중의원 의석 대거 확보를 통해 더욱 확장적 재정정책을 시행할 가능성. 이에 시장은 재정 우려를 엔화 가치에 반영, 달러당 엔화 가치는 0.59% 절하. 미국 핵심 고용지표 실적은 시장 예상과 다소 엇갈린 모습. 12월 비농업 고용은 전월대비 5만명 증가하며 예상치 (+7만명)를 하회. 지난 11월 수치는 기존의 +6.4만명에서 +5.6만명으로 하향 조정. 정부 부문을 제외한 민간 고용 증가 폭은 +3.7만명으로 예상치 (+7.5만명)를 크게 하회. 하지만 12월 실업률은 4.4%로 예상치인 4.5%를 하회. 11월 수치 역시 기존 4.6%에서 4.5%로 하향 조정. 시간당 평균임금은 12월에 전월대비 0.3% 상승하며 예상치에 부합 [마켓 이슈] 연초 달러/원 상승의 주된 배경은 국내보다는 글로벌 강 달러 지난주 1,459원으로 마감한 달러/원 환율은 주간 기준 1.0% 상승, 연말 종가 대비 1.4% 상승. 같은 기간 미 달러화 지수 (DXY)는 각각 0.7% 및 0.8% 상승한 99.1pt 기록. 즉, 최근 달러/원 상승의 주된 배경은 글로벌 외환시장에서의 달러 강세 흐름에 있다는 판단. 이 같은 글로벌 강 달러는 미국 요인보다는 유로화 및 엔화 약세 등 미국 외 요인 비중이 더 큼. 미 고용지표는 전반적으로 시장 예상에 부합 (구인건수 둔화, 비농업 고용 부진, 실업률 호조 등). 미국 국채금리는 대체로 보합권 등락하며 달러에 중립적 영향 (단기물 약세, 장기물 강보합). 반면, 독일 소매판매 부진으로 인한 유로화 약세와 일본 조기 총선 등에 따른 엔화 약세가 강 달러의 주 요인 (EUR·JPY은 DXY의 71.2% 차지). 따라서 미 경제지표의 추가 상방 서프라이즈가 나타나지 않는다는 하, 유로화 및 엔화의 약세만 진정된다면 달러/원 상승 흐름도 다소 진정될 것으로 예상</t>
+  </si>
+  <si>
+    <t>오늘 고용 앞두고 마음껏 활개 치는 달러 [금일 달러/원 환율 1,449~1,455원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 글로벌 강 달러 및 매수 우위에 상방, 1,450원대 등락 전일 달러/원 환율은 미국 서비스업 호조에 따른 달러 강세에 상승 개장. 오전 장중 국민연금 선물환 매도 소식에 일시 하락한 뒤 바로 매수세 유입되며 반등. 오후장은 강 달러 및 상단 경계로 인해 매우 좁은 범위에서 등락했으나, 장막판 매수세가 대거 유입되며 1,450원 상회, 전일 종가 대비 4.8원 상승한 1,450.6원에 정규장 마감. 야간장에서는 미국 성장 호조 기대에 따른 달러 강세에 상승하며 1,451.8원에 마감. 역외 NDF 환율은 2.10원 상승한 1,451.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,450원대 개장 예상. 미국 성장 호조 기대가 달러 강세 촉발하며 달러/원 상방 자극. 더불어 국민연금의 선물환 매도 소식에도 역내 매수 우위 보이며 하단 지지 형국. 그동안 심리적 저항선이었던 1,450원이 이제 단기 지지선으로 작용. 금일 환율은 대내외 상방 압력에 1,450원대 등락 예상. 다만 외환당국 개입 및 미 고용 경계에 변동성은 크지 않을 전망 [글로벌 동향] 미 무역적자 대폭 축소 및 노동 생산성 급등에 달러 강세 전일 미 달러화는 미국 경제성장 호조 기대에 강세 지속. 주요 6개국 통화로 구성된 달러화 지수는 0.21% 상승한 98.92pt 기록. 미 상무부에 따르면, 10월 무역수지 적자는 294억 달러로 전월비 39% 감소. 시장 예상치인 587억 달러 적자를 큰 폭 상회, 2009년 6월 이후 최대치. 이에 따른 순수출 성장 기여도 상승 기대가 달러 강세 자극. 애틀랜타 연은 GDPNow 4분기 성장률 추정치는 5.4%로 대폭 상향. 미국 노동 생산성 향상 역시 달러에 강세 압력으로 작용. 3분기 비농업 부문 생산성은 전기비 연율 4.9% 상승. 이는 2023년 3분기의 5.2% 이후 2년 만에 최고치. 미 국채금리 역시 이 같은 성장 호조 기대 반영하며 장단기물 모두 상승. 다만 뉴욕증시는 기술주 부진에 나스닥 지수 하락하며 혼조 마감. 한편 스티븐 마이런 이사는 올해 총 1.5%p 추가 금리인하가 필요하다고 주장. 미 재무부는 1월 중 연준 의장 지명 발표를 예고 [마켓 이슈] 오늘 저녁, 미국 실업률 발표 앞두고 상기해 볼 베버리지 곡선 미국 11월 구인건수가 둔화되며 구인율은 4.3%까지 하락. 관련하여 금일 저녁 발표 예정인 실업률 상방 리스크 점검 필요 (시장 컨센서스 12월 4.5%, 전월대비 0.1%p 하락). 구인율과 실업률의 관계를 설명하는 베버리지 곡선 상, 구인율 하락은 시차를 두고 실업률 상승으로 연결. 팬데믹 이후 미국 노동시장은 빠른 구인율 하락과 완만한 실업률 상승의 '기울기가 가파른' 베버리지 곡선을 형성 (그림의 ②). 다만 최근에는 기업들의 노동 초과수요가 해소, 구인-이직 미스매치도 점진적으로 개선. 관련하여 월러 연준 이사는 구인율 4.5% 하회 시 노동시장 국면 전환 가능성 주장. 이에 따라 현재 미 노동시장은 '기울기가 완만한' 베버리지 곡선으로 복귀 중 추정 (③). 완만한 곡선 (③)에서 구인율이 0.1%p 하락하면 실업률은 0.25%p 상승하는 관계. 즉, 최근 구인율 하락과 베버리지 곡선 감안 시, 금일 실업률은 예상치 4.5%를 상회할 가능성</t>
+  </si>
+  <si>
+    <t>미 고용은 탄광 속 카나리아, 달러 반등은 잠깐 [금일 달러/원 환율 1,443~1,451원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 미 고용 등 누적되는 약 달러 압력, 장중 하락 전환 예상 전일 달러/원 환율은 유로화 약세에 동조해 상승 개장한 이후 저가 매수까지 가세하며 1,449원까지 추가 상승. 하지만 당국 개입 경계에 1,450원 상회는 실패하며 상승 폭 일부 축소. 이후 외국인의 국내주식 순매수 등에 장막판 대부분의 상승 분을 되돌리며, 전일 종가 대비 0.4원 상승한 1,445.8원에 정규장 마감. 야간장에서는 미국 서비스업 호조에 따른 달러 강세와 유로화 약세에 소폭 상승하며 1,447.6원에 마감. 역외 NDF 환율은 4.00원 상승한 1,448.40원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,440원대 중후반에서 개장 예상. 미 서비스업 호조 및 독일 소비 둔화가 글로벌 달러 반등 자극. 이에 달러/원도 하방 제약된 가운데, 당국 경계에 박스권 등락 예상. 하지만 미 고용지표 부진에 달러 약세 압력 역시 가중되는 상황. 장중 글로벌 달러 약세 전환 시, 달러/원도 하락 동조 가능하다는 판단. 금일 환율은 1,450원이 심리적 상단인 가운데, 하방 압력 받을 전망 [글로벌 동향] 美 고용 부진에도 서비스업 호조, 獨 소비 둔화에 강 달러 전일 미 달러화는 미국 고용지표 부진에도 독일 경기둔화 우려 등에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.11% 상승한 98.71pt 기록. 전일 저녁 발표된 미국 고용지표는 시장 예상보다 부진. ADP의 12월 민간고용은 4.1만명 증가하며 전월치 (- 2.9만명)보다는 개선. 하지만 예상치 +5.0만명은 하회, 주로 정보 및 전문비즈니스 부문에서 부진. JOLTs의 11월 구인건수는 714만건으로 전월치 (745만건)과 예상치 (765만건) 모두 하회. 이는 2024년 9월 이후 최저 수준으로, 노동수요의 둔화 시사. 11월 구인율은 4.3%로 전월대비 0.2%p 하락. 하지만 미국 서비스업황 호조가 고용 부진 영향 상쇄. 12월 ISM 서비스업 지수는 54.4pt로 2025년 중 최고치 기록. 한편 유로화는 독일 소비 둔화와 분트 금리 하락에 약세. 독일의 11월 소매판매는 전월대비 0.6% 감소. 이에 독일 분트 금리가 3거래일 연속 하락하며 유로화 약세에 기여 [마켓 이슈] 관세 충격은 인플레이션이 아닌 디스인플레이션 유발 (FRBSF) 샌프란시스코 연은에 따르면, 대규모의 관세 인상이 실업률 상승 및 물가 압력 둔화를 유발한 것으로 분석 (FRBSF ECONOMIC LETTER 2026-01). 19세기 말~20세기 초의 관세 인상 사례를 분석한 결과, 관세 충격은 비용 상승보다는 불확실성 확대 및 총수요 위축을 통해 디스인플레이션으로 연결. 이러한 역사적 분석 결과를 현재 미국 경제 상황에 대입해보면, 향후 실업률은 추가 상승 여지, 물가상승률은 시장 예상보다 더 낮아질 것으로 예상. 이 경우 연준 통화정책 목표에서 물가보다는 고용 안정에 대한 가중치가 더욱 확대. 연준의 금리경로 역시 기존보다 더욱 완화적으로 이동할 가능성. 즉 물가 불안이 크지 않은 상황에서 고용 둔화가 심화될수록, 연준의 금리인하 명분은 더욱 강화되고 달러 약세 압력 역시 가중될 것으로 예상. 따라서 금주, 차주에 발표될 고용 및 물가지표 결과, 이에 따른 연준 금리경로 기대 변화에 주목할 필요</t>
+  </si>
+  <si>
+    <t>다 된 밥에 유로화 약세 뿌리기 [금일 달러/원 환율 1,443~1,450원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] AI 낙관론 등 위험선호에도 유로화 약세 동조에 혼조세 전일 달러/원 환율은 미국 제조업 지수 부진에도 불구하고 장초반 글로벌 달러 반등과 저가 매수에 1,449원까지 상승. 하지만 이후 달러가 재차 약세로 전환한 가운데, 정부 개입 경계 등에 장중 일시적으로 하락 전환. 오후장에서는 외국인의 국내주식 순매도 등 수급 부담에 하단 지지되며 전일 종가 대비 1.6원 상승한 1,445.4원에 정규장 마감. 야간장에서는 유로화 약세 등 글로벌 강 달러에 상승하며 1,447.1원에 마감. 역외 NDF 환율은 2.25원 상승한 1,446.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,440원대 중후반에서 개장 예상. 당국 개입 경계가 작용하며 1,450원 부근에서는 추가 상방이 억제. 더불어 AI 낙관론 속 위험선호심리 역시 원화에 긍정적인 요인으로 작용. 장중 외국인 국내주식 플로우에 따라 하락 전환도 가능. 다만 유로發 글로벌 강 달러와 저가 매수가 달러/원 상방 자극. 금일 환율은 위험선호심리 회복에도 유로화 약세 동조에 혼조 예상 [글로벌 동향] 유로존 경기 부진 및 독일 물가 우려 완화에 미 달러 강세 전일 미 달러화는 유로화 부진 속 반발 매수에 강세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.31% 상승한 98.60pt 기록. 뉴욕증시는 AI 낙관론 속 3대 지수 모두 상승하며 위험선호 분위기. 하지만 유로화는 유로존 경기 부진 및 독일 물가 우려 완화 등에 약세. 유로존 12월 PMI 확정치는 51.5pt로 직전치 (52.8pt)와 예비치 (51.9pt) 모두 하회. 기준치인 50pt는 상회하며 확장 국면이었으나, 그 모멘텀은 약화된 것으로 확인. 독일 물가지표 발표 이후 유로/달러는 1.17달러 하회하며 약세 폭 확대. 독일의 12월 소비자물가지수는 전년비 1.8% 상승에 그치며 예상치 (+2.1%) 하회. 이에 독일 분트 금리가 일제히 하락하며 유로화 약세로 연결. 스티븐 마이런 이사는 올해 100bp 인하의 정당성을 주장. 그는 지나치게 제약적인 통화정책은 성장 동력을 약화시킬 수 있다고 지적. 하지만 미 국채금리는 해당 발언에도 불구, 회사채 수급 부담에 상승 [마켓 이슈] 베네수엘라 사태는 표면, 미국發 지정학 리스크가 사태의 본질 베네수엘라 사태는 단기적으로 시장에 호재로 인식되는 분위기. 국제유가는 안정적인 가운데, 글로벌 증시는 안도 랠리. 다만 문제는 '지금의 베네수엘라'가 아닌 '앞으로의 미국'. 이번 사태는 미국의 공격적 외교·안보 스탠스가 다시 전면에 부상하고 있음을 알린 신호. 실제로 지정학적 리스크 지수는 이번 사태를 계기로 6개월 만에 최고치를 기록. 이는 지난해 6월 미국의 이란 무력 개입 당시 이후로 가장 높은 레벨. 이 같은 미국의 일방적 무력 사용은 중국과 러시아 등 전략적 경쟁국을 자극할 수 있는 사안. 이로 인해 외교 갈등이 불거짐과 더불어 다시 관세 전쟁, 기술 제재 등 경제적 충돌이 발생할 가능성. 이 과정에서 한국 원화의 취약성이 다시 부각될 가능성도 상존. 원화는 대외 변수에 민감하게 반응하는 대표적인 '위험 통화' 중 하나. 이번 사태로 인해 향후 지정학적 갈등이 심화할 경우, 원화 역시 변동성이 확대될 리스크에 유의</t>
+  </si>
+  <si>
+    <t>美 경기 꺾일 때마다 따라붙는 저가 매수 [금일 달러/원 환율 1,438~1,446원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 약 달러 및 위험선호에 하락 조정, 저가 매수가 하단 지지 전일 달러/원 환율은 미국의 베네수엘라 침공에 따른 위험회피와 달러 강세에 상승 개장. 장중 달러 추가 강세에 환율도 1,449원까지 추가 상승. 하지만 KOSPI 3% 이상 급등 및 외국인의 국내주식 대거 순매수가 상방 제약. 오후장에서는 레벨 부담에 상승 폭 축소되며 전일 종가 대비 2.0원 상승한 1,443.8원에 정규장 마감. 야간장에서는 저가 매수에 반등한 이후 미 제조업 부진 및 약 달러에 상승 폭 되돌리며 1,445.6원에 마감. 역외 NDF 환율은 1.45원 상승한 1,443.80원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세 및 역외 거래 감안해 보합권에서 개장 예상. 미국 제조업 부진에 따른 국채금리 하락과 성장 추정치 하향에 달러 약세. 반면 뉴욕증시는 베네수엘라 이벤트에 반등하며 위험선호 분위기. 이 같은 약 달러 및 위험선호 조합에 원화 강세 전환 기대. 다만 국내증시와 원화 연계성 약화로 달러/원 하락 폭 제한적일 가능성. 더불어 지속 유입되는 저가 매수세가 하단 지지할 전망 [글로벌 동향] 미 제조업 부진에 달러와 국채금리 하락, 성장 추정치 하향 전일 미 달러화는 미국 제조업황 부진 영향에 약세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.16% 하락한 98.29pt 기록. 미국 공급관리협회 (ISM) 12월 제조업 지수는 47.9pt 기록. 기준치 50pt를 10개월 연속 하회, 예상치 48.4pt도 소폭 하회. 하위 지수별로는 생산 (51.0pt)과 가격 (58.5pt)이 기준치 상회. 반면 고용 (44.9pt), 신규 주문 (47.7pt), 재고 (45.2pt)는 위축 국면. 애틀랜타 연은 GDPNow는 제조업 지수 반영해 4분기 성장률 추정치를 2.7%로 0.3%p 하향. PCE 증가율은 2.7%에서 2.4%로, 투자 증가율은 7.0%에서 6.5%로 하향. 미 국채금리 역시 제조업황 부진을 반영하며 장단기물 대체로 하락. 뉴욕증시는 미국 정유사들의 베네수엘라 진출 기대에 3대 지수 상승 마감. 닐 카시카리 총재의 발언은 달러와 국채금리 낙폭을 일부 제약. 그는 현재가 중립금리 수준으로 추정된다며 추가 인하에 대해서 신중한 입장 표출 [마켓 이슈] 미국 경제성장의 무게중심 이동: 개인소비지출에서 AI 투자로 미국 경제는 2025년 1~3분기 동안 전기비 연율 기준 평균 2.5%의 성장률을 기록. 겉으로 보면 견조한 성장 흐름이 유지되고 있으나, 성장 구성 내역은 과거와는 달라진 모습. 2025년 미국 성장에서 AI 관련 투자 기여도는 평균 0.9%p로, 전체 성장률의 36.4% 차지. 이는 2024년 AI 투자 기여도 0.2%p (9.6%)보다 비중이 급격히 확대. 반면 전통적인 성장 동력인 개인소비지출 평균 기여도는 1.5%p로, 전체 경제성장의 59.9% 차지. 이는 2024년 기여도 2.3%p (94.3%)에서 뚜렷하게 낮아진 수준. 즉, 최근 미국 경제성장은 AI 투자 의존도가 크게 높아진 형태로 전환. 이 같은 성장 비중 변화는 최근 시장에서 제기되는 AI 버블 논란과도 연결. 만약 향후 AI 과잉 투자 관련 논란이 확산되며 투자지출의 조정이 발생할 경우, 미국 경제에 미칠 충격은 과거보다 훨씬 커질 가능성. 따라서 AI 투자 지속 가능성이 미국 경제성장 경로의 관전 포인트</t>
+  </si>
+  <si>
+    <t>꿈틀대는 대외 변수들, 원화 약세는 일시적 [금일 달러/원 환율 1,439~1,447원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 글로벌 강 달러, 지정학 이벤트에 일시적 상방 변동 예상 전일 달러/원 환율은 일본 엔화 약세 연동 및 저가 매수세 유입에 소폭 상승 개장한 뒤 1,440원대 초반에서 박스권 등락. 장중 미 달러화가 약세를 보이고, 외국인의 국내 주식 순매수세 등에도 불구하고, 결제수요 등 달러 매수가 우위를 보이며 상방 우세 흐름, 전일 종가 대비 2.8원 상승한 1,441.8원에 정규장 마감. 야간장에서는 강 달러 및 저가 매수에 1,450원까지 상승하기도 했으나, 장 막판 상승 폭을 일부 되돌리며 1,444.7원에 마감. 역외 NDF 환율은 0.30원 상승한 1,440.65원에 최종 호가 금일 달러/원 환율은 주말간 달러 강세와 역외 거래 감안해 1,440원대 중반에서 상승 개장 예상. 유로존 제조업황 부진에 따른 유로화 약세가 글로벌 달러 강세 자극. 이에 달러/원도 상승 압력 받으며 1,440원대에서 등락 예상. 더불어 이란 및 베네수엘라 등에서 발생한 지정학 이벤트가 원화 약세 자극할 소지. 다만, 해당 이벤트의 글로벌 시장 파급력은 제한적. 따라서 달러/원의 변동성도 일시에 그칠 것으로 예상 [글로벌 동향] 유로존 제조업 경기 부진이 강 달러 자극, 위안화도 강세 전일 미 달러화는 유로존 제조업황 부진에 따른 유로화 절하 등에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.16% 상승한 98.45pt 기록. 유로존의 12월 제조업 PMI 확정치는 48.8pt로 예비치인 49.2pt 하회. 이는 2025년 3월의 48.6pt 이후 최저치로, 유로존 경기회복이 지연되고 있음을 시사. 이에 유로/달러 환율은 0.23% 하락하며 1.17달러 부근에서 등락. 파운드화 역시 유로화 약세에 동조, 파운드/달러 환율은 0.12% 하락. 일본 엔화도 선진국 통화 약세에 일부 동조했으나, 외환당국 구두 개입 경계에 약세 폭은 제한적. 중국 위안화는 미 달러화 강세에도 불구하고 절상 흐름 지속. 역외 달러/위안 환율은 0.19% 하락한 6.97위안으로 2023년 5월 이후 최저치. 미 국채금리는 장기물 중심 상승, 뉴욕증시는 새해 첫 거래에서 기술주 부진에 3대 지수 혼조 마감. 한편 주말간 중동과 남미에서 지정학적 이벤트들이 발생 [마켓 이슈] 연초부터 불거진 지정학 이벤트들, 하지만 시장 영향은 제한적 새해 초부터 중동과 남미에서 지정학적 이벤트가 연이어 발생. 이란에서는 경제난을 배경으로 한 반정부 시위가 확산. 베네수엘라는 미국의 무력 침공으로 인해 긴장이 고조되는 상황. 다만 해당 이벤트가 유가 급등 등 시장에 미칠 파급력은 제한적이라는 판단. 우선 이란 사태는 내부 갈등이 표면화된 사건에 불과. 즉, 해당 사태의 중동 전역 확산이나 호르무즈 해협 등 주요 원유 운송로 차질이 발생할 가능성은 제한적. 한편 베네수엘라의 글로벌 경제 및 교역 비중은 매우 낮고, 금융시장에서의 존재감도 미미. 또한 이란과 베네수엘라의 원유 생산 비중은 전세계의 약 5% 수준. 즉 두 국가에서의 원유 공급 차질이 국제유가를 추세적으로 끌어올리긴 역부족. 원화는 글로벌 리스크에 민감한 통화라는 점에서 단기적으로는 영향을 받을 가능성. 하지만 해당 이벤트들의 성격을 종합하면 달러/원의 변동성이 유의미하게 확대될 가능성은 크지 않다는 판단</t>
+  </si>
+  <si>
+    <t>성장하는 곳에 돈이 머문다 [금일 달러/원 환율 1,437~1,443원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 새해 첫 개장, 역내 수급 대치에 1,440원 부근 박스권 2025년 12월 31일과 2026년 1월 1일 달러/원 환율은 서울 외환시장 휴장으로 거래 제한. 하지만 역외에서는 저가 매수세가 유입되며 하단 지지. 글로벌 달러가 소폭 약세를 보였고, 중국 위안화가 강세를 보였음에도 오히려 원화는 일본 엔화 약세에 일부 동조되는 모습. 하지만 연말 적은 거래량 속, 역외 달러/원 환율은 12월 30일 종가인 1,439원에서 큰 이탈 없이 보합권 등락. 역외 NDF 환율은 2.00원 상승한 1,439.45원에 최종 호가 금일 달러/원 환율은 주말간 엔화 약세와 역외 거래 감안해 1,440원 부근 개장 예상. 특별한 이벤트 없이 저가 매수세 유입되며 일시 반등 국면. 새해 맞아 거래량 부진한 가운데, 주로 역내 실수요에 따라 등락 예상. 거주자 해외투자용 달러 환전, 수입업체 결제수요 등이 하단 지지. 반면 국민연금 전략적 환헤지를 필두로 한 달러 매도 물량 출회 기대. 금일 환율은 한산한 거래 속, 역내 수급 대치에 박스권 등락 예상 [글로벌 동향] 미 달러화 약 보합, 위안화는 2024년 9월 이후 최대 강세 2024년 12월 31일 미 달러화는 연말 글로벌 주요 금융시장 휴장인 관계로 큰 변동 없이 약 보합. 주요 6개국 통화로 구성된 달러화 지수는 0.02% 하락한 98.24pt 기록. 31일 발표된 미국 고용지표는 시장 예상보다 다소 양호한 결과보였으나 시장 반응은 미온적. 신규 실업수당 청구건수는 19.9만건으로 집계되며 예상치 (21.8만건) 및 전주치 (21.5만건) 하회. 하지만 변동성이 비교적 적은 연속 실업수당 청구건수는 186.6만건으로 집계되며 예상치 (190.2만건) 및 전주치 (191.3만건) 하회. 중국의 역외 위안화는 중국 경제지표 호조에 강세 흐름 지속. 달러당 역외 위안화 환율은 0.23% 급락한 6.975위안으로 2024년 9월 이후 최저치. 중국의 12월 PMI는 제조업 및 비제조업 모두 시장 예상 상회. 제조업 PMI는 50.1pt, 비제조업 PMI는 50.2pt로 모두 기준치 50pt 상회. 선진국 통화는 유로화 강세, 엔화 약세로 상이한 퍼포먼스 [마켓 이슈] 수급 불균형은 겉으로 드러난 '증상', 한미 성장 격차가 '근본' 2025년 고환율의 배경으로 해외투자 확대에 따른 달러 수요 우위, 즉 수급 불균형이 지적. 다만 이러한 수급 불균형은 고환율의 '원인'이라기보다는 고환율과 함께 동반된 '증상'에 가깝다는 판단. 고환율의 근본적인 원인은 한미 간 잠재성장률 격차의 구조적 확대에 있음. 각국 잠재성장률은 그 나라의 장기 투자수익률을 대변하는 변수. 그리고 수익률이 더 높은 곳으로 자본이 이동하는 것이 자본시장의 기본 메커니즘. 실제 한미 잠재성장률은 2020년 전후로 역전된 이후 그 격차가 지속 확대. 한국 잠재성장률은 인구감소 및 생산성 둔화 등에 하락세. 반면 미국은 이민자 유입과 AI 등 생산성 향상 기대가 성장 잠재력을 지지 중. 이 같은 잠재성장률 격차는 금리 및 자산 기대수익률 차이로 이어지고, 이는 달러 수요 우위의 원화 약세라는 결과로 반영. 즉, 한국의 성장 잠재력 제고 없이는 원화 약세 역시 구조적으로 고착화될 가능성이 크다는 판단</t>
+  </si>
 </sst>
 </file>
 
@@ -15413,7 +15582,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -15451,6 +15620,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Verdana"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -15825,7 +16001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3338"/>
+  <dimension ref="A1:G3333"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -65081,7 +65257,7 @@
       </c>
       <c r="F3280" s="1"/>
     </row>
-    <row r="3281" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3281" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3281" s="3">
         <v>46019</v>
       </c>
@@ -65096,7 +65272,7 @@
       </c>
       <c r="F3281" s="1"/>
     </row>
-    <row r="3282" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3282" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3282" s="3">
         <v>46020</v>
       </c>
@@ -65111,7 +65287,7 @@
       </c>
       <c r="F3282" s="1"/>
     </row>
-    <row r="3283" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3283" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3283" s="3">
         <v>46021</v>
       </c>
@@ -65126,7 +65302,7 @@
       </c>
       <c r="F3283" s="1"/>
     </row>
-    <row r="3284" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3284" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3284" s="3">
         <v>46022</v>
       </c>
@@ -65141,12 +65317,12 @@
       </c>
       <c r="F3284" s="1"/>
     </row>
-    <row r="3285" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3285" s="3">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B3285" s="3">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C3285" s="9">
         <v>0.36805555555555558</v>
@@ -65154,14 +65330,22 @@
       <c r="D3285" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3285" s="1"/>
-    </row>
-    <row r="3286" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3285" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3285" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3285" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3286" s="3">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B3286" s="3">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C3286" s="9">
         <v>0.36805555555555558</v>
@@ -65169,14 +65353,22 @@
       <c r="D3286" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3286" s="1"/>
-    </row>
-    <row r="3287" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3286" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3286" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3286" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3287" s="3">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="B3287" s="3">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C3287" s="9">
         <v>0.36805555555555558</v>
@@ -65184,14 +65376,22 @@
       <c r="D3287" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3287" s="1"/>
-    </row>
-    <row r="3288" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3287" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3287" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3287" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3288" s="3">
-        <v>46026</v>
+        <v>46029</v>
       </c>
       <c r="B3288" s="3">
-        <v>46026</v>
+        <v>46029</v>
       </c>
       <c r="C3288" s="9">
         <v>0.36805555555555558</v>
@@ -65199,14 +65399,22 @@
       <c r="D3288" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3288" s="1"/>
-    </row>
-    <row r="3289" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3288" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3288" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3288" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3289" s="3">
-        <v>46027</v>
+        <v>46030</v>
       </c>
       <c r="B3289" s="3">
-        <v>46027</v>
+        <v>46030</v>
       </c>
       <c r="C3289" s="9">
         <v>0.36805555555555558</v>
@@ -65214,14 +65422,22 @@
       <c r="D3289" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3289" s="1"/>
-    </row>
-    <row r="3290" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3289" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3289" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3289" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3290" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="B3290" s="3">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="C3290" s="9">
         <v>0.36805555555555558</v>
@@ -65229,14 +65445,22 @@
       <c r="D3290" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3290" s="1"/>
-    </row>
-    <row r="3291" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3290" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3290" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3290" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3291" s="3">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="B3291" s="3">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="C3291" s="9">
         <v>0.36805555555555558</v>
@@ -65244,14 +65468,22 @@
       <c r="D3291" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3291" s="1"/>
-    </row>
-    <row r="3292" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3291" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3291" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3291" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3292" s="3">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="B3292" s="3">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="C3292" s="9">
         <v>0.36805555555555558</v>
@@ -65259,14 +65491,22 @@
       <c r="D3292" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3292" s="1"/>
-    </row>
-    <row r="3293" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3292" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3292" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3292" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3293" s="3">
-        <v>46031</v>
+        <v>46036</v>
       </c>
       <c r="B3293" s="3">
-        <v>46031</v>
+        <v>46036</v>
       </c>
       <c r="C3293" s="9">
         <v>0.36805555555555558</v>
@@ -65274,14 +65514,22 @@
       <c r="D3293" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3293" s="1"/>
-    </row>
-    <row r="3294" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3293" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3293" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3293" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3294" s="3">
-        <v>46032</v>
+        <v>46037</v>
       </c>
       <c r="B3294" s="3">
-        <v>46032</v>
+        <v>46037</v>
       </c>
       <c r="C3294" s="9">
         <v>0.36805555555555558</v>
@@ -65289,14 +65537,22 @@
       <c r="D3294" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3294" s="1"/>
-    </row>
-    <row r="3295" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3294" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3294" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3294" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3295" s="3">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="B3295" s="3">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="C3295" s="9">
         <v>0.36805555555555558</v>
@@ -65304,14 +65560,22 @@
       <c r="D3295" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3295" s="1"/>
-    </row>
-    <row r="3296" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3295" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3295" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3295" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3296" s="3">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="B3296" s="3">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="C3296" s="9">
         <v>0.36805555555555558</v>
@@ -65319,14 +65583,22 @@
       <c r="D3296" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3296" s="1"/>
-    </row>
-    <row r="3297" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3296" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3296" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3296" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3297" s="3">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B3297" s="3">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="C3297" s="9">
         <v>0.36805555555555558</v>
@@ -65334,14 +65606,22 @@
       <c r="D3297" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3297" s="1"/>
-    </row>
-    <row r="3298" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3297" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3297" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3297" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3298" s="3">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B3298" s="3">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="C3298" s="9">
         <v>0.36805555555555558</v>
@@ -65349,14 +65629,22 @@
       <c r="D3298" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3298" s="1"/>
-    </row>
-    <row r="3299" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3298" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3298" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3298" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3299" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B3299" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C3299" s="9">
         <v>0.36805555555555558</v>
@@ -65364,14 +65652,22 @@
       <c r="D3299" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3299" s="1"/>
-    </row>
-    <row r="3300" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3299" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3299" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3299" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3300" s="3">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B3300" s="3">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="C3300" s="9">
         <v>0.36805555555555558</v>
@@ -65379,14 +65675,22 @@
       <c r="D3300" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3300" s="1"/>
-    </row>
-    <row r="3301" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3300" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3300" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3300" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3301" s="3">
-        <v>46039</v>
+        <v>46048</v>
       </c>
       <c r="B3301" s="3">
-        <v>46039</v>
+        <v>46048</v>
       </c>
       <c r="C3301" s="9">
         <v>0.36805555555555558</v>
@@ -65394,14 +65698,22 @@
       <c r="D3301" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3301" s="1"/>
-    </row>
-    <row r="3302" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3301" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3301" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3301" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3302" s="3">
-        <v>46040</v>
+        <v>46049</v>
       </c>
       <c r="B3302" s="3">
-        <v>46040</v>
+        <v>46049</v>
       </c>
       <c r="C3302" s="9">
         <v>0.36805555555555558</v>
@@ -65409,14 +65721,22 @@
       <c r="D3302" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3302" s="1"/>
-    </row>
-    <row r="3303" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3302" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3302" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3302" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3303" s="3">
-        <v>46041</v>
+        <v>46050</v>
       </c>
       <c r="B3303" s="3">
-        <v>46041</v>
+        <v>46050</v>
       </c>
       <c r="C3303" s="9">
         <v>0.36805555555555558</v>
@@ -65424,14 +65744,22 @@
       <c r="D3303" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3303" s="1"/>
-    </row>
-    <row r="3304" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3303" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3303" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3303" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3304" s="3">
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="B3304" s="3">
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="C3304" s="9">
         <v>0.36805555555555558</v>
@@ -65439,14 +65767,22 @@
       <c r="D3304" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3304" s="1"/>
-    </row>
-    <row r="3305" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3304" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3304" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3304" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3305" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="B3305" s="3">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="C3305" s="9">
         <v>0.36805555555555558</v>
@@ -65454,14 +65790,22 @@
       <c r="D3305" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3305" s="1"/>
-    </row>
-    <row r="3306" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3305" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3305" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3305" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3306" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="B3306" s="3">
-        <v>46044</v>
+        <v>46055</v>
       </c>
       <c r="C3306" s="9">
         <v>0.36805555555555558</v>
@@ -65469,14 +65813,22 @@
       <c r="D3306" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3306" s="1"/>
-    </row>
-    <row r="3307" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3306" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3306" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3306" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3307" s="3">
-        <v>46045</v>
+        <v>46056</v>
       </c>
       <c r="B3307" s="3">
-        <v>46045</v>
+        <v>46056</v>
       </c>
       <c r="C3307" s="9">
         <v>0.36805555555555558</v>
@@ -65484,14 +65836,22 @@
       <c r="D3307" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3307" s="1"/>
-    </row>
-    <row r="3308" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3307" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3307" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3307" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3308" s="3">
-        <v>46046</v>
+        <v>46057</v>
       </c>
       <c r="B3308" s="3">
-        <v>46046</v>
+        <v>46057</v>
       </c>
       <c r="C3308" s="9">
         <v>0.36805555555555558</v>
@@ -65499,14 +65859,22 @@
       <c r="D3308" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3308" s="1"/>
-    </row>
-    <row r="3309" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3308" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3308" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3308" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3309" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3309" s="3">
-        <v>46047</v>
+        <v>46058</v>
       </c>
       <c r="B3309" s="3">
-        <v>46047</v>
+        <v>46058</v>
       </c>
       <c r="C3309" s="9">
         <v>0.36805555555555558</v>
@@ -65514,14 +65882,22 @@
       <c r="D3309" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3309" s="1"/>
-    </row>
-    <row r="3310" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3309" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3309" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3309" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3310" s="3">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="B3310" s="3">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="C3310" s="9">
         <v>0.36805555555555558</v>
@@ -65529,14 +65905,22 @@
       <c r="D3310" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3310" s="1"/>
-    </row>
-    <row r="3311" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3310" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3310" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3310" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3311" s="3">
-        <v>46049</v>
+        <v>46062</v>
       </c>
       <c r="B3311" s="3">
-        <v>46049</v>
+        <v>46062</v>
       </c>
       <c r="C3311" s="9">
         <v>0.36805555555555558</v>
@@ -65544,14 +65928,22 @@
       <c r="D3311" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3311" s="1"/>
-    </row>
-    <row r="3312" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3311" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3311" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3311" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3312" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3312" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="B3312" s="3">
-        <v>46050</v>
+        <v>46063</v>
       </c>
       <c r="C3312" s="9">
         <v>0.36805555555555558</v>
@@ -65559,14 +65951,22 @@
       <c r="D3312" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3312" s="1"/>
-    </row>
-    <row r="3313" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3312" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3312" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3312" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3313" s="3">
-        <v>46051</v>
+        <v>46064</v>
       </c>
       <c r="B3313" s="3">
-        <v>46051</v>
+        <v>46064</v>
       </c>
       <c r="C3313" s="9">
         <v>0.36805555555555558</v>
@@ -65574,14 +65974,22 @@
       <c r="D3313" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3313" s="1"/>
+      <c r="E3313" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3313" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3313" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3314" s="3">
-        <v>46052</v>
+        <v>46065</v>
       </c>
       <c r="B3314" s="3">
-        <v>46052</v>
+        <v>46065</v>
       </c>
       <c r="C3314" s="9">
         <v>0.36805555555555558</v>
@@ -65590,21 +65998,21 @@
         <v>53</v>
       </c>
       <c r="E3314" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F3314" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G3314" s="4" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3315" s="3">
-        <v>46055</v>
+        <v>46066</v>
       </c>
       <c r="B3315" s="3">
-        <v>46055</v>
+        <v>46066</v>
       </c>
       <c r="C3315" s="9">
         <v>0.36805555555555558</v>
@@ -65613,21 +66021,21 @@
         <v>53</v>
       </c>
       <c r="E3315" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F3315" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G3315" s="4" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3316" s="3">
-        <v>46056</v>
+        <v>46072</v>
       </c>
       <c r="B3316" s="3">
-        <v>46056</v>
+        <v>46072</v>
       </c>
       <c r="C3316" s="9">
         <v>0.36805555555555558</v>
@@ -65636,21 +66044,21 @@
         <v>53</v>
       </c>
       <c r="E3316" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3316" s="1" t="s">
-        <v>74</v>
+        <v>47</v>
+      </c>
+      <c r="F3316" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G3316" s="4" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3317" s="3">
-        <v>46057</v>
+        <v>46073</v>
       </c>
       <c r="B3317" s="3">
-        <v>46057</v>
+        <v>46073</v>
       </c>
       <c r="C3317" s="9">
         <v>0.36805555555555558</v>
@@ -65659,21 +66067,21 @@
         <v>53</v>
       </c>
       <c r="E3317" s="1" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="F3317" s="1" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="G3317" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3318" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3318" s="3">
-        <v>46058</v>
+        <v>46076</v>
       </c>
       <c r="B3318" s="3">
-        <v>46058</v>
+        <v>46076</v>
       </c>
       <c r="C3318" s="9">
         <v>0.36805555555555558</v>
@@ -65682,21 +66090,21 @@
         <v>53</v>
       </c>
       <c r="E3318" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F3318" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3318" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="G3318" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3319" s="3">
-        <v>46059</v>
+        <v>46077</v>
       </c>
       <c r="B3319" s="3">
-        <v>46059</v>
+        <v>46077</v>
       </c>
       <c r="C3319" s="9">
         <v>0.36805555555555558</v>
@@ -65705,21 +66113,21 @@
         <v>53</v>
       </c>
       <c r="E3319" s="1" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F3319" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G3319" s="4" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3320" s="3">
-        <v>46062</v>
+        <v>46078</v>
       </c>
       <c r="B3320" s="3">
-        <v>46062</v>
+        <v>46078</v>
       </c>
       <c r="C3320" s="9">
         <v>0.36805555555555558</v>
@@ -65728,21 +66136,21 @@
         <v>53</v>
       </c>
       <c r="E3320" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="F3320" s="1" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G3320" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3321" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3321" s="3">
-        <v>46063</v>
+        <v>46079</v>
       </c>
       <c r="B3321" s="3">
-        <v>46063</v>
+        <v>46079</v>
       </c>
       <c r="C3321" s="9">
         <v>0.36805555555555558</v>
@@ -65751,21 +66159,21 @@
         <v>53</v>
       </c>
       <c r="E3321" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F3321" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3321" s="1" t="s">
-        <v>58</v>
+        <v>37</v>
+      </c>
+      <c r="G3321" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3322" s="3">
-        <v>46064</v>
+        <v>46080</v>
       </c>
       <c r="B3322" s="3">
-        <v>46064</v>
+        <v>46080</v>
       </c>
       <c r="C3322" s="9">
         <v>0.36805555555555558</v>
@@ -65774,21 +66182,21 @@
         <v>53</v>
       </c>
       <c r="E3322" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F3322" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G3322" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3323" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3323" s="3">
-        <v>46065</v>
+        <v>46084</v>
       </c>
       <c r="B3323" s="3">
-        <v>46065</v>
+        <v>46084</v>
       </c>
       <c r="C3323" s="9">
         <v>0.36805555555555558</v>
@@ -65797,21 +66205,21 @@
         <v>53</v>
       </c>
       <c r="E3323" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="F3323" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3323" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3323" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3324" s="3">
-        <v>46066</v>
+        <v>46085</v>
       </c>
       <c r="B3324" s="3">
-        <v>46066</v>
+        <v>46085</v>
       </c>
       <c r="C3324" s="9">
         <v>0.36805555555555558</v>
@@ -65820,21 +66228,21 @@
         <v>53</v>
       </c>
       <c r="E3324" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F3324" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G3324" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3325" s="3">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="B3325" s="3">
-        <v>46072</v>
+        <v>46086</v>
       </c>
       <c r="C3325" s="9">
         <v>0.36805555555555558</v>
@@ -65843,21 +66251,21 @@
         <v>53</v>
       </c>
       <c r="E3325" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3325" s="7" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="F3325" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G3325" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3326" s="3">
-        <v>46073</v>
+        <v>46087</v>
       </c>
       <c r="B3326" s="3">
-        <v>46073</v>
+        <v>46087</v>
       </c>
       <c r="C3326" s="9">
         <v>0.36805555555555558</v>
@@ -65866,21 +66274,21 @@
         <v>53</v>
       </c>
       <c r="E3326" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F3326" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G3326" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3327" s="3">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="B3327" s="3">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="C3327" s="9">
         <v>0.36805555555555558</v>
@@ -65889,21 +66297,21 @@
         <v>53</v>
       </c>
       <c r="E3327" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F3327" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G3327" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3328" s="3">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="B3328" s="3">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="C3328" s="9">
         <v>0.36805555555555558</v>
@@ -65912,21 +66320,21 @@
         <v>53</v>
       </c>
       <c r="E3328" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F3328" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G3328" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3329" s="3">
-        <v>46078</v>
+        <v>46092</v>
       </c>
       <c r="B3329" s="3">
-        <v>46078</v>
+        <v>46092</v>
       </c>
       <c r="C3329" s="9">
         <v>0.36805555555555558</v>
@@ -65935,220 +66343,105 @@
         <v>53</v>
       </c>
       <c r="E3329" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3329" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3329" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3329" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3329" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3330" s="3">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="B3330" s="3">
-        <v>46079</v>
+        <v>46093</v>
       </c>
       <c r="C3330" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3330" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3330" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3330" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3330" s="4" t="s">
-        <v>33</v>
+        <v>91</v>
+      </c>
+      <c r="F3330" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3330" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="3331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3331" s="3">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="B3331" s="3">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C3331" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3331" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3331" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3331" s="1" t="s">
-        <v>35</v>
+        <v>89</v>
+      </c>
+      <c r="F3331" t="s">
+        <v>88</v>
       </c>
       <c r="G3331" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3332" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3332" s="3">
-        <v>46084</v>
+        <v>46097</v>
       </c>
       <c r="B3332" s="3">
-        <v>46084</v>
+        <v>46097</v>
       </c>
       <c r="C3332" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3332" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3332" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3332" s="1" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="F3332" t="s">
+        <v>86</v>
       </c>
       <c r="G3332" s="1" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3333" s="3">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="B3333" s="3">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="C3333" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3333" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3333" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3333" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3333" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3334" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B3334" s="3">
-        <v>46086</v>
-      </c>
-      <c r="C3334" s="9">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3334" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3334" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3334" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3334" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3335" s="3">
-        <v>46087</v>
-      </c>
-      <c r="B3335" s="3">
-        <v>46087</v>
-      </c>
-      <c r="C3335" s="9">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3335" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3335" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3335" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3335" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3336" s="3">
-        <v>46090</v>
-      </c>
-      <c r="B3336" s="3">
-        <v>46090</v>
-      </c>
-      <c r="C3336" s="9">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3336" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3336" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3336" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3336" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3337" s="3">
-        <v>46091</v>
-      </c>
-      <c r="B3337" s="3">
-        <v>46091</v>
-      </c>
-      <c r="C3337" s="9">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3337" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3337" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3337" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3337" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3338" s="3">
-        <v>46092</v>
-      </c>
-      <c r="B3338" s="3">
-        <v>46092</v>
-      </c>
-      <c r="C3338" s="9">
-        <v>0.36805555555555558</v>
-      </c>
-      <c r="D3338" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3338" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3338" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3338" s="1" t="s">
-        <v>33</v>
+        <v>83</v>
+      </c>
+      <c r="F3333" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3333" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C482383-A482-4187-850B-6B301E916091}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F993B6F0-63EA-4D76-9C51-98A0BEEECBCB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3532" uniqueCount="155">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -15572,6 +15572,87 @@
   </si>
   <si>
     <t>[달러/원 환율] 새해 첫 개장, 역내 수급 대치에 1,440원 부근 박스권 2025년 12월 31일과 2026년 1월 1일 달러/원 환율은 서울 외환시장 휴장으로 거래 제한. 하지만 역외에서는 저가 매수세가 유입되며 하단 지지. 글로벌 달러가 소폭 약세를 보였고, 중국 위안화가 강세를 보였음에도 오히려 원화는 일본 엔화 약세에 일부 동조되는 모습. 하지만 연말 적은 거래량 속, 역외 달러/원 환율은 12월 30일 종가인 1,439원에서 큰 이탈 없이 보합권 등락. 역외 NDF 환율은 2.00원 상승한 1,439.45원에 최종 호가 금일 달러/원 환율은 주말간 엔화 약세와 역외 거래 감안해 1,440원 부근 개장 예상. 특별한 이벤트 없이 저가 매수세 유입되며 일시 반등 국면. 새해 맞아 거래량 부진한 가운데, 주로 역내 실수요에 따라 등락 예상. 거주자 해외투자용 달러 환전, 수입업체 결제수요 등이 하단 지지. 반면 국민연금 전략적 환헤지를 필두로 한 달러 매도 물량 출회 기대. 금일 환율은 한산한 거래 속, 역내 수급 대치에 박스권 등락 예상 [글로벌 동향] 미 달러화 약 보합, 위안화는 2024년 9월 이후 최대 강세 2024년 12월 31일 미 달러화는 연말 글로벌 주요 금융시장 휴장인 관계로 큰 변동 없이 약 보합. 주요 6개국 통화로 구성된 달러화 지수는 0.02% 하락한 98.24pt 기록. 31일 발표된 미국 고용지표는 시장 예상보다 다소 양호한 결과보였으나 시장 반응은 미온적. 신규 실업수당 청구건수는 19.9만건으로 집계되며 예상치 (21.8만건) 및 전주치 (21.5만건) 하회. 하지만 변동성이 비교적 적은 연속 실업수당 청구건수는 186.6만건으로 집계되며 예상치 (190.2만건) 및 전주치 (191.3만건) 하회. 중국의 역외 위안화는 중국 경제지표 호조에 강세 흐름 지속. 달러당 역외 위안화 환율은 0.23% 급락한 6.975위안으로 2024년 9월 이후 최저치. 중국의 12월 PMI는 제조업 및 비제조업 모두 시장 예상 상회. 제조업 PMI는 50.1pt, 비제조업 PMI는 50.2pt로 모두 기준치 50pt 상회. 선진국 통화는 유로화 강세, 엔화 약세로 상이한 퍼포먼스 [마켓 이슈] 수급 불균형은 겉으로 드러난 '증상', 한미 성장 격차가 '근본' 2025년 고환율의 배경으로 해외투자 확대에 따른 달러 수요 우위, 즉 수급 불균형이 지적. 다만 이러한 수급 불균형은 고환율의 '원인'이라기보다는 고환율과 함께 동반된 '증상'에 가깝다는 판단. 고환율의 근본적인 원인은 한미 간 잠재성장률 격차의 구조적 확대에 있음. 각국 잠재성장률은 그 나라의 장기 투자수익률을 대변하는 변수. 그리고 수익률이 더 높은 곳으로 자본이 이동하는 것이 자본시장의 기본 메커니즘. 실제 한미 잠재성장률은 2020년 전후로 역전된 이후 그 격차가 지속 확대. 한국 잠재성장률은 인구감소 및 생산성 둔화 등에 하락세. 반면 미국은 이민자 유입과 AI 등 생산성 향상 기대가 성장 잠재력을 지지 중. 이 같은 잠재성장률 격차는 금리 및 자산 기대수익률 차이로 이어지고, 이는 달러 수요 우위의 원화 약세라는 결과로 반영. 즉, 한국의 성장 잠재력 제고 없이는 원화 약세 역시 구조적으로 고착화될 가능성이 크다는 판단</t>
+  </si>
+  <si>
+    <t>고유가 랠리 진정, 원화 약세도 속도 조절 [금일 달러/원 환율 1,484~1,493원 전망]</t>
+  </si>
+  <si>
+    <t>이민혁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대외 여건 진정에 하락 예상, 중동 불안은 하단 지지 요소 전일 달러/원 환율은 유가 상승과 미국 PPI 서프라이즈, 그리고 매파적 연준에 따른 달러화 강세에 1,505원으로 갭 상승 개장. 이후 외환당국 경고성 멘트에 추가 상승은 제한된 가운데, 적극 출회되는 네고 물량에 1,500원선을 일시 하회. 하지만 외국인의 국내주식 순매도가 하단을 지지, 전일 종가 대비 17.9원 상승한 1,501.0원에 정규장 마감. 야간장에서는 매파 BOE·ECB에 따른 달러 약세에 1,495.0원으로 하락 마감. 역외 NDF 환율은 13.35원 하락한 1,486.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,480원대 하락 개장 예상. 유가 상승세가 완화됨에 따라 원화 약세 압력은 다소 누그러진 상황. 더불어 ECB 등 주요 중앙은행의 매파 기조에 강 달러 압력 역시 약화. 금일 환율은 대외 여건 진정에 하락 흐름이 우세할 전망. 하지만 글로벌 증시 부진 등 위험회피심리는 여전히 잔존. 불안 심리 자극할 중동 관련 소식 나올 시 낙폭 줄이며 1,490원대 재진입도 가능 [글로벌 동향] 유가 상승세 다소 진정, 매파 BOE·ECB에 미 달러화 약세 전일 미 달러화는 트럼프의 유가 안정 의지와 유럽계 중앙은행들의 매파 기조에 약세. 주요 6개국 통화로 구성된 달러화 지수는 1.09% 하락한 99.20pt 기록. 미국 트럼프 대통령은 이스라엘이 더 이상 이란 에너지 시설을 공격하지 않을 것이며, 이란에 대한 군사 작전은 빨리 끝날 것이라고 발언. 베센트 재무장관은 전략 비축유 추가 방출 옵션 제시한 가운데, 이란 원유에 대한 제재 해제 가능성도 거론. 이에 국제유가 상승세는 다소 누그러지며, WIT 가격은 전장 대비 0.19% 하락. 전일 영국 BOE와 유로 ECB는 통화정책회의를 열고 만장일치로 금리 동결. BOE 금리는 3.75%로 동결되었는데, 그 배경은 인플레이션 리스크. ECB 금리 역시 동결된 가운데, 일부 위원들 사이에서 4월 인상 가능성이 제기. OIS 시장에 반영된 4월 금리인상 확률은 BOE 55%, ECB 63%. 이에 파운드화 및 유로화 가치가 미 달러화 대비 1% 이상 절상 [마켓 이슈] 달러/원 장기 추세 연장 시, 연말 환율 레인지 1,468~1,578원 최근 달러/원 환율은 2021년부터 형성된 장기 상승 추세를 따라 등락. 월평균 환율에 최소제곱법을 적용한 결과, 환율의 중심 추세는 우상향 흐름 유지. 지난 5년 간 환율은 해당 추세를 중심으로 대부분의 기간 동안 ±0.5표준편차 내에서 변동. 이러한 추세가 2026년 말까지 연장될 경우, 연말 레인지는 1,468~1,578원으로 추정 (연말 추세 환율 1,523원 ±0.5표준편차 적용). 또한 2026년 한 해 동안 환율이 1,500원대에 머물 확률은 약 35% 수준 (면적 기준으로 계산). 추세 상 연말로 갈수록 1,500원대 구간의 면적이 확대되는 구조. 이는 현재 1,500원대 환율이 이례적 수준이라기보다, 통계적으로 유의미한 범위에 포함될 수 있음 시사. 다만, 이러한 추정 결과는 추세의 지속성을 전제로 한 단순 계산 결과임을 염두할 필요. 실제 환율 경로는 중동 전황과 유가 수준, 당국의 정책 대응, 그리고 수급 환경 변화 등에 따라 언제든 바뀔 수 있음</t>
+  </si>
+  <si>
+    <t>이제는 놀랍지 않은 1,500원 [금일 달러/원 환율 1,495~1,510원 전망]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이민혁</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 중동 불안 + 매파 FOMC에 급등, 1,500원대 안착 예상 전일 달러/원 환율은 미 달러화 약세에 1,487원으로 하락 개장한 이후 일시적으로 낙폭 되돌렸으나 1,490원대 진입은 실패. 이후 국제유가 하락과 더불어 국내증시는 반등하는 등 위험선호심리 회복됨에 따라 1,480원대 초중반 등락. 정규장 후반에는 달러화 약세에 동조하며 낙폭 확대, 전일 종가 대비 10.5원 하락한 1,483.1원에 정규장 마감. 야간장에서는 중동 불안과 매파적 FOMC에 1,500.7원으로 상승 마감. 역외 NDF 환율은 26.50원 상승한 1,508.25원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,500원대 개장 예상. 중동 긴장이 고조되며 유가 상방 압력, 즉 원화 약세 압력 역시 커진 상황. 여기에 매파적 연준에 따른 강 달러도 달러/원을 밀어 올리는 형국. 이에 시장 참여자들의 환율에 대한 눈높이도 한층 더 높아졌을 듯. 물론 외환당국이 미세조정 나서며 상승세는 다소 진정될 전망. 금일 환율은 장중 변동성이 큰 가운데 1,500원대 안착할 것으로 예상 [글로벌 동향] 중동·PPI·FOMC 3연타, 달러화 지수 100pt 재차 상회 전일 미 달러화는 중동 불안, 미국 PPI 서프라이즈와 매파 FOMC에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.73% 상승한 100.29pt 기록. 미국과 이스라엘 군이 이란 에너지 시설을 공격하며 유가 상승 우려 재발. 이란은 사우디와 UAE, 카타르의 에너지 시설에 대한 보복을 예고. WTI 국제유가는 전장 대비 0.11% 상승해 배럴당 96.32달러에 거래. 미국 2월 생산자물가지수 (PPI)가 예상을 상회하며 달러 강세에 기여. 2월 PPI는 전월 대비 0.7% 상승 (예상치 +0.3%, 전월치 +0.5%). 연준의 3월 FOMC 회의 결과가 매파적으로 해석되며 강 달러 요인으로 작용. 연준 금리는 1월과 마찬가지로 기존의 3.50~3.75%로 동결. 경제전망 (SEP)에서 성장 및 물가 전망치는 모두 상향 조정. 파월 의장은 물가 진전 없이는 인하도 없다는 입장. 매파적 FOMC에 미 국채금리는 장단기물 모두 상승. 뉴욕증시는 3대 지수 모두 1% 이상 급락 마감 [마켓 이슈] 미 연준 3월 FOMC에서 매파적 동결, 금리인상 가능성도 제기 3월 FOMC에서 연준은 연방기금금리를 3.50~3.75%로 동결. 견고한 성장과 안정적 실업률, 그리고 물가 상방 리스크가 동결의 배경. 이번 최신화된 경제전망 (SEP)에서 동결의 구체적인 근거가 제시. 26~28년 3개년 실질 경제성장률 전망치는 기존보다 0.1~0.3%p 상향 조정. 올해 실업률 전망치는 기존과 같은 4.4%로 유지. 헤드라인 및 근원 PCE 인플레이션 전망치는 올해 각각 0.3%p, 0.2%p 상향. 점도표는 26~28년 3개년 모두 중간값이 그대로 유지. 올해 말 금리 예상치는 3.375%로 연내 1회 인하 시사. 파월 의장은 이번 회의에서 금리인상 가능성이 제기되었다고 언급. 인상이 기본 시나리오는 아니라고 덧붙였지만, 해당 발언으로 인해 연준의 인하 기대는 더욱 약화. 선물시장에서는 연내 동결을 점치는 반면, 인하 시점은 내년 6월로 연기 (FedWatch). 한편 파월은 이번 이란 전쟁의 경제 영향 판단이 어려워 더 지켜볼 필요가 있다고 언급</t>
+  </si>
+  <si>
+    <t>이번 FOMC에서 뭣이 중헌디 [금일 달러/원 환율 1,483~1,492원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] FOMC 경계에 낙폭 제한적, 고유가에 완만한 반등 시도 전일 달러/원 환율은 국제유가 하락 및 달러화 약세에 1,490원으로 하락 개장한 이후 오전장 내내 횡보하다가 호주 RBA 금리 인상 및 일본 외환당국의 구두 개입 재료를 소화하며 오후 장중 1,487원까지 하락. 하지만 국제유가가 반등하자 환율도 낙폭을 일부 반납하며 1,490원대에 재차 진입, 전일 종가 대비 3.9원 하락한 1,493.6원에 정규장 마감. 야간장에서는 미 달러화 약세 전환에 1,488.4원으로 하락 마감. 역외 NDF 환율은 6.00원 하락한 1,486.30원에 최종 호가 금일 달러/원 환율은 간밤 달러화 약세와 역외 거래 감안해 1,480원대로 하락 개장 예상. 하지만 익일 새벽 FOMC 결과 앞두고 시장내 경계 심리 팽배, 환율 추가 하락은 제한적일 전망. 간밤 달러 약세는 포지션 정리 등 기술적 요인 탓, 아시아장에서 재차 반등 여지. 달러/원 역시 달러 반등에 동조하며 낙폭 줄여 나갈 듯. 더불어 지속되는 고유가 역시 원화 가치 회복 제약 요소. 금일 환율은 하락 개장 이후 완만한 반등 전망 [글로벌 동향] FOMC D-1, 유로화 저가 매수 및 달러 포지션 일부 정리 전일 미 달러화는 유로화 저가 매수와 FOMC 앞둔 포지션 정리에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.25% 하락한 99.56pt 기록. 중동 지역 긴장과 에너지 가격 부담에 유로존 경제는 비관적 전망으로 선회. WTI 국제유가는 중동 불안 지속에 2.72% 상승한 배럴당 96.04달러에 거래. 독일 경제연구소 ZEW 3월 경기기대지수는 -8.5pt 기록하며 전월 대비 47.9pt 급락. 시장 참여자들은 이를 오히려 유로화 저가 매수 기회로 인식하며 유로 환율 반등. 유로/달러 환율은 0.31% 상승한 1.154달러 기록. 한편 시장은 19일 새벽 연준 FOMC 결과를 앞두고 달러 포지션을 일부 정리한 것으로 추정. 유가 상승 여파에 3월 연준 금리는 동결 유력 (FedWatch 확률 99%). 선물시장은 연준의 연내 1회 정도의 금리 인하를 기대 중. 이번 FOMC에 대한 시장의 초점은 중동 전쟁의 미국 경제 영향에 대한 연준의 해석에 맞춰질 전망 [마켓 이슈] 3월 FOMC 관전 포인트: 전쟁의 경제 영향에 대한 연준 해석 19일 새벽에는 FOMC 정례회의 결과가 발표될 예정. 금리는 3.50~3.75%로 동결이 예상. 최근까지 발표된 경제 데이터는 전반적으로 양호한 상태. 여기에 최근 이란 전쟁 → 유가 상승 → 기대 인플레이션 자극까지 우려할 만한 상황. 그리고 이번 회의에서는 SEP와 점도표도 함께 발표될 예정. 성장률과 물가 전망은 소폭 상향 조정, 연말 금리 중간값은 그대로 유지 예상. 즉 '아직 경제가 괜찮기 때문에 인하도 급할 필요 없다'는 입장. 이번 FOMC 관전 포인트는 '유가 상승의 경제 영향'에 대한 연준의 해석에 있음. 연준 FRB/US 모델에 따르면, 유가 상승은 초기에는 물가에 상방 압력으로 작용하나, 시간이 지나면 경기 둔화가 근원 물가에 하방 압력을 가하는 구조. 기자회견에서 파월 의장도 유가의 물가·경기에 대한 이중적 영향을 모두 고려하겠다는 입장 표명할 전망. 시장은 연준의 '해석'에 반응할 것이며, 이 과정 중에는 가격 변동성이 불가피해 보임</t>
+  </si>
+  <si>
+    <t>2025년 결산, 확연히 높아진 달러/원 눈높이</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 연말 종가는 1,439원, 연평균은 1,422원으로 역대 최고 전일 달러/원 환율은 달러 강세 영향에 소폭 상승 개장한 이후, 꾸준한 결제수요 유입 등에 완만한 상방 흐름. 국내증시에서 외국인의 주식 순매도까지 가세하는 등 달러 수요 증가에 1,440원 근접. 이후 외환당국 종가관리 경계에 상단 제약되며 전일 종가 대비 9.2원 하락한 1,439.0원에 정규장 마감. 야간장에서는 정규장 마감 이후 저가 매수에 1,440원 상회한 이후 추가 상승한 뒤, 되돌림 나타나며 1,439.5원으로 마감. 역외 NDF 환율은 0.35원 하락한 1,437.10원에 최종 호가 금일 서울 외환시장은 연말연초를 맞아 휴장. 2025년 환율 종가는 1,439원 기록하며 지난해 종가인 1,472원 대비 33.5원 하락. 외환당국의 강한 개입과 국민연금 환헤지 재개가 연말 환율 하락에 기여. 하지만 연평균 환율은 1,422원으로 연간 기준 역대 최대치 기록. 역내 달러 수요 우위 등 수급 불균형이 금년 환율 상승의 주 요인. 내년 역시 구조적 수급 변화에 1,400원대 고환율 구간 유지 예상 [글로벌 동향] 별 내용 없던 FOMC 의사록, 미 달러화는 기술적인 강세 전일 미 달러화는 연말 맞아 거래량 한산한 가운데, 반발 매수 등 기술적 요인에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.22% 상승한 98.25pt 기록. 시장은 주요 경제지표 부재 속, FOMC 의사록에 주목. 하지만 이미 예상된 내용이었다는 점에서 시장 반응은 미온적. 의사록에 따르면, 대부분 위원들은 인플레이션 완화 시 추가 인하가 적절하다는 입장. 다만 일부 위원들은 당분간 금리동결 기조 유지를 주장. 시장 참가자들은 내년 3월부터 연준이 금리인하를 재개할 것으로 기대. FedWatch에서 1월 금리인하 확률은 14.9%, 3월 확률은 53.1%로 반영 중. 미 국채금리는 의사록 재료 소화하며 장단기물 혼조 마감. 한편 시카고 PMI는 전월대비 7.2p 급등한 43.5p 기록. 하지만 기준치인 50p는 하회하며 업황 위축 국면 시사. 중국 역외 위안화 환율은 달러당 7위안 하회하며 지난해 9월 이후 최저치 기록 [마켓 이슈] 고점은 낮아졌지만 높아진 눈높이... 1,400원대 머무를 달러/원 2025년 달러/원 환율은 1,439원으로 정규장 마감. 최근 1,480원을 넘나들던 국면과 비교하면 상당 폭 하락. 하지만 절대 수준으로는 여전히 과거 대비 높은 구간. 연평균 환율은 1,422원으로 역대 최고, 연말 기준으로는 1997년과 2024년 이후 세 번째로 높은 레벨. 단기적으로는 추가 하락 여력이 존재. 기술적으로 급격한 고점 형성 이후 조정 국면에 진입한 데다, 당국의 환율 안정 조치가 상단 제약 중. 대외적으로도 연준 금리인하 사이클, QT 종료, 차기 연준 의장 지명 등 달러 약세 환경이 조성 중. 다만 이를 원화의 추세적 강세로 해석하기에는 시기상조. 한미 금리 역전이 지속되고 있고, 거주자 해외투자 확대 등 구조적 달러 수요가 잔존. 이 같은 구조의 근원에는 한미 간 잠재성장률 역전이 자리 잡고 있음. 중장기 성장 기대의 상대적 우위가 미국에 있는 한, 달러/원 역시 과거 평균으로의 회귀보다는 1,400원대에 고착될 가능성이 크다는 판단</t>
+  </si>
+  <si>
+    <t>2025년 종가, 정부의 강한 환율 안정 의지 [금일 달러/원 환율 1,425~1,436원 전망]</t>
+  </si>
+  <si>
+    <t>문정희</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 2025년 마지막 거래일, 종가는 1,420원대 마감 예상 전일 달러/원 환율은 0.3원 하락한 1,440원으로 출발했으나, 이후 국내 증시 상승 등 증시 호조와 외국인 주식 순매수 지속, 당국 물량으로 추정되는 달러 매도 압력, 수출 네고 물량까지 출회되어 종가는 10.5원 하락한 1,429.8원에 정규장이 마감됨. 야간장에서는 단기 급락에 대한 되돌림과 뉴욕증시 조정에 따른 위험회피 심리 등에 1,434.1원으로 반등, NDF 역외 환율도 1,430원대 초반에서 호가됨 금일 달러/원 환율은 올해 마지막 환율로 역외에서는 1,430원대까지 반등했으나, 전일에도 개장 이후 하방 압력이 지속되었다는 점, 연말 종가가 매우 중요하다는 점에서 다시 1,420원대로 회귀할 전망. 연말에 거래가 많지 않다는 점과 수출 업체의 네고물량 출회, 대외적으로 일본 엔화 및 중국 위안화 등 아시아 통화 강세, 마지막으로 정부의 환율 안정 의지 등 전일과 유사한 개장 이후 환율 하방이 예상됨 [글로벌 동향] 달러 강보합에도 일본 엔화와 중국 위안화의 동반 강세 전일 미 달러화는 연말로 시장 분위기가 차분한 가운데 일본 엔화의 강세에도 유로화 약세 등에 0.02% 상승, 강보합을 기록함. 경제지표가 부재한 가운데 미국 11월 잠정 주택판매는 전월대비 3.3% 증가하여 호조를 보였지만 댈러스 연준 제조업 활동지수는 - 10.9로 기준치를 하회하는 위축국면을 지속하여 상반된 결과로 발표됨. 전일 공개된 일본 BOJ 12월 금정위 의사록에서 일부 위원들이 너무 낮은 실질금리와 엔화의 과도한 약세를 지적하며 추가 금리인상 필요성을 강조함. 이에 달러/엔 환율이 0.27% 하락하여 엔화가 달러 대비 강세를 이어감. 중국 역외 위안화 환율은 다시 7.0위안을 하회했으며 지난 9월 이후 최저치를 기록함. 미국 국채 금리는 장단기에서 모두 소폭 하락했고, 뉴욕증시는 3대 지수 모두 조정을 보였으며, 국제유가는 2% 이상 상승함. 시장은 연말 거래가 많지 않은 가운데 조용하게 지나가고 있음 [마켓 이슈] 2025년 연말 종가, 여전히 원화는 주요 통화 대비 약세 달러/원 환율이 연말 앞두고 1주일 동안 약 40원 이상 하락했으나, 아직도 원화는 달러 대비 약세를 보이고 있음. 달러화 지수는 연초 107.8pt에서 전일 98pt로 연초 대비 9.1% 하락, 연평균으로는 3.2% 하락함. 반면 달러/원 환율은 연초 1,470원에서 전일 1,430원으로 2.7% 하락했으나, 연평균 환율은 1,422원으로 전년도 평균 환율 1,364원에 비해 4.2% 상승함. 즉 달러화는 전세계적으로 3% 이상 하락한 반면 달러/원 환율이 4.2% 상승했다는 점에서 원화는 달러 대비 약 7% 이상 약세를 보였음. 특히 지난 8월부터 원화의 달러 약세 양상은 심화, 10월부터 12월까지도 이러한 현상은 지속됨. 달러 약세에도 달러/원 환율 상승 배경으로 달러 부족현상을 지목하고 있으나 역내 달러 부족 현상보다 수요가 몰리는 가운데 공급이 부족한 수급 불균형 영향이 컸음. 따라서 2025년 환율 상승은 외환 수급 불균형이라고 판단됨</t>
+  </si>
+  <si>
+    <t>브레이크가 고장난 KRW [금일 달러/원 환율 1,433~1,445원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 강한 하락 모멘텀에 1,430원대 진입 후 추가 하락 시도 전일 달러/원 환율은 외환당국 실개입 경계와 더불어 국민연금의 전략적 환헤지 재개 소식 등에 하락세 지속. 환율 급락으로 수출업체 추격 네고물량 출회, 외국인의 국내 주식 순매수까지 가세하며 장중 1,420원대 진입. 이후 저가 매수세 유입에 낙폭 일부 축소되며 전일 종가 대비 9.5원 하락한 1,440.3원에 정규장 마감. 야간장에서는 거래량 한산한 가운데 저가 매수에 소폭 반등하며 1,442.2원으로 마감. 역외 NDF 환율은 1.90원 상승한 1,440.60원에 최종 호가 금일 달러/원 환율은 주말 동안 달러 흐름과 역외 거래 감안해 1,440원대 개장 예상. 연말 맞아 달러/원 자극할 특별한 대외 이벤트는 부재한 상황. 하지만 얇은 유동성 속, 여전히 잔존한 당국 개입 경계에 변동성 확대될 소지. 기술적으로도 고점 형성 이후 본격 하락 국면 진입 판단. 반발 매수에 일시 반등 가능하나 추세적으로는 하방 우위 구간. 금일 환율은 강한 하락 모멘텀에 1,430원대 진입 이후 추가 하락 시도 예상 [글로벌 동향] 연말 얇은 유동성 속, 일본 엔저 등에 미 달러화 강보합 전일 미 달러화는 특별한 이벤트 부재한 가운데, 적은 거래량과 엔저에 강보합. 주요 6개국 통화로 구성된 달러화 지수는 0.09% 상승한 98.02pt 기록. 미 국채금리는 장단기 대체로 하락한 반면, 한산한 거래에 주요 통화 움직임은 제한적. 유로/달러는 0.01% 소폭 하락하며 보합권에서 등락. 반면 일본 엔화는 소비자물가지수의 시장 예상 하회 등에 약세로 전환. 12월 도쿄 소비자물가지수는 전년대비 2.0% 상승에 그치며 예상치 (+2.3%) 하회. 이에 달러당 엔화 환율은 0.51% 상승한 156.50엔 기록하며 달러화 지수 상승에 기여. 한편 중국 위안화 환율은 역외에서 일시적으로 7위안 하회하며 위안화 강세 흐름. 시장에서는 위안화 강세에 대응한 중국 외환당국 개입을 경계하는 상황. 인민은행 (PBOC)은 환율 기대 관리를 강화해 과도한 변동 리스크를 방지할 것이라고 밝힘 [마켓 이슈] 산이 높았던 만큼 골도 깊을 달러/원, 얼마나·언제까지 하락? 통상 환율은 상승 및 하락 국면 모두에서 관성을 갖는 가격 변수. 특히 고점이 높았던 국면일수록 조정 폭과 기간 역시 일정 수준 확보되는 경향. 즉, 이번 달러/원 흐름 역시 본격적인 하락 국면에 진입했을 가능성. 따라서 향후 환율이 얼마나, 언제까지 내려갈 수 있을지 가늠할 필요. 2022년 이후 달러/원 환율의 상승 이후 되돌림 (하락) 사례는 크게 5번. 이들 사례에서 상승분 대비 되돌림 비율은 평균 76% (67~88%). 하락에 소요된 기간은 평균 60영업일 (51~75영업일). 이 같은 과거의 패턴을 현재 국면에 적용 시, 향후 환율은 1~2개월 동안 추가 하락할 가능성. 올해 6~12월 동안 128원 상승분을 기준으로 과거 되돌림 비율 (67~88%) 적용 시, 향후 달러/원 환율 저점은 1,368~1,396원 수준으로 추정. 단, 이는 추세적 원화 강세 전환이라기보다는, 고점 형성 이후 나타나는 전형적인 조정 패턴으로 해석하는 것이 합리적이라는 판단</t>
+  </si>
+  <si>
+    <t>모처럼 아래로 '큰 거 한 방'을 보여준 달러/원 [금일 달러/원 환율 1,438~1,455원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 하방 변동성이 확대된 환율, 1,450원 하회 안착이 관건 지난 24일 달러/원 환율은 1.4원 상승 출발했으나, 이후 정부의 강력한 환율 안정 대응 소식에 급락, 하루 만에 33.8원 급락하며 1,449.8원에 마감함. 야간 장에서도 달러 약세와 원화 강세가 지속되며 1,445.7원으로 종료되었고, 역외 NDF 환율 역시 1,443.4원으로 낮아지는 등 달러/원 환율은 1,440원대로 레벨이 하락함 금일 달러/원 환율은 지난 24일 단기 급락에 따른 일부 되돌림이 나올 것인지, 추가 하락할 것인지 변동성이 클 것으로 예상됨. 연말 거래량이 많지 않고, 역외에서 달러가 약세를 보이는 점, 일본 엔화와 중국 위안화 등 아시아 통화도 일제히 강세를 보이고 있어 금일 환율은 단기 반등 이후 다시 하락할 가능성이 크다고 판단됨. 다만, 환율 급락으로 그 동안 미뤘던 결제 수요가 유입될 것으로도 예상되어 금일 환율은 1,440원대 중반에서 등락이 예상됨 [글로벌 동향] 연말 산타 랠리, 달러 약세에 아시아 통화 동반 강세 전일 미 달러화는 크리스마스 데이로 휴장한 가운데 역외에서 소폭 하락, 지수는 98pt를 하회함. 24일 뉴욕 증시는 오전 장만 열리고 조기 폐장한 가운데 연말 및 산타 랠리 등 위험선호 심리에 상승, S&amp;P500 지수는 사상 최고치를 경신함. 미 국채 금리도 소폭 하락하며 채권 가격도 강세를 보임. 24일 발표된 주간 실업수당청구건수느 21만 4천건으로 예상치 22만 4천건을 하회함. 고용시장이 비교적 양호하다는 것을 의미. 한편, 중국 달러/위안 환율이 장중 7위안을 하회하기도 하는 등 전체적으로 달러가 약세를 지속함. 일본 엔화도 달러 대비 강세, 한국 시장에서 원화가 급격한 강세를 보임에 따라 엔화도 강세를 이어가 달러/엔 환율도 156엔을 하회함. 연말 거래가 많지 않은 가운데 위험회피심리 완화, 달러 약세에 비 달러 통화가 대부분 강세를 보임 [마켓 이슈] 정부의 강한 정책 대응과 달러 약세 조합에 모처럼 큰 폭 하락 지난 24일 달러/원 환율이 30원 이상 급락하며 모처럼 큰 폭 하락함. 개장 전 김용범 대통령실 정책실장이 '말보다 행동'을 언급하며 환율 안정에 강한 의지를 피력했고, 오전에 기획재정부에서 외환수급 불균형 해소를 위한 세제지원 방안이 발표된 바 있음. 이번 환율 하락은 연말을 앞두고 거래량이 많지 않은 가운데 대외적으로 달러가 약세를 보이고, 그 동안 고환율의 레벨 부담, 정부의 강한 환율 안정 의지 등이 동반되며 하루 만에 30원 이상 급락함. 연말까지 거래일이 많지 않은 가운데 정부가 여기서 멈추지는 않을 것으로 판단. 만약 연말까지 환율이 1,450원을 하회하고 안착한다면 연초 이후에는 환율 레인지가 한 단계 낮아진 1,400원에서 1,450원 레인지로 회귀할 것으로 예상됨</t>
+  </si>
+  <si>
+    <t>주춤한 달러, 정부의 연이은 고환율 정책 대응 [금일 달러/원 환율 1,472~1,484원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 정부의 연이은 고환율 대응, 강한 한 방이 필요한 시점 전일 달러/원 환율은 역외에서 달러화 지수가 하락하고, 일본 엔화 등이 강세였음에도 원화가 약세를 보였음. 개장은 0.1원 하락했으나 종가는 3.5원 상승한 1,483.6원에 마감함. 야간 장에서는 미국 3분기 GDP 호조 소식에 0.90원 상승한 1,481원을 기록, NDF 역외환율은 뉴욕증시 상승과 일본 엔화 강세 및 달러가 다시 약세를 보임에 따라 3.70원 하락한 1,478.0원에 호가됨 금일 달러/원 환율은 미국 경제 호조에도 달러가 약세를 보였고, 일본 엔화가 강세를 이어간 점, 역외 환율이 소폭 하락함을 감안하면 1,480원 전후에서 등락할 것으로 예상됨. 금일 오전에도 정부와 당국은 환율 안정을 위해 강한 대응을 강조함. 최근 일본 정부 역시 당국과 중앙은행 모두 엔저에 대한 강한 대응을 언급했고, 이틀 동안 엔화도 강세를 보임. 환율이 수급 불균형과 적은 거래 등으로 상승 심리가 지속됨에 따라 정부의 강한 대응이 예상되며 이에 장중 변동폭도 클 수 있음 [글로벌 동향] 미국 3분기 GDP 호조에도 엔 강세에 달러는 98pt 하회 전일 미 달러화는 미국 3분기 실질 GDP 결과가 예상치를 크게 상회했음에도 일본 엔화 강세 영향에 0.35% 하락함. 미국 연방 정부 셧다운으로 지연 발표된 3분기 실질 성장률은 전기비 연율로 4.3%를 기록, 시장 예상치 3.3%와 애틀란타 연준에서 추정한 3.5%를 모두 큰 폭으로 상회함. 양호한 3분기 성장에도 불구하고 미국 국채 금리는 단기 2년물만 2.5bp 상승하는 등 채권 시장은 미미했으며, 뉴욕증시는 연준의 금리인하 확률 하락에도 실적 개선과 중국에 대한 반도체 관세 부과 보류 소식에 상승세를 이어감. 한편, 일본 엔화는 전 전일에 이어 전일에도 강세 흐름을 이어감. 일본 정부의 엔저에 대한 강한 경고와 일본 국채 10년물 금리가 2%를 상회함에 따라 미일 장기 금리 격차가 좁혀졌기 때문. 미국 3분기 성장 호조에도 4분기 성장은 셧다운 영향에 큰 폭 둔화가 예상된다는 점에서 달러는 크게 영향을 받지 않았음 [마켓 이슈] 미국 3분기 성장률 호조, 개인소비와 정부지출이 성장 견인 전일 저녁 발표된 미국의 3분기 실질 GDP 결과가 전기비 연율로 4.3%를 기록, 예상치는 물론 이전치를 모두 상회했고, 2023년 3분기 이후 최고치를 경신함. 세부적으로 가장 큰 비중을 차지하는 개인소비지출이 전기비 연율로 3.5% 증가, 이전 2.7%에 비해 더 큰 폭으로 성장함. 정부 지출은 전기비 연율로 2.2% 증가했으며, 총 투자는 감소했지만, 수출이 늘고 수입이 감소한 영향도 있었음. 당초 예상보다 양호한 성장이 4분기까지 지속될 가능성은 여전히 낮음. 10월 1일부터 셧다운이 6주 동안 지속되었고, 이로 인해 4분기 성장은 3분기에 비해 큰 폭 둔화가 예상됨. 한편, 이번 3분기 성장으로 연준의 금리인하 경로가 수정되지 않을 것이라는 전망도 우세. 이후 발표된 고용, 물가, 소비지표 등이 약화되었고, 전일 컨퍼런스보드 소비기대지수 12월 결과는 89pt대로 하락함. 경제는 양호했지만 앞으로 지속될 가능성은 낮다고 평가됨</t>
+  </si>
+  <si>
+    <t>연말에도 방향을 틀지 못하는 달러/원 환율 [금일 달러/원 환율 1,472~1,482원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 연말에도 1,470원대 박스권에서 벗어나지 못하는 환율 전일 달러/원 환율은 0.3원 하락한 1,476.6원에 출발했으나, 이후 상승 전환했고 오후들어 상승 폭이 조금씩 확대되며 종가는 3.8원 상승한 1,480.1원에 마감, 지난 4월 9일 이후 종가로는 최고치를 기록함. 야간장에서는 일본 재무상의 발언과 엔 강세에도 뉴욕증시 상승에 원화가 더 약세를 보이며 1,481.0원에 거래되었고, 역외 NDF 환율은 0.05원 하락한 1,478.0원에 호가됨 금일 달러/원 환율은 역외 환율 하락을 반영하여 다시 1,470원대 후반에서 출발할 것으로 예상되나, 낙폭은 제한적일 것으로 판단, 그렇다고 환율 상방도 높지 않을 가능성이 큼. 달러는 조정을 보이고 있고, 최근 유로화와 영국 파운드화, 중국 위안화 등이 강세를 보임. 반면 일본 엔화와 한국 원화는 여전히 과도한 약세. 양국 정부의 환율 안정 조치에도 외환 수급, 아시아 통화 동조화 등으로 변동성은 매우 낮아짐 [글로벌 동향] 일본 재무상의 과잉 엔저 경고, 엔 강세에 달러화 반락 전일 미 달러화는 일본 엔화의 강세에 0.42% 하락한 98.30pt를 기록함. 전일 일본 재무상 가타야마는 최근 엔 약세는 펀더멘털에 부합하지 않은 것이고 오히려 투기적인 것이었다고 주장하며 과감한 조치를 취할 것이라고 공언함. 일본 정부와 당국에서 연이은 엔 과잉 약세에 대해 경고함에 따라 전일 달러/엔 환율은 0.44% 하락함. 또한 영국 3분기 GDP는 전기 대비 0.1% 상승하여 예상치에 부합, 성장세는 다소 약하지만 회복세에 있다는 평가에 파운드화가 달러 대비 강세를 보였고, 유로화 역시 달러 대비로 강세를 보임. 한편, 미국 스티브 마이런 연준 이사는 12월 FOMC 회의에서 기준금리 50bp 인하를 주장했다고 공식 발표했고, 1월에도 금리인하가 필요하다고 주장함. 전일 엔비디아의 중국 수출 가능성 소식에 뉴욕증시가 상승, 위험회피심리 완화 역시 달러에는 약세 요인으로 작용함 [마켓 이슈] 정부의 환율 안정 조치에도 외환 수급 불균형에 고환율 지속 기획재정부와 한국은행 등 정부 당국은 지난 10월부터 연이어 환율 안정 조치를 발표하고 있음. 환율 안정 조치로 불리지만 속내는 환율 하락을 위한 대책이라고 볼 수 있음. 지난주 19일 금요일에는 한국은행의 임시 금통위가 열렸고, 중앙은행에 외화를 예치할 경우 이자를 주는 지준부리 조치도 발표함. 달러 수요뿐만 아니라 달러 공급을 위해 외환 규제를 완화하고, 외국인 투자자에게 국내 투자 (달러 공급)를 위한 완화 조치도 시행함. 그럼에도 달러/원 환율은 쉽게 꺾이지 않고 있음. 증권예탁결제원의 통계시스템인 SEIBro에 따르면 12월 현재 해외 주식 및 채권 보유 잔고는 2,234억 달러로 연초 대비 600억 달러 이상 증가했음. 해외주식 상승 영향도 있지만, 전년도에 비해 약 100억 달러 이상 증가함. 이 자금이 역내로 환류된다면 막대한 달러 공급 요인이 되겠으나, 강제할 수 없다는 점에서 수급 상에 고환율에 대한 우려는 여전함</t>
+  </si>
+  <si>
+    <t>종가관리 하기 딱 좋은 연말 장세 [금일 달러/원 환율 1,470~1,480원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 엔 약세 동조에도 회복된 위험선호심리가 상방 제약 요소 전일 달러/원 환율은 한국은행의 외환건전성 부담금 면제 등 환율 안정 조치 발표에 하락 흐름 보였고, 장중 일본 BOJ 금리인상 결정 소화하며 하락세 유지. 부족한 네고 및 외국인의 국내주식 순매도 등 수급 불균형에도 불구, 당국 경계에 1,480원 밑에서 등락. 하지만 하방 역시 제한되며 전일 종가 대비 2.0원 하락한 1,476.3원에 정규장 마감. 야간장에서는 BOJ 추가 인상 불확실성 등 엔화 약세에 동조해 1,478.0원으로 상승 마감. 역외 NDF 환율은 0.65원 하락한 1,473.70원에 최종 호가 금일 달러/원 환율은 주말간 달러 강세에도 역외 거래 감안해 보합권 개장 예상. 엔화 약세에 원화도 동조하며 하방 제약적인 흐름 보일 것으로 예상. 다만 뉴욕증시 회복 분위기에 금일 국내증시도 긍정적 기대. 위험선호심리와 외국인 자금 순유입은 원화 약세 방어 요인. 한편 외환당국의 전방위적 조치가 환율 변동성을 키울 리스크 유의. 연말 유동성 얇은 장세 속, 당국 종가관리성 개입 시 하방 변동성 확대될 소지 [글로벌 동향] BOJ의 향후 금리 경로 불확실성에 엔화 약세, 달러 반등 전일 미 달러화는 일본 BOJ 금리인상 이후 오히려 엔화 절하에 강세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.26% 상승한 98.71pt 기록. 일본 BOJ는 금정위에서 예상대로 0.25%p 금리인상 단행. 올해 1월 이후 11개월 만에 인상. 하지만 인상에도 불구하고, 일본 엔화는 다소 완화적인 기자화견 소화하며 약세. 우에다 총재는 다음 인상 시점이 향후 경제지표에 달려있다며 신중한 발언. 기자회견 중 달러/엔 환율은 156엔 상회, 유럽장에서는 157엔을 상회. 이에 일본 재무상의 구두 개입이 나왔으나 상승세 이어지며 하루새 1.33% 급등. 한편 미 연준 일부 위원의 다소 매파적 발언은 달러에 강세 요인으로 작용. 존 윌리엄스 총재는 통화정책이 '약간 제약적'이며, 긴급 인하 필요성은 없다고 언급. 이에 미 국채금리는 장단기물 대체로 소폭 상승하며 마감. 뉴욕증시는 틱톡 불확실성 해소에 위험선호 회복되며 3대 지수 모두 상승 마감 [마켓 이슈] 연말 유동성 얇은 장세 속, 당국發 환율 하락 쏠림 리스크 유의 최근 달러/원 환율은 1,480원을 상회하며 1,500원 레벨 위협하는 고환율 구간 진입. 이에 외환당국은 강력한 구두개입에 이어 달러 유동성 개선 조치 등을 연달아 발표. 더불어 국민연금과의 외환스와프 재개까지 나서며 고환율에 대한 명확한 경계 신호. 올해 거래일이 불과 6영업일 남은 상황 속, 시기적으로 연말 거래량 감소로 유동성이 얇아지는 구간 진입. 달러/원 현물환 시장 12월 거래량은 연평균의 약 70% 수준에 불과. 이 같은 환경에서 정부의 연말 종가관리성 달러 매도 개입도 가능한 상황이란 판단. 종가관리의 배경에는 외화부채, 재정지표, 공공기관 성과 등 회계적 요인 존재. 하지만 보다 중요한 목적은 지금 같은 '고환율 고착화' 기대 심리를 꺾는 데에 있다는 판단. 즉, 지금 같이 유동성이 얇은 장세에서 당국 개입이 본격화할 경우, 환율 하락 쏠림이 단기에 급격히 나타날 소지. 따라서 시장 참여자들도 해당 리스크 고려할 필요</t>
   </si>
 </sst>
 </file>
@@ -16001,7 +16082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3333"/>
+  <dimension ref="A1:G3331"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -65017,7 +65098,7 @@
       </c>
       <c r="F3264" s="1"/>
     </row>
-    <row r="3265" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3265" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3265" s="3">
         <v>46003</v>
       </c>
@@ -65032,7 +65113,7 @@
       </c>
       <c r="F3265" s="1"/>
     </row>
-    <row r="3266" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3266" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3266" s="3">
         <v>46004</v>
       </c>
@@ -65047,7 +65128,7 @@
       </c>
       <c r="F3266" s="1"/>
     </row>
-    <row r="3267" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3267" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3267" s="3">
         <v>46005</v>
       </c>
@@ -65062,7 +65143,7 @@
       </c>
       <c r="F3267" s="1"/>
     </row>
-    <row r="3268" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3268" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3268" s="3">
         <v>46006</v>
       </c>
@@ -65077,7 +65158,7 @@
       </c>
       <c r="F3268" s="1"/>
     </row>
-    <row r="3269" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3269" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3269" s="3">
         <v>46007</v>
       </c>
@@ -65092,7 +65173,7 @@
       </c>
       <c r="F3269" s="1"/>
     </row>
-    <row r="3270" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3270" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3270" s="3">
         <v>46008</v>
       </c>
@@ -65107,7 +65188,7 @@
       </c>
       <c r="F3270" s="1"/>
     </row>
-    <row r="3271" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3271" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3271" s="3">
         <v>46009</v>
       </c>
@@ -65122,7 +65203,7 @@
       </c>
       <c r="F3271" s="1"/>
     </row>
-    <row r="3272" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3272" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3272" s="3">
         <v>46010</v>
       </c>
@@ -65137,12 +65218,12 @@
       </c>
       <c r="F3272" s="1"/>
     </row>
-    <row r="3273" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3273" s="3">
-        <v>46011</v>
+        <v>46013</v>
       </c>
       <c r="B3273" s="3">
-        <v>46011</v>
+        <v>46013</v>
       </c>
       <c r="C3273" s="9">
         <v>0.36805555555555558</v>
@@ -65150,14 +65231,22 @@
       <c r="D3273" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3273" s="1"/>
-    </row>
-    <row r="3274" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3273" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3273" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3273" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3274" s="3">
-        <v>46012</v>
+        <v>46014</v>
       </c>
       <c r="B3274" s="3">
-        <v>46012</v>
+        <v>46014</v>
       </c>
       <c r="C3274" s="9">
         <v>0.36805555555555558</v>
@@ -65165,14 +65254,22 @@
       <c r="D3274" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3274" s="1"/>
-    </row>
-    <row r="3275" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3274" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3274" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3274" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3275" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B3275" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C3275" s="9">
         <v>0.36805555555555558</v>
@@ -65180,14 +65277,22 @@
       <c r="D3275" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3275" s="1"/>
-    </row>
-    <row r="3276" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3275" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3275" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3275" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3276" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B3276" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="C3276" s="9">
         <v>0.36805555555555558</v>
@@ -65195,14 +65300,22 @@
       <c r="D3276" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3276" s="1"/>
-    </row>
-    <row r="3277" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3276" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3276" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3276" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3277" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B3277" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C3277" s="9">
         <v>0.36805555555555558</v>
@@ -65210,14 +65323,22 @@
       <c r="D3277" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3277" s="1"/>
-    </row>
-    <row r="3278" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3277" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3277" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3277" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3278" s="3">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="B3278" s="3">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="C3278" s="9">
         <v>0.36805555555555558</v>
@@ -65225,14 +65346,22 @@
       <c r="D3278" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3278" s="1"/>
-    </row>
-    <row r="3279" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3278" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3278" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3278" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3279" s="3">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="B3279" s="3">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="C3279" s="9">
         <v>0.36805555555555558</v>
@@ -65240,14 +65369,22 @@
       <c r="D3279" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3279" s="1"/>
-    </row>
-    <row r="3280" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3279" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3279" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3279" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3280" s="3">
-        <v>46018</v>
+        <v>46024</v>
       </c>
       <c r="B3280" s="3">
-        <v>46018</v>
+        <v>46024</v>
       </c>
       <c r="C3280" s="9">
         <v>0.36805555555555558</v>
@@ -65255,14 +65392,22 @@
       <c r="D3280" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3280" s="1"/>
-    </row>
-    <row r="3281" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3280" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3280" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3280" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3281" s="3">
-        <v>46019</v>
+        <v>46027</v>
       </c>
       <c r="B3281" s="3">
-        <v>46019</v>
+        <v>46027</v>
       </c>
       <c r="C3281" s="9">
         <v>0.36805555555555558</v>
@@ -65270,14 +65415,22 @@
       <c r="D3281" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3281" s="1"/>
-    </row>
-    <row r="3282" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3281" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3281" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3281" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3282" s="3">
-        <v>46020</v>
+        <v>46028</v>
       </c>
       <c r="B3282" s="3">
-        <v>46020</v>
+        <v>46028</v>
       </c>
       <c r="C3282" s="9">
         <v>0.36805555555555558</v>
@@ -65285,14 +65438,22 @@
       <c r="D3282" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3282" s="1"/>
-    </row>
-    <row r="3283" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3282" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3282" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3282" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3283" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="B3283" s="3">
-        <v>46021</v>
+        <v>46029</v>
       </c>
       <c r="C3283" s="9">
         <v>0.36805555555555558</v>
@@ -65300,14 +65461,22 @@
       <c r="D3283" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3283" s="1"/>
-    </row>
-    <row r="3284" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3283" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3283" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3283" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3284" s="3">
-        <v>46022</v>
+        <v>46030</v>
       </c>
       <c r="B3284" s="3">
-        <v>46022</v>
+        <v>46030</v>
       </c>
       <c r="C3284" s="9">
         <v>0.36805555555555558</v>
@@ -65315,14 +65484,22 @@
       <c r="D3284" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3284" s="1"/>
+      <c r="E3284" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3284" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3284" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="3285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3285" s="3">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="B3285" s="3">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C3285" s="9">
         <v>0.36805555555555558</v>
@@ -65331,10 +65508,10 @@
         <v>53</v>
       </c>
       <c r="E3285" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F3285" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G3285" s="4" t="s">
         <v>84</v>
@@ -65342,10 +65519,10 @@
     </row>
     <row r="3286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3286" s="3">
-        <v>46027</v>
+        <v>46034</v>
       </c>
       <c r="B3286" s="3">
-        <v>46027</v>
+        <v>46034</v>
       </c>
       <c r="C3286" s="9">
         <v>0.36805555555555558</v>
@@ -65354,10 +65531,10 @@
         <v>53</v>
       </c>
       <c r="E3286" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F3286" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G3286" s="4" t="s">
         <v>84</v>
@@ -65365,10 +65542,10 @@
     </row>
     <row r="3287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3287" s="3">
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="B3287" s="3">
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="C3287" s="9">
         <v>0.36805555555555558</v>
@@ -65377,10 +65554,10 @@
         <v>53</v>
       </c>
       <c r="E3287" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F3287" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G3287" s="4" t="s">
         <v>84</v>
@@ -65388,10 +65565,10 @@
     </row>
     <row r="3288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3288" s="3">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B3288" s="3">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="C3288" s="9">
         <v>0.36805555555555558</v>
@@ -65400,10 +65577,10 @@
         <v>53</v>
       </c>
       <c r="E3288" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F3288" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G3288" s="4" t="s">
         <v>84</v>
@@ -65411,10 +65588,10 @@
     </row>
     <row r="3289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3289" s="3">
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="B3289" s="3">
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="C3289" s="9">
         <v>0.36805555555555558</v>
@@ -65423,10 +65600,10 @@
         <v>53</v>
       </c>
       <c r="E3289" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F3289" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G3289" s="4" t="s">
         <v>84</v>
@@ -65434,10 +65611,10 @@
     </row>
     <row r="3290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3290" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="B3290" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="C3290" s="9">
         <v>0.36805555555555558</v>
@@ -65446,10 +65623,10 @@
         <v>53</v>
       </c>
       <c r="E3290" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F3290" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G3290" s="4" t="s">
         <v>84</v>
@@ -65457,10 +65634,10 @@
     </row>
     <row r="3291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3291" s="3">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="B3291" s="3">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="C3291" s="9">
         <v>0.36805555555555558</v>
@@ -65469,10 +65646,10 @@
         <v>53</v>
       </c>
       <c r="E3291" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F3291" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G3291" s="4" t="s">
         <v>84</v>
@@ -65480,10 +65657,10 @@
     </row>
     <row r="3292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3292" s="3">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="B3292" s="3">
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="C3292" s="9">
         <v>0.36805555555555558</v>
@@ -65492,10 +65669,10 @@
         <v>53</v>
       </c>
       <c r="E3292" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F3292" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G3292" s="4" t="s">
         <v>84</v>
@@ -65503,10 +65680,10 @@
     </row>
     <row r="3293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3293" s="3">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B3293" s="3">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="C3293" s="9">
         <v>0.36805555555555558</v>
@@ -65515,10 +65692,10 @@
         <v>53</v>
       </c>
       <c r="E3293" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F3293" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G3293" s="4" t="s">
         <v>84</v>
@@ -65526,10 +65703,10 @@
     </row>
     <row r="3294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3294" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="B3294" s="3">
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="C3294" s="9">
         <v>0.36805555555555558</v>
@@ -65538,10 +65715,10 @@
         <v>53</v>
       </c>
       <c r="E3294" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F3294" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G3294" s="4" t="s">
         <v>84</v>
@@ -65549,10 +65726,10 @@
     </row>
     <row r="3295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3295" s="3">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="B3295" s="3">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="C3295" s="9">
         <v>0.36805555555555558</v>
@@ -65561,10 +65738,10 @@
         <v>53</v>
       </c>
       <c r="E3295" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F3295" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G3295" s="4" t="s">
         <v>84</v>
@@ -65572,10 +65749,10 @@
     </row>
     <row r="3296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3296" s="3">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="B3296" s="3">
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="C3296" s="9">
         <v>0.36805555555555558</v>
@@ -65584,10 +65761,10 @@
         <v>53</v>
       </c>
       <c r="E3296" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F3296" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G3296" s="4" t="s">
         <v>84</v>
@@ -65595,10 +65772,10 @@
     </row>
     <row r="3297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3297" s="3">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="B3297" s="3">
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="C3297" s="9">
         <v>0.36805555555555558</v>
@@ -65607,10 +65784,10 @@
         <v>53</v>
       </c>
       <c r="E3297" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F3297" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G3297" s="4" t="s">
         <v>84</v>
@@ -65618,10 +65795,10 @@
     </row>
     <row r="3298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3298" s="3">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B3298" s="3">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="C3298" s="9">
         <v>0.36805555555555558</v>
@@ -65630,10 +65807,10 @@
         <v>53</v>
       </c>
       <c r="E3298" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F3298" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G3298" s="4" t="s">
         <v>84</v>
@@ -65641,10 +65818,10 @@
     </row>
     <row r="3299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3299" s="3">
-        <v>46044</v>
+        <v>46051</v>
       </c>
       <c r="B3299" s="3">
-        <v>46044</v>
+        <v>46051</v>
       </c>
       <c r="C3299" s="9">
         <v>0.36805555555555558</v>
@@ -65653,10 +65830,10 @@
         <v>53</v>
       </c>
       <c r="E3299" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F3299" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G3299" s="4" t="s">
         <v>84</v>
@@ -65664,10 +65841,10 @@
     </row>
     <row r="3300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3300" s="3">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="B3300" s="3">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="C3300" s="9">
         <v>0.36805555555555558</v>
@@ -65676,21 +65853,21 @@
         <v>53</v>
       </c>
       <c r="E3300" s="1" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="F3300" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G3300" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3301" s="3">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="B3301" s="3">
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="C3301" s="9">
         <v>0.36805555555555558</v>
@@ -65699,21 +65876,21 @@
         <v>53</v>
       </c>
       <c r="E3301" s="1" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="F3301" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="G3301" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3302" s="3">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="B3302" s="3">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="C3302" s="9">
         <v>0.36805555555555558</v>
@@ -65722,21 +65899,21 @@
         <v>53</v>
       </c>
       <c r="E3302" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F3302" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G3302" s="4" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3303" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B3303" s="3">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="C3303" s="9">
         <v>0.36805555555555558</v>
@@ -65745,21 +65922,21 @@
         <v>53</v>
       </c>
       <c r="E3303" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="F3303" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="G3303" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3304" spans="1:7" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3304" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3304" s="3">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="B3304" s="3">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="C3304" s="9">
         <v>0.36805555555555558</v>
@@ -65768,21 +65945,21 @@
         <v>53</v>
       </c>
       <c r="E3304" s="1" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F3304" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3304" s="4" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="G3304" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3305" s="3">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="B3305" s="3">
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="C3305" s="9">
         <v>0.36805555555555558</v>
@@ -65791,21 +65968,21 @@
         <v>53</v>
       </c>
       <c r="E3305" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F3305" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G3305" s="4" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3306" s="3">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="B3306" s="3">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="C3306" s="9">
         <v>0.36805555555555558</v>
@@ -65814,21 +65991,21 @@
         <v>53</v>
       </c>
       <c r="E3306" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F3306" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G3306" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3307" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3307" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3307" s="3">
-        <v>46056</v>
+        <v>46063</v>
       </c>
       <c r="B3307" s="3">
-        <v>46056</v>
+        <v>46063</v>
       </c>
       <c r="C3307" s="9">
         <v>0.36805555555555558</v>
@@ -65837,21 +66014,21 @@
         <v>53</v>
       </c>
       <c r="E3307" s="1" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F3307" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3307" s="4" t="s">
-        <v>72</v>
+        <v>57</v>
+      </c>
+      <c r="G3307" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3308" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B3308" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="C3308" s="9">
         <v>0.36805555555555558</v>
@@ -65860,21 +66037,21 @@
         <v>53</v>
       </c>
       <c r="E3308" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F3308" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G3308" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3309" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3309" s="3">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="B3309" s="3">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="C3309" s="9">
         <v>0.36805555555555558</v>
@@ -65883,21 +66060,21 @@
         <v>53</v>
       </c>
       <c r="E3309" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F3309" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3309" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="G3309" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3310" s="3">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="B3310" s="3">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="C3310" s="9">
         <v>0.36805555555555558</v>
@@ -65906,21 +66083,21 @@
         <v>53</v>
       </c>
       <c r="E3310" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F3310" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G3310" s="4" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3311" s="3">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="B3311" s="3">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="C3311" s="9">
         <v>0.36805555555555558</v>
@@ -65929,21 +66106,21 @@
         <v>53</v>
       </c>
       <c r="E3311" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3311" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
+      </c>
+      <c r="F3311" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G3311" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3312" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3312" s="3">
-        <v>46063</v>
+        <v>46073</v>
       </c>
       <c r="B3312" s="3">
-        <v>46063</v>
+        <v>46073</v>
       </c>
       <c r="C3312" s="9">
         <v>0.36805555555555558</v>
@@ -65952,21 +66129,21 @@
         <v>53</v>
       </c>
       <c r="E3312" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F3312" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3312" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="G3312" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3313" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="B3313" s="3">
-        <v>46064</v>
+        <v>46076</v>
       </c>
       <c r="C3313" s="9">
         <v>0.36805555555555558</v>
@@ -65975,10 +66152,10 @@
         <v>53</v>
       </c>
       <c r="E3313" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F3313" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G3313" s="4" t="s">
         <v>33</v>
@@ -65986,10 +66163,10 @@
     </row>
     <row r="3314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3314" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="B3314" s="3">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="C3314" s="9">
         <v>0.36805555555555558</v>
@@ -65998,10 +66175,10 @@
         <v>53</v>
       </c>
       <c r="E3314" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F3314" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G3314" s="4" t="s">
         <v>33</v>
@@ -66009,10 +66186,10 @@
     </row>
     <row r="3315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3315" s="3">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="B3315" s="3">
-        <v>46066</v>
+        <v>46078</v>
       </c>
       <c r="C3315" s="9">
         <v>0.36805555555555558</v>
@@ -66021,10 +66198,10 @@
         <v>53</v>
       </c>
       <c r="E3315" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F3315" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G3315" s="4" t="s">
         <v>33</v>
@@ -66032,10 +66209,10 @@
     </row>
     <row r="3316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3316" s="3">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="B3316" s="3">
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="C3316" s="9">
         <v>0.36805555555555558</v>
@@ -66044,10 +66221,10 @@
         <v>53</v>
       </c>
       <c r="E3316" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3316" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="F3316" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G3316" s="4" t="s">
         <v>33</v>
@@ -66055,10 +66232,10 @@
     </row>
     <row r="3317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3317" s="3">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="B3317" s="3">
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="C3317" s="9">
         <v>0.36805555555555558</v>
@@ -66067,21 +66244,21 @@
         <v>53</v>
       </c>
       <c r="E3317" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F3317" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G3317" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3318" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3318" s="3">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B3318" s="3">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="C3318" s="9">
         <v>0.36805555555555558</v>
@@ -66090,21 +66267,21 @@
         <v>53</v>
       </c>
       <c r="E3318" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F3318" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3318" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3318" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3319" s="3">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B3319" s="3">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="C3319" s="9">
         <v>0.36805555555555558</v>
@@ -66113,21 +66290,21 @@
         <v>53</v>
       </c>
       <c r="E3319" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F3319" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G3319" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3320" s="3">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B3320" s="3">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="C3320" s="9">
         <v>0.36805555555555558</v>
@@ -66136,21 +66313,21 @@
         <v>53</v>
       </c>
       <c r="E3320" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F3320" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G3320" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3321" s="3">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B3321" s="3">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="C3321" s="9">
         <v>0.36805555555555558</v>
@@ -66159,21 +66336,21 @@
         <v>53</v>
       </c>
       <c r="E3321" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F3321" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G3321" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3322" s="3">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B3322" s="3">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="C3322" s="9">
         <v>0.36805555555555558</v>
@@ -66182,21 +66359,21 @@
         <v>53</v>
       </c>
       <c r="E3322" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F3322" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G3322" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3323" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3323" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="B3323" s="3">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="C3323" s="9">
         <v>0.36805555555555558</v>
@@ -66205,21 +66382,21 @@
         <v>53</v>
       </c>
       <c r="E3323" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F3323" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3323" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="G3323" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3324" s="3">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B3324" s="3">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="C3324" s="9">
         <v>0.36805555555555558</v>
@@ -66228,136 +66405,136 @@
         <v>53</v>
       </c>
       <c r="E3324" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3324" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3324" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
+      </c>
+      <c r="F3324" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3324" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3325" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="B3325" s="3">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="C3325" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3325" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3325" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3325" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3325" s="4" t="s">
-        <v>28</v>
+        <v>91</v>
+      </c>
+      <c r="F3325" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3325" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="3326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3326" s="3">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="B3326" s="3">
-        <v>46087</v>
+        <v>46094</v>
       </c>
       <c r="C3326" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3326" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3326" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3326" s="1" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="F3326" t="s">
+        <v>88</v>
       </c>
       <c r="G3326" s="4" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3327" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="B3327" s="3">
-        <v>46090</v>
+        <v>46097</v>
       </c>
       <c r="C3327" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3327" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3327" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3327" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3327" s="4" t="s">
-        <v>23</v>
+        <v>87</v>
+      </c>
+      <c r="F3327" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3327" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3328" s="3">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="B3328" s="3">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="C3328" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3328" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3328" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3328" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3328" s="4" t="s">
-        <v>23</v>
+        <v>83</v>
+      </c>
+      <c r="F3328" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3328" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3329" s="3">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B3329" s="3">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="C3329" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3329" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E3329" s="1" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="F3329" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="G3329" s="1" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3330" s="3">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="B3330" s="3">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="C3330" s="9">
         <v>0.36805555555555602</v>
@@ -66366,21 +66543,21 @@
         <v>80</v>
       </c>
       <c r="E3330" s="1" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="F3330" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G3330" s="1" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3331" s="3">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="B3331" s="3">
-        <v>46094</v>
+        <v>46101</v>
       </c>
       <c r="C3331" s="9">
         <v>0.36805555555555602</v>
@@ -66389,59 +66566,13 @@
         <v>80</v>
       </c>
       <c r="E3331" s="1" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="F3331" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3331" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3332" s="3">
-        <v>46097</v>
-      </c>
-      <c r="B3332" s="3">
-        <v>46097</v>
-      </c>
-      <c r="C3332" s="9">
-        <v>0.36805555555555602</v>
-      </c>
-      <c r="D3332" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3332" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3332" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3332" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3333" s="3">
-        <v>46098</v>
-      </c>
-      <c r="B3333" s="3">
-        <v>46098</v>
-      </c>
-      <c r="C3333" s="9">
-        <v>0.36805555555555602</v>
-      </c>
-      <c r="D3333" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3333" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3333" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3333" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
+      </c>
+      <c r="G3331" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7794D7FF-CCA6-4B60-B87C-713ED967465E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8A2502-A7E8-4EA2-B26D-645F67D509A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3561" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="180">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -23019,6 +23019,12 @@
   </si>
   <si>
     <t>[달러/원 환율] 1,500원 부근 개장, 중동 소식과 국제유가에 밀접 연동 전일 달러/원 환율은 유가 상승세 진정 및 미 달러화 약세 영향에 1,492원으로 하락 개장. 이후 일시적으로 낙폭 확대해 1,487원까지 하락했으나, 중동 불안 지속에 따른 위험회피심리에 저가 매수 유입. 이내 1,490원대에 재진입하며 낙폭을 지속적 반납, 전일 종가 대비 0.4원 하락한 1,500.6원에 정규장 마감. 야간장에서는 미국 지상군 투입 가능성 등 위험회피심리와 달러화 강세에 1,504.7원으로 상승 마감. 역외 NDF 환율은 5.40원 상승한 1,504.60원에 최종 호가 금일 달러/원 환율은 주말간 강 달러 및 역외 거래 감안해 1,500원 부근 개장 예상. 미국의 이란에 대한 지상군 투입 가능성 불거지며 전쟁 장기화 조짐. 이에 국제유가 역시 재차 뛰며, 원화도 약세 압력 받는 중. 다만 이란 대통령의 호르무즈 해협 개방 선언 이후 장중 유가 추이 주목. 유가 상승 진정 시, 원화 약세 압력도 다소 완화. 한편 1,500원 위에서 적극 출회되는 수출 네고 물량은 상방을 일부 제한할 것으로 예상 [글로벌 동향] 미국의 지상군 투입 가능성, 국제유가 급등에 달러화 강세 전일 미 달러화는 미국의 지상군 투입 가능성과 국제유가 재급등에 강세 전환. 주요 6개국 통화로 구성될 달러화 지수는 0.30% 상승한 99.50pt 기록. 일부 외신 보도에 따르면, 미국이 이란에 해병대를 투입할 가능성 제기. 투입될 해병대원은 오키나와에 주둔한 2천 200명, 캘리포니아 기지 소속 2천 200~2천500명 등 최대 4천 700명. 이로 인한 중동 전황 고조 우려에 국제유가는 재차 급등. WTI 국제유가는 전장 대비 2.27% 상승한 배럴당 98.32달러에 거래. 미 국채금리는 유가 등 공급측 인플레이션 압력 우려에 큰 폭으로 상승. 2년물, 10년물 국채금리는 각각 10.9bp, 13.1bp 급등. FedWatch에서는 연내 금리 동결 확률이 80% 이상으로 우세. 금리 인하 시점은 내년 9월로 지연. 오히려 이제는 금리 인상에 대한 기대가 점차 생겨나는 상황. 뉴욕증시는 유가 충격 및 매파 연준 우려 등 위험회피심리 확산에 3대 지수 모두 급락 [마켓 이슈] 한국 원화는 유가 변동에 민감 반응, 금주도 중동 전황이 관건 이란 전쟁이 벌써 4주차에 접어든 가운데, 국제유가가 급등락하고 각국의 환율 역시 유가 변동에 따라 등락 거듭. 특히 그중에서도 한국 같이 원유 수입에 크게 의존하는 국가의 통화 가치가 유가 변동에 유독 민감하게 반응. 현재 미국의 이란에 대한 지상군 투입 가능성 등 전황이 길어지는 상황. 이로 인해 고유가 흐름 역시 장기화될 가능성 커지는 상황. 이에 따른 글로벌 물가상승 등 경제 파급 효과 및 한국 외환시장 수급 환경 변화 가능성에 주목할 필요. 시장은 고유가 장기화로 인한 주요국 중앙은행들의 금리 인상 가능성을 서서히 반영 중. 이로 인한 글로벌 고금리는 시장의 위험회피심리 자극 요인. 또한 고유가의 장기화는 국내 외환시장에서 달러 수요 증가 요인. 원유 수입 비중이 높은 우리나라 경제 특성 상, 국제유가 상승은 수입액 증가로 이어질 것이기 때문. 이는 다른 조건이 일정할 때 환율 상승 요인임 (수입=달러 수요)</t>
+  </si>
+  <si>
+    <t>트럼프 한 마디에 출렁이는 환율 [금일 달러/원 환율 1,480~1,492원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 1,480원대로 갭 하락 개장 예상, 수급도 원화에 우호적 전일 달러/원 환율은 미국의 이란에 대한 지상군 투입 가능성 등 전쟁 장기화 조짐에 1,504원으로 개장. 이후 유가증권시장에서 매도 사이드카 발동 등 투심 악화로 인해 달러/원은 1,512원까지 추가 상승. 오후장에서는 분기말 수출 네고에도 불구하고, 안전자산 선호에 따른 달러 수요 증가에 상승 폭 확대, 전일 종가 대비 16.7원 상승한 1,517.3원에 정규장 마감. 야간장에서는 트럼프의 이란 공격 철회에 1,486.7원으로 하락 마감. 역외 NDF 환율은 30.45원 하락한 1,485.70원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,480원대로 급락 개장 예상. 트럼프 대통령의 이란 공격 철회 소식에 유가 급락, 원화에 긍정적으로 작용. 더불어 분기말 수출 네고 물량 출회가 기대된다는 점에서 원화는 더욱 강세 압력을 받을 전망. 다만 급락에 따른 저가 매수가 하단 지지할 것으로 예상. 금일 환율은 하방이 우세한 가운데, 중동 관련 추가 소식에 민감하게 반응할 전망 [글로벌 동향] 트럼프의 이란 공격 철회, 달러 약세 전환과 위험선호 회복 전일 미 달러화는 트럼프 대통령의 이란 공격 철회 소식에 약세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.36% 하락한 99.14pt 기록. 당초 트럼프 대통령은 이란에 호르무즈 해협 개방을 요구하며 최후통첩 선언. 트럼프는 이란이 합의를 원하고 있고, 이에 따라 이란 에너지 시설에 대한 공격을 5일 동안 유예할 것이라고 발언. 트럼프는 실제로 이란의 최고위급 인사와 협상을 진행 중이라고 언급. 이에 대해 이란은 미국과 아무런 합의가 없었다고 응답. 트럼프 발언으로 에너지 대란 우려가 완화되며 국제유가 급락. WTI 가격은 전장 대비 10.36% 급락해 배럴당 88.13달러에 거래. 미 국채금리논 유가 급락에 따른 인플레 우려 진정에 장단기물 모두 하락. 뉴욕증시는 위험선호심리가 회복되며 3대 지수 모두 1% 이상 급등 마감. 한편 메리 데일리 샌프란시스코 연은 총재는 이란 전쟁에 따른 불확실성이 큰 상황이라고 지적 [마켓 이슈] 달러/원 환율 역사적 고점 구간 진입, 추가 상승 여력 고민 필요 3월 23일 달러/원 환율은 장중 1,518.4원까지 상승. 월중 고가 기준 역사상 8번째로 높은 수준. 97~98년 외환위기, 08~09년 금융위기 이후 처음으로 1,500원대 진입. 최근 환율 상승은 이란 전쟁 장기화 및 고유가 지속, 투자 심리 악화에 따른 안전자산 선호에 기인. 즉 전쟁 종료와 유가 안정, 이로 인한 투심 회복까지 동반된다면 환율은 하락 전환 가능. 하지만 현재 전쟁 장기화을 조짐 고려하면, 달러/원 하락 전환보다는 추가 상승 여력을 고민할 필요. 환율 고점 판단의 기준은 다양하나, 지금처럼 상황이 복잡할수록 더욱 단순하게 판단할 필요. 현재 달러/원이 1,500원이라는 강한 심리적 저항선 돌파, 시장은 자연스레 전고점을 앞으로의 상단으로 염두할 듯. 이를 감안하면, 다음 상단은 1,520원대 (08년 11월)→1,540원대 (09년 2월)→1,590원대 (09년 3월) 순으로 높아질 듯. 1,590원을 돌파할 경우 다음 상단은 외환위기 당시로 이동</t>
   </si>
 </sst>
 </file>
@@ -23450,7 +23456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3327"/>
+  <dimension ref="A1:G3328"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -73968,6 +73974,29 @@
         <v>176</v>
       </c>
       <c r="G3327" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3328" s="3">
+        <v>46105</v>
+      </c>
+      <c r="B3328" s="3">
+        <v>46105</v>
+      </c>
+      <c r="C3328" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3328" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3328" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3328" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3328" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\market\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8A2502-A7E8-4EA2-B26D-645F67D509A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353A830F-8548-4D4B-A789-3EB69C9302E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="USDKRW" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="194">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -15363,9 +15366,6 @@
   <si>
     <t>Daily</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://obank.kbstar.com/quics?page=C101425#loading</t>
   </si>
   <si>
     <t>• 달러/원 환율은 전일 대비 13.70 원 하락한 1,194.60 원으로 마감. • 달러/원 환율은 역외시장을 반영하여 전일 대비 5.80 원 하락한 1,202.50 원에 출발. 미국 연방준비제도(Fed) 위원들의 발언이 그다지 금리인상에 무게를 싣지 않으면서 달러 매도가 우위를 보였고, 1,200 원선 부근에서 지지 되는 듯 하였으나 달러/위안 환율이 상승폭을 줄이면서 달러/원 환율은 1,200 원선 밑으로 하락폭을 키우며 전일 대비 13.70 원 하락한 1,194.60 원으로 마감. 금일예상 • 역외 NDF 시장은 1201.50 원 (전 거래일 종가대비 6.85 원 상승) 마감. • 금일 달러/원 환율은 밤사이 뛰어오른 달러/위안 환율에 연동해 상승 출발 예상. 다만 도널드 트럼프 대통령 당선인의 기자회견에서 세부 정책 내용을 확인하고 가자는 심리로 관망세 예상되며, 최근의 변동성에 대한 부담 및 관망세에 따른 포지션 정리성 매도 물량으로 인해 상승은 제한 될 것으로 예상. 예상범위 달러/원: 1,195~1,210 원 엔/원: 1,028~1,047 원 유로/원: 1,259~1,278 원</t>
@@ -23026,6 +23026,52 @@
   <si>
     <t>[달러/원 환율] 1,480원대로 갭 하락 개장 예상, 수급도 원화에 우호적 전일 달러/원 환율은 미국의 이란에 대한 지상군 투입 가능성 등 전쟁 장기화 조짐에 1,504원으로 개장. 이후 유가증권시장에서 매도 사이드카 발동 등 투심 악화로 인해 달러/원은 1,512원까지 추가 상승. 오후장에서는 분기말 수출 네고에도 불구하고, 안전자산 선호에 따른 달러 수요 증가에 상승 폭 확대, 전일 종가 대비 16.7원 상승한 1,517.3원에 정규장 마감. 야간장에서는 트럼프의 이란 공격 철회에 1,486.7원으로 하락 마감. 역외 NDF 환율은 30.45원 하락한 1,485.70원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,480원대로 급락 개장 예상. 트럼프 대통령의 이란 공격 철회 소식에 유가 급락, 원화에 긍정적으로 작용. 더불어 분기말 수출 네고 물량 출회가 기대된다는 점에서 원화는 더욱 강세 압력을 받을 전망. 다만 급락에 따른 저가 매수가 하단 지지할 것으로 예상. 금일 환율은 하방이 우세한 가운데, 중동 관련 추가 소식에 민감하게 반응할 전망 [글로벌 동향] 트럼프의 이란 공격 철회, 달러 약세 전환과 위험선호 회복 전일 미 달러화는 트럼프 대통령의 이란 공격 철회 소식에 약세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.36% 하락한 99.14pt 기록. 당초 트럼프 대통령은 이란에 호르무즈 해협 개방을 요구하며 최후통첩 선언. 트럼프는 이란이 합의를 원하고 있고, 이에 따라 이란 에너지 시설에 대한 공격을 5일 동안 유예할 것이라고 발언. 트럼프는 실제로 이란의 최고위급 인사와 협상을 진행 중이라고 언급. 이에 대해 이란은 미국과 아무런 합의가 없었다고 응답. 트럼프 발언으로 에너지 대란 우려가 완화되며 국제유가 급락. WTI 가격은 전장 대비 10.36% 급락해 배럴당 88.13달러에 거래. 미 국채금리논 유가 급락에 따른 인플레 우려 진정에 장단기물 모두 하락. 뉴욕증시는 위험선호심리가 회복되며 3대 지수 모두 1% 이상 급등 마감. 한편 메리 데일리 샌프란시스코 연은 총재는 이란 전쟁에 따른 불확실성이 큰 상황이라고 지적 [마켓 이슈] 달러/원 환율 역사적 고점 구간 진입, 추가 상승 여력 고민 필요 3월 23일 달러/원 환율은 장중 1,518.4원까지 상승. 월중 고가 기준 역사상 8번째로 높은 수준. 97~98년 외환위기, 08~09년 금융위기 이후 처음으로 1,500원대 진입. 최근 환율 상승은 이란 전쟁 장기화 및 고유가 지속, 투자 심리 악화에 따른 안전자산 선호에 기인. 즉 전쟁 종료와 유가 안정, 이로 인한 투심 회복까지 동반된다면 환율은 하락 전환 가능. 하지만 현재 전쟁 장기화을 조짐 고려하면, 달러/원 하락 전환보다는 추가 상승 여력을 고민할 필요. 환율 고점 판단의 기준은 다양하나, 지금처럼 상황이 복잡할수록 더욱 단순하게 판단할 필요. 현재 달러/원이 1,500원이라는 강한 심리적 저항선 돌파, 시장은 자연스레 전고점을 앞으로의 상단으로 염두할 듯. 이를 감안하면, 다음 상단은 1,520원대 (08년 11월)→1,540원대 (09년 2월)→1,590원대 (09년 3월) 순으로 높아질 듯. 1,590원을 돌파할 경우 다음 상단은 외환위기 당시로 이동</t>
   </si>
+  <si>
+    <t>https://obank.kbstar.com/quics?page=C101425#loading</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TACO는 과학이다 [금일 달러/원 환율 1,490~1,500원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 협상 분위기 vs. 군사적 긴장, 1,490원대에서 혼조 예상 전일 달러/원 환율은 트럼프의 이란 에너지 시설 공격 철회 소식에 따른 달러 약세 및 위험선호심리 회복에 1,490원으로 갭 하락 개장. 이후 외국인의 국내주식 순매도 등 수급 부담에 재차 1,500원대 진입했으나, 분기말 수출 네고 출회에 다시 낙폭 확대. 이후 1,490원대에서 혼조, 전일 종가 대비 22.1원 하락한 1,495.2원에 정규장 마감. 야간장에서는 중동 지역 지정학 불확실성 지속으로 인해 1,499.9원으로 상승 마감. 역외 NDF 환율은 0.15원 상승한 1,493.90원에 최종 호가 금일 달러/원 환율은 간밤 달러 반등과 역외 거래 감안해 보합권 개장 예상. 미·이란 협상 분위기 속 군사적 긴장감 이어지며 시장은 혼란스러운 모습. 이에 달러/원 역시 뚜렷한 방향성 잡지 못하고 1,490원대 혼조 예상. 1,500원 부근에서는 당국 개입과 네고 출회가 상방을 제한. 동시에 고유가 지속 및 투심 위축 등이 원화 가치 회복을 제약. 금일 환율 역시 중동 관련 소식과 유가에 민감하게 반응할 전망 [글로벌 동향] 미국의 대이란 협상 제안에도 군사적 긴장에 달러 강 보합 전일 미 달러화는 미·이란 협상 분위기 속 잔존한 군사적 긴장감에 강 보합세. 주요 6개국 통화로 구성된 달러화 지수는 0.09% 상승한 99.23pt 기록. 트럼프 대통령은 이란과 협상을 진행 중이며, 이란이 미국에 큰 선물을 줬다고 언급. 미국은 이란에 1개월 휴전을 제안하고 15개의 협상 조항을 전달. 협상안의 골자는 '핵 포기', '역내 대리 세력 지원 중단', '미사일 사용 제한'. 더불어 미국은 이란에 26일 고위급 회담을 제안. 하지만 이란은 이 같은 협상안에 대해 아직 무응답. 협상과는 별개로 미·이란의 군사적 긴장감은 한층 더 고조. 외신 보도에 따르면, 미국은 이란에 약 3천명 규모의 공수부대원 파병 계획 중. 이란은 혁명수비대 출신 강경파 졸가르드를 안보 수장으로 임명. 이에 WTI 국제유가는 0.33% 상승한 배럴당 88.42달러에 거래. 미 국채금리는 장단기물 대체로 상승, 뉴욕증시는 투심 위축에 3대 지수 모두 하락 마감 [마켓 이슈] TACO 패턴: 위협 → 시장 충격 → TACO 발동 (평균 2~3일) 2025~2026년 트럼프 정책 패턴 보면 공통점 존재. 강한 위협 이후 시장이 흔들리면 한발 물러서는, 이른바 TACO 반복. 대표 사례는 2025년 4월 상호관세 유예, 최근은 이란 에너지 인프라 공격 연기. 지금까지 사례 보면 TACO 발동까지 평균 7.6일 소요. 다만 미중 관세 사례 제외 시 평균 2.8일 소요, 즉 TACO는 사실상 단기 이벤트 성격. TACO 발동 트리거는 '증시 급락과 장기금리 급등' 같은 시장 충격이 발생하는 경우. 한편 TACO는 달러/원의 상단을 꺾는 재료. 관세 TACO는 달러 강세와 위험회피를 완화시켜 환율 하락으로 연결. 중동 TACO 역시 유가 상승세 진정 등을 통해 달러/원 하락에 일조. 정리하면, '강한 위협→시장 충격→TACO 발동→환율 하락' 패턴 반복. 즉 TACO는 급등한 환율의 상단을 제어하는 장치이자, 단기 하방 변동성 확대 요인. 따라서 앞으로도 TACO 발생 시 빠른 되돌림 가능성에 대비한 포지션 접근 필요</t>
+  </si>
+  <si>
+    <t>길어진 전쟁, 익숙한 1,500원 [금일 달러/원 환율 1,495~1,510원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험회피, 고유가, 역외 롱 심리에 1,500원 부근 혼조세 전일 달러/원 환율은 미국·이란 협상 분위기 반영하며 소폭 하락 개장했으나 낙폭은 제한적. 미국의 지상군 투입 가능성 등 불확실성에 저가 매수세가 유입되고 외국인은 국내주식을 1조원 가량 순매도. 오후장에서 환율은 낙폭을 지속 축소하다가 상승으로 전환, 전일 종가 대비 4.5원 상승한 1,499.7원에 정규장 마감. 야간장에서는 중동 불확실성 및 달러 강세로 인해 1,501.7원으로 상승 마감. 역외 NDF 환율은 6.35원 상승한 1,504.70원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래를 감안해 1,500원 부근 개장 예상. 이란이 미국 협상안을 거부하며 전황 장기화 조짐. 이에 더해 이란이 주변국 공격까지 시사하며 불안감은 더욱 고조. 이에 따른 위험회피심리와 유가 상방 압력이 원화 약세 자극. 더불어 안전자산 선호에 따른 글로벌 달러 강세가 역외 롱 심리를 부추기는 중. 다만 1,500원대에서 적극 출회될 수출 네고 물량이 상방을 일부 제한할 전망 [글로벌 동향] 이란의 협상 거부, 미국과 주변국에 강경 기조, 달러 강세 전일 미 달러화는 이란의 협상 거부 등 중동 불안 지속에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.42% 상승한 99.64pt 기록. 미국은 이란에 1개월 휴전을 제안하고 15개의 협상 조항을 전달했으나, 이란이 거부. 이란 외무장관은 미국과 협상한 적도, 협상할 의사도 없다고 발언. 또한 그는 전쟁 이후 호르무즈 해협에 대한 새로운 통제 체계를 갖게 될 것이라고 첨언. 이란 의회 의장 갈리바프는 미국의 이란 섬 점령 작전에 대해 경고. 그는 섬 점령을 돕는 국가들의 모든 핵심 인프라 시설을 공격할 것이라 선언. 국제유가는 이란의 협상 거부에 낙폭을 상당 부분 되돌림. WTI 유가는 배럴당 90.32달러에 마감했으나, 장중 저점은 86달러. 주요국 중앙은행들은 이란 전쟁의 경제 파급 효과를 우려하는 분위기. ECB 총재는 필요 시 어떤 회의에서든 정책 변경에 나설 수 있다고 발언. BOE 위원은 에너지 인플레이션이 우려된다고 언급 [마켓 이슈] 숫자로 보는 TACO, 누적되는 시장 스트레스와 달러/원 반응 트럼프 강경 발언 이후 시장이 흔들리면, 결국 한발 물러서는 TACO 반복. 이번에는 시장가격이 구체적으로 어느 정도 변동했을 때 TACO가 발동되었는지 숫자로 확인. 주요 TACO 국면 5건을 기준으로 보면, 발동까지 걸린 기간은 평균 3.8일. 그 사이에 S&amp;P500지수는 평균 4.0% 하락, 미 10년물 금리는 평균 13.3bp 상승. TACO 발동 직후 달러/원 환율의 평균 낙폭은 20.3원. 이중에서 가장 변동폭이 컸던 사례는 단연 상호관세 이벤트. 당시 S&amp;P500지수는 14.7% 급락하고 미 10년물 금리는 38.1bp 급등. 트럼프 대통령도 결국 7일 만에 90일 동안 관세 유예 선언. 직후에 달러/원 환율 낙폭은 최대 40.6원까지 확대되며 극심한 변동성 시현. 이를 보면, 일정 수준 이상의 변동성 확대가 TACO 발동을 유도하는 경향. 과거 사례 감안 시, S&amp;P500 하락폭 약 3~5%, 미 10년물 상승폭 +10bp 내외에서 TACO 발동될 가능성 크다는 판단</t>
+  </si>
+  <si>
+    <t>전황 악화일로, 이젠 1,500이 지지선 [금일 달러/원 환율 1,500~1,512원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 시장 혼란 가중, 위험자산 회피 고조에 1,500원대 등락 전일 달러/원 환율은 이란의 미국 협상안 거부 등 전쟁 장기화 조짐에 1,503원으로 상승 개장한 이후 꾸준히 고점을 높여 나감. 국내 증시 부진과 외국인의 주식 순매도 등 수급 부담까지 겹치며 장중 1,509원까지 추가 상승. 이후 1,510원 돌파는 실패, 상승 폭을 축소했으나 1,500원대 등락, 전일 종가 대비 7.3원 상승한 1,507.0원에 정규장 마감. 야간장에서는 중동 불안에 따른 달러 강세에 1,508.0원으로 상승 마감. 역외 NDF 환율은 1.35원 상승한 1,507.10원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 보합권 개장 예상. 트럼프의 군사 위협과 유예가 반복되며 시장 혼란이 가중된 국면. 당장에 시장은 고유가 및 강 달러로 반응하고 있어 달러/원 역시 하단이 막힌 형국. 더군다나 위험회피 고조에 글로벌 증시 역시 부진. 이에 외국인 증시 자금 대거 유출 시 환율 상방 자극될 소지. 다만 당국 개입 시 고점 인식 형성, 고점권에서 네고 출회되며 환율 하락 전환도 가능 [글로벌 동향] 미·이란 군사 충돌 위험에 유가 및 금리 급등, 달러 강세 전일 미 달러화는 트럼프의 이란 공격 위협 등 군사적 긴장 고조에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.31% 상승한 99.95pt 기록. 트럼프 대통령은 이란에 협상안 수용을 촉구하는 동시에 군사 위협도 병행. 당초 미국은 이란에 핵 포기 등의 내용이 담긴 15개 조항 합의안을 제시. 하지만 이란이 이를 거부하며 양국 간 긴장이 더욱 고조. 한편 일부 소식통에 따르면, 미국의 대규모 지상군 투입 가능성이 커졌다고 이스라엘 언론이 보도. 국제유가는 미·이란 군사 충돌 경계에 큰 폭으로 상승. WTI 국제유가는 전장 대비 4.61% 상승해 배럴당 94.48달러에 거래. 미 국채금리 역시 고유가로 인한 인플레 우려 반영하며 장단기물 모두 상승. 뉴욕증시는 전쟁 장기화 등 위험자산 회피에 3대 지수 모두 급락 마감. 이후 트럼프는 이란 에너지 시설 공격을 4월 6일까지 유예 발표 (기존에는 3월 28일까지 유예) [마켓 이슈] 고유가 장기화 → 연준 금리 인상? 이번에는 2022년과 다를까 미국·이란 전쟁 장기화 조짐에 유가 불안 이어지며, 시장은 22년 러시아·우크라니아 전쟁 당시의 인플레이션 재현 가능성 의식하는 분위기. 다만 이번 국면을 22년과 동일 선상에서 보기엔 차이가 분명함. 당시는 팬데믹 이후 수요 회복이 강했고, 여기에 공급 충격까지 겹치며 물가 전반이 빠르게 상승. 반면 지금은 고용이 완만하게 둔화하는 등 미국 내 수요측 압력이 예전만 못한 상황. 샌프란시스코 연은의 PCE 물가 요인분해를 봐도 흐름은 뚜렷. 수요측 인플레이션 압력은 22년 연평균 2.58%p에서 25년 연평균 1.30%p로 하락. 공급 충격은 물가를 자극하기도 하나, 오히려 소비 등 성장에는 부담 주는 성격이 강함. 즉 유가 상승이 공급측 물가압력을 자극할 수는 있어도, 수요측에는 제한적 영향. 이런 환경에서는 연준도 인상 재개보다는 인하 시점을 늦추는 방식으로 대응하는 것이 합리적. 즉 인상까진 아니라는 점에서 달러 강세도 다소 제한될 전망</t>
+  </si>
+  <si>
+    <t>원화 던진 外人, 바닥 굳힌 1,500 [금일 달러/원 환율 1,503~1,514원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 1,510원 부근 개장, 양측 수급 대치에 1,500원대 혼조 전일 달러/원 환율은 미·이란 군사 충돌 위험에 따른 달러 강세에 1,508원으로 상승 개장. 위험자산 회피 심리에 장중 1,512원까지 추가 상승한 이후 당국 개입 경계와 수출 네고 물량 출회에 상승 폭 축소. 하지만 외국인의 국내 주식 3조원 이상 순매도 등 수급 부담에 1,500원 하회는 실패, 전일 종가 대비 1.9원 상승한 1,508.9원에 정규장 마감. 야간장에서는 중동 불안에 따른 달러 강세에 1,511.4원으로 상승 마감. 역외 NDF 환율은 0.50원 하락한 1,507.30원에 최종 호가 금일 달러/원 환율은 주말간 달러 강세와 역외 거래 감안해 1,510원 부근 개장 예상. 미·이란의 해소되지 않는 군사적 긴장이 원화에 지속 부담 주는 국면. 고유가와 투심 악화 역시 원화 약세 압력으로 작용 중. 그간의 외국인 국내 주식 매도분의 달러 환전 규모가 환율 추가 상승 자극할 소지. 다만 당국 미세조정 및 분기말 네고는 상방 일부 제약하는 요소. 금일 환율은 상승 개장 뒤, 양방향 수급 대치에 1,500원대 혼조 예상 [글로벌 동향] 중동 불확실성에 달러화 지수 100pt, WTI 100달러 육박 전일 미 달러화는 중동 지역 전황 불확실성에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.25% 상승한 100.20pt 기록. 이란 혁명수비대는 미국·이스라엘의 동맹국 선박은 해협을 통과할 수 없다고 경고. 혁명수비대는 트럼프 대통령의 호르무즈 해협 개방 발언은 거짓이라고 반박. 이에 중국 소유의 대형 컨테이너선도 해협 통과에 실패. 이 같은 원유 운송 차질에 국제유가는 상승세가 이어지는 중. WTI 국제유가는 전장 대비 5.46% 상승한 배럴당 99.64달러에 거래. 달러당 엔화 환율은 2024년 7월 이후 처음으로 160엔 돌파. 일본 경제의 높은 에너지 수입 의존도가 엔화에 약세 압력으로 작용. 뉴욕 증시는 전쟁 장기화에 따른 위험자산 회피 반영하며 3대 지수 모두 하락세. 기술주인 나스닥 지수는 전일에 무려 2% 이상 급락 마감. 한편 미국 미시간대의 3월 소비자심리지수 최종치는 53.3pt로 전월의 56.6pt를 하회 [마켓 이슈] 이란 전쟁 5주차, 원화 자산 회피 심화에 1,500원대 구간 유지 이란 전쟁이 이제 5주차에 접어 들며 전황이 길어지는 상황. 이로 인해 안전자산 선호 역시 강해지며 달러는 강세인 국면. 반면 글로벌 투자 심리가 위축되며 주식과 원화 등 위험자산에 대한 회피 분위기 확산. 외국인 투자자는 지난 3월 한 달 동안 국내 주식을 무려 30조원 가까이 순매도. 이는 월간 기준 역대 최대치인데, 그만큼 원화 자산에 대한 회피가 상당함을 방증. 주식 매도 자금 상당액이 달러로 환전 시, 달러/원 상방이 더욱 자극될 소지. 4월 외환시장은 전쟁 속 혼란스러운 상황에 변동성이 상당히 클 것으로 예상. 이란의 협상 거부와 미국의 지상군 투입 계획 등 확전 가능성도 배제하기 어려움. 사태 악화 시, 달러/원 환율 상단은 1,540원까지도 열어 둘 필요 (2009년 2월 고점). 반대로 극적으로 협상 타결 시 투심 회복에 1,500원 하회도 충분히 가능. 다만 고유가 부담 누적으로 인해 하단은 지난 3월 하단인 1,455원보다는 높을 전망</t>
+  </si>
+  <si>
+    <t>더 올라간 달러/원의 눈높이 [금일 달러/원 환율 1,510~1,522원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험회피와 수급 부담에 고환율, 당국 미세조정은 경계 전일 달러/원 환율은 지속되는 중동 불안에 1,513원으로 상승 개장. 장초반 분기말 수출 네고에 상승 폭 일부 축소하기도 했으나, 고유가와 위험회피 등 원화 약세 압력 지속되며 1,510원 하회는 실패. 오후장에서는 수급상 달러 수요가 소폭 우위 보이며 상승 폭 확대, 전일 종가 대비 6.8원 상승한 1,515.7원에 정규장 마감. 야간장에서는 안전자산 선호로 인한 달러 강세로 인해 1,518.2원으로 상승 마감. 역외 NDF 환율은 1.15원 상승한 1,515.50원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세와 역외 거래 감안해 1,510원대 중반 개장 예상. 전쟁 장기화 속, 이제는 원자재 공급 충격으로 인한 글로벌 경기둔화 우려까지 부각. 이로 인한 안전자산 선호 (위험자산 회피)가 환율 하단 지지. 다만 외환당국이 상방 변동성 완화 위해 미세조정 나설 가능성 점증. 당국의 1차 사수 라인은 1,520원으로 추정. 시장 참여자들도 이를 의식해 해당 레벨 부근에서는 경계심 커질 것으로 예상 [글로벌 동향] 중동 확전 및 경기둔화 우려에 국채금리 하락, 달러 강세 전일 미 달러화는 중동 불안과 경기둔화 우려에 따른 안전자산 선호에 강세. 주요 6개국 통화로 구성된 달러화 지수는 0.29% 상승한 100.49pt 기록. 미국의 위협과 이란의 주변국 공격이 이어지며 여전히 중동 정세는 혼란. 트럼프는 해협을 개방하지 않을 경우, 이란 에너지 시설을 파괴할 것이라 위협. 그는 군사 작전 종료를 위해 이란 정권과 협의 중이라 밝힘. 이란은 주변국 핵심 알루미늄 공장을 타격하며 군사 충돌 수위가 높아지는 상황. 더불어 후티 반군도 전쟁 참여 의사 밝히며, 홍해 물류 차질 가능성도 부각. 한편 전쟁 장기화에 글로벌 경제의 성장둔화 우려가 확산. 글로벌 주요 국채금리는 물가상승보다 경기둔화 우려 더욱 의식하며 하락. 파월 연준 의장은 공급 충격에 통화정책으로 대응하는 것은 적절치 않다고 발언. 존 윌리엄스 뉴욕 연은 총재는 이란 전쟁 인한 스태그플레이션 위험을 시사 [마켓 이슈] 전쟁이 밀어 올린 비료값, 애그인플레이션 재발 가능성 점증 호르무즈 해협 봉쇄 여파가 원유를 넘어 비료 시장까지 번지는 중. 중동은 질소비료의 핵심 생산지인데, 이 지역 물량 상당수가 호르무즈 해협 통과. 이에 따른 공급 차질이 곧바로 비료 가격 급등으로 연결. 현재 국제 비료 가격은 톤당 780달러로, 지난 2월의 490달러 대비 60% 급등. 문제는 현재 북반구 지역이 봄철 파종기라는 점 (3~4월). 비료 가격 급등은 농업 생산 비용 등 작황 부담으로 이어질 수 있고, 이는 결국 하반기 글로벌 식량 가격 상승 압력을 키울 소지. 이에 따라 2022년 러시아-우크라이나 전쟁 당시 애그플레이션 재발도 우려되는 상황. 이는 글로벌 물가의 상방 압력을 자극하며, 주요국 통화정책 완화 기대를 더 약화시킬 수 있음. 또는 공급 충격으로 인한 경기둔화 우려가 위험자산 회피 분위기를 더욱 부추길 수 있음. 이 경우 외국인 투자자의 한국 주식 등 원화 자산 매도 압력이 가중, 달러/원의 추가 상방이 자극될 수 있음</t>
+  </si>
+  <si>
+    <t>만우절인데... 종전각? [금일 달러/원 환율 1,499~1,514원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 종전 기대에 갭 하락, 위험선호 회복 등에 추가 하락 예상 전일 달러/원 환율은 글로벌 경기둔화 우려로 인한 달러 강세에 1,519원으로 상승 개장한 이후 위험자산 회피 분위기에 상승 폭 확대. 외국인의 국내 주식 순매도액이 3조원에 달하는 등 수급상 달러 수요가 우위 보이며 오후장에서 1,536원까지 급등. 이후 박스권 흐름 보이며, 전일 종가 대비 14.4원 상승한 1,530.1원에 정규장 마감. 야간장에서는 종전 기대로 인한 달러 약세에 1,517.0원으로 하락 마감. 역외 NDF 환율은 23.45원 하락한 1,505.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 갭 하락 개장 예상. 미국과 이란의 협상 분위기가 불거지며 강 달러 압력 약화. 이에 전날 환율 급등을 유발했던 역외 롱 플레이도 다소 누그러질 전망. 더불어 뉴욕증시가 회복하는 등 위험자산 선호 심리에 국내증시에도 훈풍. 이에 그간 지속된 외인 주식 순매도가 멈추며 환율 추가 하락에 기여 예상. 다만 저가 매수 유입으로 변동성 커질 가능성에 유의할 필요 [글로벌 동향] 미·이란 종전 기대에 달러 약세, 위험자산 선호 심리 회복 전일 미 달러화는 이란과 미국 정상의 전쟁 종료 시사 발언에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.59% 하락한 99.89pt 기록. 이란의 페제시키안 대통령은 전쟁을 끝낼 준비가 되어있다고 발언. 다만 그는 이란이 더 이상 공격 받지 않는다는 보장이 필요하다고 덧붙임. 미국 트럼프 대통령은 이란과의 협상이 잘 이루어지고 있다고 언급. 그는 앞으로 2~3주 안에 철수할 것이라며, 종전 기대를 자극. 하지만 이 같은 협상 분위기 속, 미국의 3번째 항공모함이 중동으로 출발. 협상이 결렬될 경우 확전을 대응하는 옵션 고려 중인 것으로 추정. 시장은 전반적으로 종전 기대 반영하는 등 투자 심리가 회복. 미 국채금리는 장단기물 모두 하락, 뉴욕증시는 3대 지수 모두 급등. 특히 기술주 위주의 나스닥 지수는 전장 대비 4% 가까이 폭등하며 마감. WTI 국제유가는 전장 대비 1.46% 하락한 배럴당 101.38달러에 거래 [마켓 이슈] 유가 충격에 더 취약한 미국 밖 경제, 전쟁의 승자는 결국 달러 이란 전쟁 및 고유가 장기화로 인해 글로벌 공급 충격이 불가피한 국면. 외환시장에서 관건은 유가 상승 그 자체보다, 어느 경제가 에너지 충격에 더 취약한가에 있음. 이를 설명하는 직관적인 틀은 '달러 스마일 이론'. 해당 이론은 미국 경제가 매우 강하거나, 반대로 글로벌 경기 불안이 커질 때 달러가 강해진다는 논리. 현재 국면은 전자보다는 후자에 가까운 상황. 미국도 고유가 부담에서 자유롭지 않지만, 에너지 수입 의존도가 높은 국가들은 교역조건 악화와 성장둔화 압력을 더 크게 받을 가능성 높음. 지난 3월 국제유가 급등기에도 에너지 수입 의존도가 높은 국가에서 통화 약세가 부각. 한국은 에너지 수입 의존도 85%, 원화 절하율은 3%에 육박. 반면 에너지 순수출국 통화의 절하 폭은 상대적으로 제한됨. 결국 고유가는 미국 경제보다, 미국 외 경제권에 더 큰 둔화 압력 가할 전망. 미 달러는 미국 밖 경제의 상대적 취약성 반영해 강세 우위 예상</t>
+  </si>
+  <si>
+    <t>전쟁은 끝으로, 환율은 밑으로 [금일 달러/원 환율 1,505~1,520원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 금일 오전 10시 트럼프 담화문 주목, 이후 방향성 모색 전일 달러/원 환율은 미국과 이란 종전 기대에 따른 달러 강세 압력 약화와 위험자산 선호 심리 회복에 1,508원으로 갭 하락 개장. 이후 저가 매수 유입되며 1,510원 부근 등락하였으나, 국제유가 하락에 더해 KOSPI 8% 폭등 등 투자 심리 회복이 지속되며 1,500원대 초반까지 하락, 전일 종가 대비 28.8원 하락한 1,501.3원에 정규장 마감. 야간장에서는 미국 경제지표 호조와 저가 매수 유입으로 1,513.3원으로 상승 마감. 역외 NDF 환율은 15.75원 상승한 1,515.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 1,510원대로 상승 개장 예상. 금일 오전 10시 트럼프 대국민 담화 앞두고 시장 경계 고조. 담화 발표 전까지 포지션 플레이 제한되며 방향성도 부재할 전망. 담화문에서 종전 향한 유화적 메세지 나올 경우 위험자산 선호 심리 더욱 확산. 이 경우 국내 증시는 물론 원화 자산 전반이 강세 압력 받을 전망. 이에 달러/원 역시 1,500원대 초반까지 상승 폭 축소 예상 [글로벌 동향] 미국 고용 등 경제는 양호, 미·이란 종전 기대에 달러 약세 전일 미 달러화는 미국 경제지표 호조 속, 이란 종전 기대 이어지며 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.32% 하락한 99.57pt 기록. 전날 발표된 미국 지표는 시장 예상보다 대체로 양호. ADP 3월 민간고용은 전월대비 6.2만명 증가하며 예상치 (+4.0만명) 상회. 2월 소매판매는 전월대비 0.6% 증가하며 예상 (+0.5%)과 전월 (- 0.1%)을 모두 상회. 마지막으로 ISM 3월 제조업 지수는 52.7pt로 예상치 (52.3pt) 상회. 특히 제조업 가격지수는 78.3pt로 7.8pt 급등하며 물가상승 우려 점증. 하지만 시장은 미국의 양호한 경제지표보다는 종전 여부에 주목. 이란 대통령은 미국인들에게 보낸 서신을 통해 종전 의사를 전달. 트럼프 대통령은 금일 오진 10시 무렵 이란 전쟁 관련 대국민 담화 발표 예정. 미 국채금리는 관망세 보이며 장단기물 대체로 보합권 등락. WTI 국제유가는 전일대비 1.24% 하락한 배럴당 100.12달러에 거래 [마켓 이슈] 정부의 외환시장 안정 노력, 전황 진정 시 환율 하락 전환 기대 이란 전쟁과 유가 급등에 달러/원의 상방 변동성 역시 커진 국면. 전쟁이 길어질수록 위험회피와 에너지 공급 차질이 원화에 계속 부담으로 작용. 이런 상황 속에서 정부는 외환시장 안정과 달러수급 개선 위한 대응에 총력. 최근 국회 통과된 '환율안정 3법'은 민간의 달러수요 완화 및 해외자금 국내 환류 유도에 방점. '국민연금 뉴프레임워크'는 해외투자 비중 조정과 외화채 발행을 통해 신규 달러수요를 줄이고, 환헤지 확대 통해 필요시 환율 안정에 기여할 수 있음. '외환시장 선진화'는 원화 거래 접근성 및 유동성 개선을 통해 환율 변동성 완화에 기여할 전망. 즉, 현재 정부의 환율 정책 방향은 단순 개입보다는 달러수급 구조 개선에 초점. 당장의 환율 향방에는 이란 전쟁 양상과 유가 추이가 가장 중요. 하지만 향후 전황이 진정되고 유가도 안정될 경우, 해당 정책 요인 효과까지 겹치며 달러/원 하락 전환 압력이 커질 것으로 예상</t>
+  </si>
 </sst>
 </file>
 
@@ -23035,7 +23081,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -23082,6 +23128,14 @@
       <name val="Verdana"/>
       <family val="3"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -23100,12 +23154,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -23142,9 +23199,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -23456,7 +23517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3328"/>
+  <dimension ref="A1:G3335"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -23626,7 +23687,7 @@
         <v>53</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>15</v>
@@ -70536,13 +70597,13 @@
         <v>53</v>
       </c>
       <c r="E3135" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3135" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G3135" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3136" spans="1:7" x14ac:dyDescent="0.25">
@@ -70559,13 +70620,13 @@
         <v>53</v>
       </c>
       <c r="E3136" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F3136" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G3136" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3137" spans="1:7" x14ac:dyDescent="0.25">
@@ -70582,13 +70643,13 @@
         <v>53</v>
       </c>
       <c r="E3137" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F3137" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G3137" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3138" spans="1:7" x14ac:dyDescent="0.25">
@@ -70605,13 +70666,13 @@
         <v>53</v>
       </c>
       <c r="E3138" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F3138" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G3138" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3139" spans="1:7" x14ac:dyDescent="0.25">
@@ -70628,13 +70689,13 @@
         <v>53</v>
       </c>
       <c r="E3139" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F3139" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G3139" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3140" spans="1:7" x14ac:dyDescent="0.25">
@@ -70651,13 +70712,13 @@
         <v>53</v>
       </c>
       <c r="E3140" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F3140" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G3140" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3141" spans="1:7" x14ac:dyDescent="0.25">
@@ -70674,13 +70735,13 @@
         <v>53</v>
       </c>
       <c r="E3141" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F3141" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G3141" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3142" spans="1:7" x14ac:dyDescent="0.25">
@@ -70697,13 +70758,13 @@
         <v>53</v>
       </c>
       <c r="E3142" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F3142" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G3142" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3143" spans="1:7" x14ac:dyDescent="0.25">
@@ -70720,13 +70781,13 @@
         <v>53</v>
       </c>
       <c r="E3143" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F3143" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G3143" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3144" spans="1:7" x14ac:dyDescent="0.25">
@@ -70743,13 +70804,13 @@
         <v>53</v>
       </c>
       <c r="E3144" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F3144" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3144" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="G3144" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3145" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
@@ -72611,13 +72672,13 @@
         <v>53</v>
       </c>
       <c r="E3268" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F3268" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G3268" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3269" spans="1:7" x14ac:dyDescent="0.25">
@@ -72634,13 +72695,13 @@
         <v>53</v>
       </c>
       <c r="E3269" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F3269" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G3269" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3270" spans="1:7" x14ac:dyDescent="0.25">
@@ -72657,13 +72718,13 @@
         <v>53</v>
       </c>
       <c r="E3270" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F3270" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G3270" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3271" spans="1:7" x14ac:dyDescent="0.25">
@@ -72680,13 +72741,13 @@
         <v>53</v>
       </c>
       <c r="E3271" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3271" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G3271" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3272" spans="1:7" x14ac:dyDescent="0.25">
@@ -72703,13 +72764,13 @@
         <v>53</v>
       </c>
       <c r="E3272" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F3272" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G3272" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3273" spans="1:7" x14ac:dyDescent="0.25">
@@ -72726,13 +72787,13 @@
         <v>53</v>
       </c>
       <c r="E3273" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F3273" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3273" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="G3273" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3274" spans="1:7" x14ac:dyDescent="0.25">
@@ -72749,13 +72810,13 @@
         <v>53</v>
       </c>
       <c r="E3274" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F3274" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3274" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3275" spans="1:7" x14ac:dyDescent="0.25">
@@ -72772,13 +72833,13 @@
         <v>53</v>
       </c>
       <c r="E3275" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F3275" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3275" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3276" spans="1:7" x14ac:dyDescent="0.25">
@@ -72795,13 +72856,13 @@
         <v>53</v>
       </c>
       <c r="E3276" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F3276" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G3276" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3277" spans="1:7" x14ac:dyDescent="0.25">
@@ -72818,13 +72879,13 @@
         <v>53</v>
       </c>
       <c r="E3277" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3277" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G3277" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3278" spans="1:7" x14ac:dyDescent="0.25">
@@ -72841,13 +72902,13 @@
         <v>53</v>
       </c>
       <c r="E3278" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F3278" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G3278" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3279" spans="1:7" x14ac:dyDescent="0.25">
@@ -72864,13 +72925,13 @@
         <v>53</v>
       </c>
       <c r="E3279" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F3279" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G3279" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3280" spans="1:7" x14ac:dyDescent="0.25">
@@ -72887,13 +72948,13 @@
         <v>53</v>
       </c>
       <c r="E3280" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F3280" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G3280" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3281" spans="1:7" x14ac:dyDescent="0.25">
@@ -72910,13 +72971,13 @@
         <v>53</v>
       </c>
       <c r="E3281" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3281" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G3281" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3282" spans="1:7" x14ac:dyDescent="0.25">
@@ -72933,13 +72994,13 @@
         <v>53</v>
       </c>
       <c r="E3282" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F3282" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G3282" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3283" spans="1:7" x14ac:dyDescent="0.25">
@@ -72956,13 +73017,13 @@
         <v>53</v>
       </c>
       <c r="E3283" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3283" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G3283" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3284" spans="1:7" x14ac:dyDescent="0.25">
@@ -72979,13 +73040,13 @@
         <v>53</v>
       </c>
       <c r="E3284" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3284" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F3284" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="G3284" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3285" spans="1:7" x14ac:dyDescent="0.25">
@@ -73002,13 +73063,13 @@
         <v>53</v>
       </c>
       <c r="E3285" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3285" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3285" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3286" spans="1:7" x14ac:dyDescent="0.25">
@@ -73025,13 +73086,13 @@
         <v>53</v>
       </c>
       <c r="E3286" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3286" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3286" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3287" spans="1:7" x14ac:dyDescent="0.25">
@@ -73048,13 +73109,13 @@
         <v>53</v>
       </c>
       <c r="E3287" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F3287" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3287" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3288" spans="1:7" x14ac:dyDescent="0.25">
@@ -73071,13 +73132,13 @@
         <v>53</v>
       </c>
       <c r="E3288" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3288" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3288" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3289" spans="1:7" x14ac:dyDescent="0.25">
@@ -73094,13 +73155,13 @@
         <v>53</v>
       </c>
       <c r="E3289" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F3289" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G3289" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3290" spans="1:7" x14ac:dyDescent="0.25">
@@ -73117,13 +73178,13 @@
         <v>53</v>
       </c>
       <c r="E3290" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F3290" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3290" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3291" spans="1:7" x14ac:dyDescent="0.25">
@@ -73140,13 +73201,13 @@
         <v>53</v>
       </c>
       <c r="E3291" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3291" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3291" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3292" spans="1:7" x14ac:dyDescent="0.25">
@@ -73163,13 +73224,13 @@
         <v>53</v>
       </c>
       <c r="E3292" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3292" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F3292" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="G3292" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3293" spans="1:7" x14ac:dyDescent="0.25">
@@ -73186,13 +73247,13 @@
         <v>53</v>
       </c>
       <c r="E3293" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3293" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3293" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3294" spans="1:7" x14ac:dyDescent="0.25">
@@ -73209,13 +73270,13 @@
         <v>53</v>
       </c>
       <c r="E3294" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3294" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G3294" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3295" spans="1:7" x14ac:dyDescent="0.25">
@@ -73232,13 +73293,13 @@
         <v>53</v>
       </c>
       <c r="E3295" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3295" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3295" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3296" spans="1:7" x14ac:dyDescent="0.25">
@@ -73255,13 +73316,13 @@
         <v>53</v>
       </c>
       <c r="E3296" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3296" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3296" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3297" spans="1:7" x14ac:dyDescent="0.25">
@@ -73278,13 +73339,13 @@
         <v>53</v>
       </c>
       <c r="E3297" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3297" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3297" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3298" spans="1:7" x14ac:dyDescent="0.25">
@@ -73301,13 +73362,13 @@
         <v>53</v>
       </c>
       <c r="E3298" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3298" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3298" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="G3298" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3299" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
@@ -73324,10 +73385,10 @@
         <v>53</v>
       </c>
       <c r="E3299" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3299" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3299" s="1" t="s">
         <v>58</v>
@@ -73804,16 +73865,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3320" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3320" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3320" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G3320" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3321" spans="1:7" x14ac:dyDescent="0.25">
@@ -73827,16 +73888,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3321" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3321" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3321" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3321" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="E3321" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3321" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3321" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3322" spans="1:7" x14ac:dyDescent="0.25">
@@ -73850,16 +73911,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3322" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3322" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3322" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G3322" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3323" spans="1:7" x14ac:dyDescent="0.25">
@@ -73873,16 +73934,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3323" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3323" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3323" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3323" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E3323" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3323" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3323" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3324" spans="1:7" x14ac:dyDescent="0.25">
@@ -73896,16 +73957,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3324" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3324" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F3324" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G3324" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3325" spans="1:7" x14ac:dyDescent="0.25">
@@ -73919,16 +73980,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3325" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3325" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F3325" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3325" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="G3325" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3326" spans="1:7" x14ac:dyDescent="0.25">
@@ -73942,16 +74003,16 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3326" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3326" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F3326" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3326" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G3326" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3327" spans="1:7" x14ac:dyDescent="0.25">
@@ -73965,13 +74026,13 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3327" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3327" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F3327" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3327" s="1" t="s">
         <v>23</v>
@@ -73988,15 +74049,176 @@
         <v>0.36805555555555602</v>
       </c>
       <c r="D3328" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3328" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F3328" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G3328" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3329" s="3">
+        <v>46106</v>
+      </c>
+      <c r="B3329" s="3">
+        <v>46106</v>
+      </c>
+      <c r="C3329" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3329" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3329" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3329" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3329" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3330" s="3">
+        <v>46107</v>
+      </c>
+      <c r="B3330" s="3">
+        <v>46107</v>
+      </c>
+      <c r="C3330" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3330" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3330" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3330" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3330" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3331" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B3331" s="3">
+        <v>46108</v>
+      </c>
+      <c r="C3331" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3331" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3331" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3331" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3331" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3332" s="3">
+        <v>46111</v>
+      </c>
+      <c r="B3332" s="3">
+        <v>46111</v>
+      </c>
+      <c r="C3332" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3332" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3332" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3332" t="s">
+        <v>186</v>
+      </c>
+      <c r="G3332" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3333" s="3">
+        <v>46112</v>
+      </c>
+      <c r="B3333" s="3">
+        <v>46112</v>
+      </c>
+      <c r="C3333" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3333" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3333" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3333" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3333" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3334" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B3334" s="3">
+        <v>46113</v>
+      </c>
+      <c r="C3334" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3334" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3334" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3334" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3334" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3335" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B3335" s="3">
+        <v>46114</v>
+      </c>
+      <c r="C3335" s="9">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3335" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3335" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3335" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3335" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -74017,12 +74239,12 @@
     <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>67</v>
+      <c r="C2" s="12" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -74035,6 +74257,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" location="loading" xr:uid="{D78A8DDD-B28F-4768-92AE-88106F1DECAE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353A830F-8548-4D4B-A789-3EB69C9302E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945BD0CF-1692-4A76-ABAB-8E840E7518D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11235" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
   <sheets>
     <sheet name="USDKRW" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3613" uniqueCount="208">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -23071,6 +23071,48 @@
   </si>
   <si>
     <t>[달러/원 환율] 금일 오전 10시 트럼프 담화문 주목, 이후 방향성 모색 전일 달러/원 환율은 미국과 이란 종전 기대에 따른 달러 강세 압력 약화와 위험자산 선호 심리 회복에 1,508원으로 갭 하락 개장. 이후 저가 매수 유입되며 1,510원 부근 등락하였으나, 국제유가 하락에 더해 KOSPI 8% 폭등 등 투자 심리 회복이 지속되며 1,500원대 초반까지 하락, 전일 종가 대비 28.8원 하락한 1,501.3원에 정규장 마감. 야간장에서는 미국 경제지표 호조와 저가 매수 유입으로 1,513.3원으로 상승 마감. 역외 NDF 환율은 15.75원 상승한 1,515.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 1,510원대로 상승 개장 예상. 금일 오전 10시 트럼프 대국민 담화 앞두고 시장 경계 고조. 담화 발표 전까지 포지션 플레이 제한되며 방향성도 부재할 전망. 담화문에서 종전 향한 유화적 메세지 나올 경우 위험자산 선호 심리 더욱 확산. 이 경우 국내 증시는 물론 원화 자산 전반이 강세 압력 받을 전망. 이에 달러/원 역시 1,500원대 초반까지 상승 폭 축소 예상 [글로벌 동향] 미국 고용 등 경제는 양호, 미·이란 종전 기대에 달러 약세 전일 미 달러화는 미국 경제지표 호조 속, 이란 종전 기대 이어지며 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.32% 하락한 99.57pt 기록. 전날 발표된 미국 지표는 시장 예상보다 대체로 양호. ADP 3월 민간고용은 전월대비 6.2만명 증가하며 예상치 (+4.0만명) 상회. 2월 소매판매는 전월대비 0.6% 증가하며 예상 (+0.5%)과 전월 (- 0.1%)을 모두 상회. 마지막으로 ISM 3월 제조업 지수는 52.7pt로 예상치 (52.3pt) 상회. 특히 제조업 가격지수는 78.3pt로 7.8pt 급등하며 물가상승 우려 점증. 하지만 시장은 미국의 양호한 경제지표보다는 종전 여부에 주목. 이란 대통령은 미국인들에게 보낸 서신을 통해 종전 의사를 전달. 트럼프 대통령은 금일 오진 10시 무렵 이란 전쟁 관련 대국민 담화 발표 예정. 미 국채금리는 관망세 보이며 장단기물 대체로 보합권 등락. WTI 국제유가는 전일대비 1.24% 하락한 배럴당 100.12달러에 거래 [마켓 이슈] 정부의 외환시장 안정 노력, 전황 진정 시 환율 하락 전환 기대 이란 전쟁과 유가 급등에 달러/원의 상방 변동성 역시 커진 국면. 전쟁이 길어질수록 위험회피와 에너지 공급 차질이 원화에 계속 부담으로 작용. 이런 상황 속에서 정부는 외환시장 안정과 달러수급 개선 위한 대응에 총력. 최근 국회 통과된 '환율안정 3법'은 민간의 달러수요 완화 및 해외자금 국내 환류 유도에 방점. '국민연금 뉴프레임워크'는 해외투자 비중 조정과 외화채 발행을 통해 신규 달러수요를 줄이고, 환헤지 확대 통해 필요시 환율 안정에 기여할 수 있음. '외환시장 선진화'는 원화 거래 접근성 및 유동성 개선을 통해 환율 변동성 완화에 기여할 전망. 즉, 현재 정부의 환율 정책 방향은 단순 개입보다는 달러수급 구조 개선에 초점. 당장의 환율 향방에는 이란 전쟁 양상과 유가 추이가 가장 중요. 하지만 향후 전황이 진정되고 유가도 안정될 경우, 해당 정책 요인 효과까지 겹치며 달러/원 하락 전환 압력이 커질 것으로 예상</t>
+  </si>
+  <si>
+    <t>트럼프 밑장빼기에 호구 잡힌 원화 [금일 달러/원 환율 1,507~1,519원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 1,510원 개장, 대외적 원화 약세 압력에 낙폭 축소 예상 전일 달러/원 환율은 트럼프의 이란 전쟁 관련 대국민 담화 경계에 1,512원으로 상승 개장한 이후 발표 직전까지 혼조세. 이후 담화문에서 종전이나 해협 개방 관련 구체적 방안이 제시되지 않아, 시장 내 실망감이 확산. 유가 반등과 증시 하락 등에 원화 역시 약세로 반응, 전일 종가 대비 18.4원 상승한 1,519.7원에 정규장 마감. 야간장에서는 이란의 호르무즈 해협 통과 관련한 프로토콜 마련 소식에 1,510.6원으로 하락 마감. 역외 NDF 환율은 9.15원 하락한 1,509.10원에 최종 호가 금일 달러/원 환율은 간밤 달러 강세에도 역외 거래 감안해 하락 개장 예상. 이란의 호르무즈 해협 프로토콜 준비 소식이 상단 제약했으나 불확실성 잔존. 미·이란 갈등 및 고유가 상황이 여전히 지속 중이기 때문. 환율은 대외적 원화 약세 압력으로 장중 낙폭 축소할 것으로 예상. 다만 WGBI 편입에 따른 외국인 채권자금 유입은 상단을 눌러주는 재료. 반면 외국인 배당 역송금 등은 하단 지지 재료 (금일 약 1.8억 달러) [글로벌 동향] 미·이란 종전 기대 약화, 국제유가 급등에 미 달러화 강세 전일 미 달러화는 미·이란 갈등 지속에 강세 전환. 주요 6개국 통화로 구성될 달러화 지수는 0.45% 상승한 100.02pt 기록. 전일 미국 트럼프 대통령은 이란 전쟁 관련 대국민 담화문 발표. 종전 메시지 낼 거란 시장 기대와는 다르게 다소 강경한 발언. 그는 수주 내 군사 철수를 언급하면서 동시에 강한 공격 가능성도 덧붙임. 이에 시장 분위기는 곧장 실망감으로 바뀌며 달러도 반등. 이란 의회 의장은 트럼프 강경 발언에 항전 의지 피력. 의장은 이란이 싸울 준비가 되어있다며 확전 분위기 자극. 이에 WTI 국제유가는 전일대비 11.41% 급등한 배럴당 111.54달러에 거래. 이란이 호르무즈 해협의 안전 통과 위한 프로토콜 마련 중이란 소식이 전해짐. 한편 전날 발표된 미국 주요 경제지표는 대체로 양호. 2월 무역수지는 573억 달러 적자로 예상치 (-606억 달러) 상회. 신규 실업수당 청구건수는 20.2만건으로 예상치 (21.2만건) 하회 [마켓 이슈] 美 고용에 대한 낮아진 눈높이, 3월 고용 부진해도 제한적 영향 금일 저녁 발표될 3월 미국 고용보고서에서 시장은 비농업고용 6.5만명 증가, 실업률 4.4%를 예상 중. 이번 고용보고서의 관전 포인트는 비농업고용 숫자 그 자체가 아님. 최근 고용 숫자가 완만하게 낮아지고 있으나, 실업률은 여전히 안정적임. 연준도 3월 회의에서 '고용 증가는 둔화하고 있지만, 실업률은 안정적'이라고 평가. 해당 배경에는 낮아진 적정 고용 수준이 중요. 댈러스 연은에 따르면, 실업률 유지에 필요한 비농업 고용 증가폭 (breakeven)은 2023년 월평균 25만명에서 2025년 하반기에는 거의 0명까지 낮아짐. 최근 3개월 고용도 breakeven을 소폭 웃도는 데 그쳤고, 동 기간 실업률은 4.3~4.5%로 안정적이었음. 따라서 이번 3월 고용이 예상보다 다소 낮게 나오더라도 '적정 수준'보다 높다면, 연준 금리인하 기대는 생각보다 크지 않을 전망. 이 경우 달러 역시 큰 폭의 약세보다는 하방이 제한된 흐름이 유력하다는 판단</t>
+  </si>
+  <si>
+    <t>미국의 물가 둔화, 환율도 추가 상승에 부담 [금일 달러/원 환율 1,468~1,478원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 정부의 환율 안정 조치에도 좀처럼 움직이지 않는 환율 전일 달러/원 환율은 2.5원 낮은 1,477.3원으로 출발한 뒤 횡보세를 보였으며, 정부의 외환건전성 개선 방안 등이 발표되고, 7대 수출 기업들과 간담회 등이 열렸으나 시장 영향은 제한적, 종가는 1.5원 내린 1,478.3원에 마감함. 야간 장에서는 미국 소비자물가의 예상 하회 소식과 뉴욕증시 반등 등 위험회피심리 완화 등에 6.7원 하락했고, NDF 역외환율은 스왑 포인트를 감안하여 1,475원 수준에서 호가됨 금일 달러/원 환율은 정부의 연이은 환율 안정 조치 및 노력에도 불구하고 역내 및 역외 시장에서 좀처럼 방향성을 잡지 못하고 있어 전일과 유사한 1,470원대에서 좁은 박스권 등락이 예상됨. 금일 오전에는 일본 BOJ 금정위가 종료되고, 이번 회의에서 기준금리 0.25%p 인상이 예상되나, 이미 인상 전망은 시장에 반영, BOJ의 추가 인상이 지연될 수 있어 오히려 금리인상 결정 이후 엔화, 원화 약세를 보일 수 있음 [글로벌 동향] 미국 11월 소비자물가 해석에 혼조, 달러는 소폭 강세 전일 미 달러화는 0.06% 상승한 98.46pt를 기록함. 전일 저녁에는 유로 ECB 회의와 영국 BOE 회의가 열렸으며, 유로 ECB는 예상대로 2.0%의 기준금리를 유지, 영국 역시 시장 예상에 부합하며 0.25%p 기준금리를 인하함. 한편 미국에서는 11월 소비자물가 결과도 주목했는데, 결과는 전월대비 0.2% 상승했으나, 전년동월대비로는 2.7%, 근원 소비자물가는 2.6% 상승률을 기록하여 예상치 3.1%와 3.0%를 모두 크게 하회함. 특히 이번 소비자물가 조사는 전월비와 전년비 상승률이 계산에 안 맞는 것으로 나타났고, 일부 항목은 조사가 되지 않았던 것으로 전해짐. 미국 장단기 금리는 소폭 하락한 가운데 뉴욕 증시는 모처럼 반등했으나, 장중 금리와 주가 모두 큰 폭의 변동성을 보였음. 달러화는 강보합, 유로화가 다소 약세를 보였음 [마켓 이슈] 달러/원 고점 인식 및 하방 리스크도 고민해야 할 시점 달러/원 환율이 1,480원에서 강한 저항을 보이고 있는 가운데, 이를 상회하기 어려울 가능성이 크며, 오히려 시장 쏠림이 상승 쪽으로 보고 있다는 점에서 하락 전환될 경우 낙폭이 클 수 있다고 판단됨. 현재 환율은 경험적으로 +3표준편차 상단에 근접하고 있고, 이는 확률적으로 99% 신뢰구간에 있음. 즉, 1,485원을 상회한 것은 경험적으로 1%에 불과함 (2008년 글로벌 금융위기). 국민연금의 전술적 환헤지 레벨도 +3표준 편차에 있다는 점, 수급 주체들이 모두 달러 매수를 붙자고 있다는 점 (한 방향 쏠림), 정부의 계속되는 환율 하락 안정 의지 등을 모두 감안해도 현재 환율에서 상승 기대보다 하락 전환될 가능성이 크다고 판단됨. 지난 2022년 10월과 2025년 1~3월, 모두 +3표준편차에서 크게 튀지 못했고, 이후 하락할 경우 낙폭이 상대적으로 컸음</t>
+  </si>
+  <si>
+    <t>핵심은 M2 아닌 수급, 당국·연금 콜라보 기대 [금일 달러/원 환율 1,469~1,477원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 약 달러 전환, 외환스와프 등 수급 개선 기대에 하락 예상 전일 달러/원 환율은 미 고용지표 부진에 따른 달러 약세에 1,474원으로 하락 개장. 하지만 아시아장에서 간밤에 하락한 미 국채금리와 달러화 지수가 기술적으로 반등, 이에 동조하며 환율은 1,480원 상회. 고점 매도에 추가 상승은 제한되었으나, 외국인 국내주식 순매도 등에 박스권 등락하며 전일 종가 대비 2.8원 상승한 1,479.8원에 정규장 마감. 야간장에서는 외환당국과 국민연금 스와프 재개에 1,474.5원으로 하락 마감. 역외 NDF 환율은 4.00원 하락한 1,473.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 반등에도 역외 거래 감안해 하락 개장 예상. 월러 이사 비둘기 발언에 글로벌 달러 추가 반등 여력은 제한적. 그보다는 금일 매파적일 유럽 ECB 회의 기대 반영하며 약 달러 전환 예상. 더불어 외환당국과 국민연금 외환스와프 재개 소식은 달러/원 하락 요인. 스와프 거래시 역내 수급 불균형 일부 완화될 것으로 기대. 다만 AI 투심 악화 등 위험회피가 국내증시와 원화에 부정적 영향 미칠 가능성 [글로벌 동향] 파운드 약세 및 AI 투심 악화에 달러 반등, 월러는 완화적 전일 미 달러화는 기술적 되돌림과 파운드화 절하, 위험회피심리 등에 강세 전환. 주요 6개국 통화로 구성된 달러화 지수는 0.19% 상승한 98.40pt 기록. 미국 실업률 상승 확인 직후 하락했던 달러는 아시아장에서 기술적 반등 시도. 더불어 영국 파운드화가 약세 전환하며 달러화 지수 상방 자극. 영국 11월 소비자물가는 전년비 3.2% 상승에 그치며 예상치 (+3.5%) 하회. 이에 영국 BOE 금리인하 기대 커지며 파운드화 약세 압력으로 작용. 뉴욕증시는 AI 관련주 투심 악화에 3대 지수 동반 하락 마감. 이 역시 위험회피심리 자극하며 달러에 일부 강세 요인으로 작용. 한편 크리스토퍼 월러 연준 이사의 비둘기 발언에 강 달러 압력이 다소 완화. 월러는 현재 금리가 중립 수준보다 50~100bp 더 높다며 추가 인하 가능성 시사. 그는 인플레이션이 통제 가능한 범위에 있다고 첨언. 그는 트럼프 대통령과의 면담에서 연준 독립성을 강조할 것이라고 밝힘 [마켓 이슈] M2 논쟁에 대한 의견: 원화 약세 배경 맞지만, 올해는 희생양 최근 달러/원 환율 상승 배경으로 한국의 M2 증가율이 미국보다 빠르다는 점이 부각. 통화량 증가 속도가 빠른 한국의 원화가 약세를 보인다는 것은 이론적으로 타당. 다만 한미 M2 증가율 역전은 한미 금리 역전 이후 3년 이상 지속된 현상. 이를 올해 원화 약세를 촉발한 '새로운 트리거'로 보기에는 한계가 존재. M2 논쟁이 부각된 배경에는 대선 이후 새정부 출범과 함께 소비쿠폰 등 확장적 재정정책이 병행되었다는 점. 이로 인해 유동성 확대 이슈가 부각, 즉 환율 변동을 설명하는 변수로 M2에 주목. 그러나 M2는 올해 환율 상승의 직접적인 원인이라기보다, '희생양 변수'로 활용되고 있다는 판단. 희생양 이론에 따르면, 환율이 '관측 불가능한' 요인으로 움직일 때 시장은 '관측 가능한' 변수를 선택해 환율 변동의 원인으로 해석하려는 경향 (박철범, 2025). 즉, 작금의 M2 논쟁 역시 이러한 맥락에서 이해, 과대 해석에는 주의가 필요하다는 판단</t>
+  </si>
+  <si>
+    <t>고용이고 뭐고, 내놓지 않을 달러 [금일 달러/원 환율 1,468~1,477원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대내외적 하락 여건에도 수급 불균형에 1,470원대 혼조 전일 달러/원 환율은 미 달러화 약세와 일본 금리인상 기대에 따른 엔화 강세 동조에 1,468원으로 하락 개장. 하지만 꾸준한 결제 수요 유입에 추가 하락이 제한된 가운데, 수출 네고 실종과 외국인의 국내주식 1조원 이상 순매도 등 수급 불균형에 1,470원 상회. 오후장 내내 상승 흐름이 이어지며 전일 종가 대비 6.0원 상승한 1,477.0원에 정규장 마감. 야간장에서는 고점 인식에 상승 폭 일부 반납하며 1,473.0원에 마감. 역외 NDF 환율은 2.30원 하락한 1,472.40원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,470원대 초반 개장 예상. 미국 고용 및 소비 등 주요 지표 둔화에 달러 약세 압력 가중. 더불어 일본 엔화 역시 강세 전환하며 원화에 긍정적. 하지만 네고 부족 및 달러 보유 심리, 꾸준한 결제 수요 등 수급 불균형이 하단 지지. 다만 당국과 연금의 스와프 및 환헤지 연장 등이 롱 심리 일부 완화. 금일 환율은 여러 하방 요인에도, 수급 불균형에 1,470원대 혼조 예상 [글로벌 동향] 미 실업률 4년 만에 최고치, 미 국채금리 하락 및 약 달러 전일 미 달러화는 미국 실업률 상승 및 소매판매 보합 등 경제지표 부진에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.09% 하락한 98.22pt 기록. 미국 노동부에 따르면, 10월 비농업 고용은 셧다운 여파에 전월대비 10.5만명 감소. 11월 고용은 기저효과에 6.4만명 증가했고 예상치 (+5만명) 상회. 하지만 파월 의장이 주장한 6만명 과대계상 감안 시, 11월 실질 고용은 1.4만명 증가. 이는 댈러스 연은이 추정한 손익분기점 고용인 3만명을 하회하는 수준. 손익분기점 고용이란 안정적인 실업률 유지를 위해 필요한 적정 고용 수준. 11월 실업률은 4.6%로 예상치 4.5%를 0.1%p 상회. 이는 2021년 9월 이후 4년 만에 가장 높은 수준으로 노동시장 냉각 시사. 미국 10월 소매판매는 전월대비 보합으로 예상치 (+0.1%) 하회. 이처럼 예상보다 부진한 지표 결과에 미 국채금리는 장단기물 모두 하락 [마켓 이슈] 외환당국-국민연금 스와프·환헤지, 역내 수급 여건 변화 조짐 15일 외환당국과 국민연금은 650억 달러 규모 외환스와프 계약을 내년 말까지 연장. 동시에 국민연금은 한시적 전략적 환헤지를 내년까지 연장하기로 결정. 이번 조치는 역내 외환시장 수급에 직접적 영향을 미칠 변수라는 판단. 스와프의 핵심은 국민연금 해외투자에 필요한 달러를 외환당국을 통해 조달하는 것. 즉 현물환 시장에서는 달러 수요가 줄어드는 것을 의미. 전략적 환헤지는 향후 환율 하락에 따른 환 손실 방어를 위해 달러를 선물환 시장에 매도하는 방식. 이는 실무적으로 현물환 시장에서의 달러 공급 증가로 연결. 요약하면 외환스와프→달러 수요 감소, 전략적 환헤지→달러 공급 증가로 정리. 즉, 수급 논리상 달러/원 환율이 하락하는 효과 발생. 이번 조치로 역내 외환시장의 가장 큰 손인 국민연금의 환 포지션이 일부 변화할 가능성. 이 경우 최근 고환율의 주요 원인이었던 역내 수급 쏠림도 일부 완화될 것으로 예상</t>
+  </si>
+  <si>
+    <t>안팎으로 조성되는 원화 반전 분위기 [금일 달러/원 환율 1,462~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 원화에 우호적인 대외 환경, 수급 쏠림 완화에 하락 방향 전일 달러/원 환율은 AI 버블 경계로 인한 위험회피심리에 상승 개장한 이후 장초반 1,477원까지 추가 상승. 하지만 외환당국 개입에 대한 경계가 작용하며 상방 제한적. 이후 국내증시 하락 및 외국인 주식 순매도 등에도 불구하고, BOJ 인상 기대에 따른 엔화 강세에 동조해 하락 전환, 전일 종가 대비 2.7원 하락한 1,471.0원에 정규장 마감. 야간장에서는 국민연금 외환스와프 연장 소식에 하락하며 1,468.6원으로 마감. 역외 NDF 환율은 2.35원 하락한 1,466.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,460원대 하락 개장 예상. 완화적 연준 기대에 달러 약세 압력 가중되는 상황. 또한 일본 엔화 강세 역시 원화에 힘을 보태줄 요소. 즉 원화에 우호적인 대외 여건 상 달러/원 하방이 우세하다는 판단. 한편 국민연금 외환스와프 연장 소식은 수급 쏠림 완화에 기여. 역내 달러 매수 우위 분위기 진정되며 달러/원 하락에 일조할 전망 [글로벌 동향] 연준 위원 완화적 발언에 약 달러, 차기 의장에 워시 부상 전일 미 달러화는 FOMC 이후 연준 인사들의 완화적 발언 소화하며 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.10% 하락한 98.31pt 기록. 존 윌리엄스 총재는 이번 FOMC에서 금리인하에 찬성했다고 언급. 그는 고용의 하방 리스크는 커졌지만, 물가 상방 리스크는 줄었다고 평가. 다만 데이터 확인이 추가로 필요하다며 1월 FOMC에 대해서는 신중한 입장. 수전 콜린스 총재는 이번 FOMC에서 금리인하 찬성은 어려운 결정이었다고 언급. 그녀는 물가 리스크가 다소 완화되었다며, 이번 찬성 결정 이유를 설명. 한편 차기 연준 의장으로 케빈 워시 전 연준 이사 부상. 폴리마켓의 워시 지명 확률은 47%, 케빈 해싯은 42%로 2위. 최근 트럼프 측근들이 해싯 임명에 우려를 표한 것으로 추정. 한국 외환당국은 국민연금과 외환스와프 기간을 내년 말까지 연장. 더불어 국민연금 기금위는 한시적 전략적 환헤지 기간 연장안을 심의 및 의결 [마켓 이슈] 파월 주장대로라면, 11월 비농업 고용은 손익분기점 하회 예상 금일 저녁 미국의 10월 및 11월 비농업 고용과 11월 실업률이 발표될 예정. 지난주 12월 FOMC 기자회견에서 파월 의장은 고용 하방 리스크를 명확히 언급. 특히 최근 비농업 고용 통계가 6만명 과대 계상되었을 가능성 제기. 현재 시장 컨센서스는 11월 비농업 고용의 '5만명 증가' 예상. 파월 의장 발언 감안할 경우, 실질적 고용 증가 폭은 '1만명 감소'로 해석될 여지. 최근 댈러스 연은이 추정한 '손익분기점 고용'은 약 3만명. 이는 실업률이 안정적으로 유지되기 위해 필요한 '적정 고용' 수준. 즉 11월 실질적인 고용이 '1만명 감소'하며 적정 고용인 '3만명 증가'를 하회할 가능성. 이 경우 실업률 역시 시차를 두고 상방 압력을 받을 것으로 판단. 이는 연준의 향후 통화정책 경로에도 중요한 함의. 지난 12월 FOMC 점도표는 내년 한 차례의 금리인하 시사. 만약 고용 둔화가 추가로 확인될 경우, 시장은 점도표보다 더 완화적인 금리 경로를 반영할 전망</t>
+  </si>
+  <si>
+    <t>수급이 너무 언발란스... 1,480원 위협 [금일 달러/원 환율 1,470~1,480원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험회피심리 및 역내 수급 불균형, 당국 경계에 혼조세 전일 달러/원 환율은 미 고용지표 둔화에 따른 달러 약세에 하락 개장한 이후 오전장 내내 1,470원대 초반에서 횡보세. 이후 국내증시 호조 및 외국인 주식 순매수 등에도 불구하고, 부족한 수출 네고 및 꾸준한 결제수요 등 달러 매수 우위에 소폭 상승. 이후 오후장 내내 혼조세 보이며 전일 종가 대비 0.7원 상승한 1,473.7원에 정규장 마감. 야간장에서는 글로벌 달러 보합에도 불구하고 AI 경계 등 위험회피에 1,477.0원으로 상승 마감. 역외 NDF 환율은 1.10원 상승한 1,472.60원에 최종 호가 금일 달러/원 환율은 주말간 달러 흐름과 역외 거래 감안해 1,470원대 중후반 개장 예상. 연준 위원들 간 엇갈린 발언에 글로벌 달러의 움직임은 크지 않았음. 하지만 브로드컴 및 오라클 주가 하락 등 AI 버블 경계가 위험회피심리 자극. 더불어 역내 수급적으로는 여전히 달러 수요 우위가 지속되며 하방 경직적. 한편 주말간 정부의 외환시장 긴급 회의 개최. 당국 미세조정 개입 경계에 1,480원 선이 저항선으로 작용 [글로벌 동향] 연준 위원 발언 소화하며 달러 반등, AI 경계에 위험회피 전일 미 달러화는 연준 위원들 발언을 소화하는 가운데, 그간 약세의 기술적 되돌림에 강 보합. 주요 6개국 통화로 구성된 달러화 지수는 0.07% 소폭 상승한 98.40pt 기록. 애나 폴슨 연은 총재는 인플레이션보다는 노동시장 약화를 강조. 그녀는 인플레이션이 내려갈 가능성이 크다며 추가 금리인하 지지 시사. 오스탄 굴스비 연은 총재는 자신은 매파적이지 않고, 금리인하에 가장 낙관적인 사람이라고 언급. 이 같은 몇몇 위원들의 완화적 발언에 미 국채금리는 단기물 중심으로 하락. 한편 베스 해맥 연은 총재는 물가 안정을 강조하며 다소 매파적 색채 드러냄. 유로화는 보합권에 머문 가운데, 파운드는 영국 GDP 하방 서프라이즈에 약세. 영국의 10월 실질 국내총생산은 전월대비 0.1% 감소하며 예상치 (+0.1%) 하회. 뉴욕증시는 AI 버블 경계에 3대 지수 모두 하락 마감. 반도체 기업 브로드컴 주가는 11% 이상 폭락, 오라클 주가는 4% 하락하며 부진 [마켓 이슈] 이번 주 미국 고용지표, ECB·BOJ 통화정책회의가 핵심 변수 지난주 FOMC에서 미 연준은 추가 금리인하 단행. 그에 반해 최근 유럽 ECB 및 일본 BOJ 등 주요국 중앙은행은 통화정책 차별화 조짐. 미 연준은 인플레이션보다는 고용 하방 리스크에 더 무게를 두며, 금리인하 사이클을 지속할 가능성. 반면 유럽 및 일본 중앙은행은 물가 관리에 초점을 맞추며 다소 긴축적인 통화정책을 시행할 가능성이 높은 상황. 따라서 이번 주에는 16일 미국 11월 고용지표와 18일 ECB 회의, 그리고 19일 BOJ 금정위가 메인 이벤트이자 핵심 변수. 만약 미국 고용지표의 부진이 다시 한번 확인된다면, 연준의 금리인하 명분은 더욱 강화. 12월 점 도표보다 더 완화적인 금리 경로 기대가 확산 예상. 반면 금주 통화정책회의에서는 ECB 금리동결, BOJ 인상 등 연준보다 매파적 기조 확인될 소지. 이 경우 미국과 주요국 간 국채금리차는 더욱 축소 예상. 즉, 미국의 금리 메리트 약화로 인해 달러는 더욱 약세 압력을 받을 전망</t>
+  </si>
+  <si>
+    <t>니가 왜 거기서 나와(feat. 오라클) [금일 달러/원 환율 1,463~1,474원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 글로벌 달러 약세 vs. AI 버블 위험회피심리에 혼조 예상 전일 달러/원 환율은 완화적으로 평가된 FOMC 회의 결과 및 달러 약세에 하락하며 개장했으나, 이내 결제 수요가 유입되며 하단 지지. 국내 증시에서 외국인의 순매도가 지속되는 가운데, 환율 불안에 따르 수출 네고 관망세 등 수급 불균형으로 상승 전환. 1,470원 위에서 횡보하다가 전일 종가 대비 2.6원 상승한 1,473.0원에 정규장 마감. 야간장에서는 약 달러에도 AI 버블 경계 등 위험회피에 하방 제한되며 1,471.9원에 마감. 역외 NDF 환율은 1.50원 하락한 1,469.30원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 보합권 개장 예상. 완화적 FOMC 여파 및 미 고용 둔화에 약 달러 흐름. 하지만 오라클 등 AI 버블 경계로 인해 아시아 증시 추가 조정 가능성. 달러/원은 대외적 달러 약세 재료 및 위험회피 재료가 대치하며 혼조 예상. 다만 당국 미세조정 경계에 상단은 1,470원대 중반으로 제한적. 오히려 위험회피 완화 및 약 달러 동조 시, 환율은 1,460원대 진입 시도 예상 [글로벌 동향] 미 고용지표 일부 둔화, 오라클發 AI 버블 경계에 약 달러 전일 미 달러화는 완화적 FOMC 여파가 이어지는 가운데, AI 버블 경계에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.32% 하락한 98.33pt 기록. 전일 연준은 3연속 금리인하 단행, 파월 의장은 기대보다 완화적인 메시지. 이 가운데 미국 주간 실업수당 청구건수가 23.6만건으로 집계되며 예상치 상회. 즉 연준 인하 배경인 고용 리스크가 일부 확인되며 달러에 약세 압력. 트럼프 대통령은 연준의 금리인하를 반겨하면서도, 더 많은 조치가 필요하다고 언급. 한편 오라클發 AI 버블 우려가 불거지며 달러 약세 압력 가중. 오라클의 과잉 투자 의구심이 제기되며 오라클 주가는 장중 16% 급락. 이 같은 분위기가 AI 산업 전반으로 번지며 나스닥 지수가 하락 조정. 이에 투자 수요가 주식 외 안전자산인 채권으로 몰리며 미 국채금리는 장단기물 모두 하락. 미 국채금리 하락에 연동되며 달러화 지수 역시 하락 [마켓 이슈] 달러/원 하락에 우호적 대외 환경 조성, 이제 일본 엔화가 관건 12월 FOMC 이후 글로벌 환경이 달러/원 환율의 하락을 뒷받침하는 방향으로 바뀌는 상황. 연준이 추가 금리인하를 단행한 가운데, 파월 발언이 당초 예상보다 완화적으로 평가. 이에 미 국채금리가 하락하고 달러는 전반적으로 약세 압력을 받고 있는 흐름. 더불어 달러/원 하락을 위한 또 다른 대외 변수로 일본 엔화에 주목. 엔화는 차주 BOJ 회의를 앞두고, 금리인상 가능성이 부각되며 강세 전환 시도 중. 최근 원화 및 엔화의 동조화가 나타나고 있어, 엔화 강세 시 원화도 영향 받을 전망. 한편 달러/원은 지난 한 달간 1,470원대에서 지속적으로 막히며 상단 인식 형성. 동시에 하단도 1,460원에서 형성되며 방향성 없는 박스권 흐름. 하지만 원화는 소규모 개방경제의 로컬 통화 특성 상 대외 여건 변화에 민감하게 반응. 즉, 글로벌 달러 약세 흐름이 확산되고, 엔화까지 강세 전환에 성공한다면, 달러/원도 박스권 하단 돌파 시도 예상</t>
   </si>
 </sst>
 </file>
@@ -23517,7 +23559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3335"/>
+  <dimension ref="A1:G3334"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" bestFit="1" customWidth="1"/>
@@ -72373,7 +72415,7 @@
       </c>
       <c r="F3248" s="1"/>
     </row>
-    <row r="3249" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3249" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3249" s="3">
         <v>45992</v>
       </c>
@@ -72388,7 +72430,7 @@
       </c>
       <c r="F3249" s="1"/>
     </row>
-    <row r="3250" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3250" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3250" s="3">
         <v>45993</v>
       </c>
@@ -72403,7 +72445,7 @@
       </c>
       <c r="F3250" s="1"/>
     </row>
-    <row r="3251" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3251" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3251" s="3">
         <v>45994</v>
       </c>
@@ -72418,7 +72460,7 @@
       </c>
       <c r="F3251" s="1"/>
     </row>
-    <row r="3252" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3252" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3252" s="3">
         <v>45995</v>
       </c>
@@ -72433,7 +72475,7 @@
       </c>
       <c r="F3252" s="1"/>
     </row>
-    <row r="3253" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3253" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3253" s="3">
         <v>45996</v>
       </c>
@@ -72448,7 +72490,7 @@
       </c>
       <c r="F3253" s="1"/>
     </row>
-    <row r="3254" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3254" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3254" s="3">
         <v>45997</v>
       </c>
@@ -72463,7 +72505,7 @@
       </c>
       <c r="F3254" s="1"/>
     </row>
-    <row r="3255" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3255" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3255" s="3">
         <v>45998</v>
       </c>
@@ -72478,7 +72520,7 @@
       </c>
       <c r="F3255" s="1"/>
     </row>
-    <row r="3256" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3256" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3256" s="3">
         <v>45999</v>
       </c>
@@ -72493,7 +72535,7 @@
       </c>
       <c r="F3256" s="1"/>
     </row>
-    <row r="3257" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3257" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3257" s="3">
         <v>46000</v>
       </c>
@@ -72508,7 +72550,7 @@
       </c>
       <c r="F3257" s="1"/>
     </row>
-    <row r="3258" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3258" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3258" s="3">
         <v>46001</v>
       </c>
@@ -72523,7 +72565,7 @@
       </c>
       <c r="F3258" s="1"/>
     </row>
-    <row r="3259" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3259" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3259" s="3">
         <v>46002</v>
       </c>
@@ -72538,7 +72580,7 @@
       </c>
       <c r="F3259" s="1"/>
     </row>
-    <row r="3260" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3260" s="3">
         <v>46003</v>
       </c>
@@ -72551,14 +72593,22 @@
       <c r="D3260" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3260" s="1"/>
-    </row>
-    <row r="3261" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3260" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3260" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3260" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3261" s="3">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="B3261" s="3">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="C3261" s="9">
         <v>0.36805555555555558</v>
@@ -72566,14 +72616,22 @@
       <c r="D3261" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3261" s="1"/>
-    </row>
-    <row r="3262" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3261" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3261" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3261" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3262" s="3">
-        <v>46005</v>
+        <v>46007</v>
       </c>
       <c r="B3262" s="3">
-        <v>46005</v>
+        <v>46007</v>
       </c>
       <c r="C3262" s="9">
         <v>0.36805555555555558</v>
@@ -72581,14 +72639,22 @@
       <c r="D3262" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3262" s="1"/>
-    </row>
-    <row r="3263" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3262" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3262" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3262" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3263" s="3">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B3263" s="3">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C3263" s="9">
         <v>0.36805555555555558</v>
@@ -72596,14 +72662,22 @@
       <c r="D3263" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3263" s="1"/>
-    </row>
-    <row r="3264" spans="1:6" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3263" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3263" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3263" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3264" s="3">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B3264" s="3">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C3264" s="9">
         <v>0.36805555555555558</v>
@@ -72611,14 +72685,22 @@
       <c r="D3264" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3264" s="1"/>
+      <c r="E3264" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3264" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3264" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3265" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3265" s="3">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B3265" s="3">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C3265" s="9">
         <v>0.36805555555555558</v>
@@ -72626,14 +72708,22 @@
       <c r="D3265" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3265" s="1"/>
-    </row>
-    <row r="3266" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3265" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3265" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3265" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3266" s="3">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B3266" s="3">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C3266" s="9">
         <v>0.36805555555555558</v>
@@ -72641,14 +72731,22 @@
       <c r="D3266" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3266" s="1"/>
-    </row>
-    <row r="3267" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="E3266" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3266" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3266" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3267" s="3">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B3267" s="3">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C3267" s="9">
         <v>0.36805555555555558</v>
@@ -72656,14 +72754,22 @@
       <c r="D3267" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F3267" s="1"/>
+      <c r="E3267" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3267" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3267" s="4" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="3268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3268" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B3268" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C3268" s="9">
         <v>0.36805555555555558</v>
@@ -72672,21 +72778,21 @@
         <v>53</v>
       </c>
       <c r="E3268" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F3268" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G3268" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3269" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B3269" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="C3269" s="9">
         <v>0.36805555555555558</v>
@@ -72695,10 +72801,10 @@
         <v>53</v>
       </c>
       <c r="E3269" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F3269" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G3269" s="4" t="s">
         <v>142</v>
@@ -72706,10 +72812,10 @@
     </row>
     <row r="3270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3270" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B3270" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C3270" s="9">
         <v>0.36805555555555558</v>
@@ -72718,21 +72824,21 @@
         <v>53</v>
       </c>
       <c r="E3270" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F3270" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G3270" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3271" s="3">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B3271" s="3">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="C3271" s="9">
         <v>0.36805555555555558</v>
@@ -72741,10 +72847,10 @@
         <v>53</v>
       </c>
       <c r="E3271" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F3271" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G3271" s="4" t="s">
         <v>142</v>
@@ -72752,10 +72858,10 @@
     </row>
     <row r="3272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3272" s="3">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B3272" s="3">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="C3272" s="9">
         <v>0.36805555555555558</v>
@@ -72764,10 +72870,10 @@
         <v>53</v>
       </c>
       <c r="E3272" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F3272" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G3272" s="4" t="s">
         <v>132</v>
@@ -72775,10 +72881,10 @@
     </row>
     <row r="3273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3273" s="3">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B3273" s="3">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="C3273" s="9">
         <v>0.36805555555555558</v>
@@ -72787,21 +72893,21 @@
         <v>53</v>
       </c>
       <c r="E3273" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F3273" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G3273" s="4" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3274" s="3">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B3274" s="3">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="C3274" s="9">
         <v>0.36805555555555558</v>
@@ -72810,21 +72916,21 @@
         <v>53</v>
       </c>
       <c r="E3274" s="1" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F3274" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="G3274" s="4" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3275" s="3">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B3275" s="3">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C3275" s="9">
         <v>0.36805555555555558</v>
@@ -72833,10 +72939,10 @@
         <v>53</v>
       </c>
       <c r="E3275" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F3275" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G3275" s="4" t="s">
         <v>83</v>
@@ -72844,10 +72950,10 @@
     </row>
     <row r="3276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3276" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B3276" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C3276" s="9">
         <v>0.36805555555555558</v>
@@ -72856,10 +72962,10 @@
         <v>53</v>
       </c>
       <c r="E3276" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F3276" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G3276" s="4" t="s">
         <v>83</v>
@@ -72867,10 +72973,10 @@
     </row>
     <row r="3277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3277" s="3">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B3277" s="3">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="C3277" s="9">
         <v>0.36805555555555558</v>
@@ -72879,10 +72985,10 @@
         <v>53</v>
       </c>
       <c r="E3277" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F3277" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G3277" s="4" t="s">
         <v>83</v>
@@ -72890,10 +72996,10 @@
     </row>
     <row r="3278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3278" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B3278" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="C3278" s="9">
         <v>0.36805555555555558</v>
@@ -72902,10 +73008,10 @@
         <v>53</v>
       </c>
       <c r="E3278" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F3278" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G3278" s="4" t="s">
         <v>83</v>
@@ -72913,10 +73019,10 @@
     </row>
     <row r="3279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3279" s="3">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B3279" s="3">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="C3279" s="9">
         <v>0.36805555555555558</v>
@@ -72925,10 +73031,10 @@
         <v>53</v>
       </c>
       <c r="E3279" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F3279" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G3279" s="4" t="s">
         <v>83</v>
@@ -72936,10 +73042,10 @@
     </row>
     <row r="3280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3280" s="3">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B3280" s="3">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="C3280" s="9">
         <v>0.36805555555555558</v>
@@ -72948,10 +73054,10 @@
         <v>53</v>
       </c>
       <c r="E3280" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F3280" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3280" s="4" t="s">
         <v>83</v>
@@ -72959,10 +73065,10 @@
     </row>
     <row r="3281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3281" s="3">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B3281" s="3">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C3281" s="9">
         <v>0.36805555555555558</v>
@@ -72971,10 +73077,10 @@
         <v>53</v>
       </c>
       <c r="E3281" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3281" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G3281" s="4" t="s">
         <v>83</v>
@@ -72982,10 +73088,10 @@
     </row>
     <row r="3282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3282" s="3">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B3282" s="3">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="C3282" s="9">
         <v>0.36805555555555558</v>
@@ -72994,10 +73100,10 @@
         <v>53</v>
       </c>
       <c r="E3282" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F3282" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G3282" s="4" t="s">
         <v>83</v>
@@ -73005,10 +73111,10 @@
     </row>
     <row r="3283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3283" s="3">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B3283" s="3">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C3283" s="9">
         <v>0.36805555555555558</v>
@@ -73017,10 +73123,10 @@
         <v>53</v>
       </c>
       <c r="E3283" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F3283" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G3283" s="4" t="s">
         <v>83</v>
@@ -73028,10 +73134,10 @@
     </row>
     <row r="3284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3284" s="3">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="B3284" s="3">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="C3284" s="9">
         <v>0.36805555555555558</v>
@@ -73040,10 +73146,10 @@
         <v>53</v>
       </c>
       <c r="E3284" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F3284" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G3284" s="4" t="s">
         <v>83</v>
@@ -73051,10 +73157,10 @@
     </row>
     <row r="3285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3285" s="3">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B3285" s="3">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="C3285" s="9">
         <v>0.36805555555555558</v>
@@ -73063,10 +73169,10 @@
         <v>53</v>
       </c>
       <c r="E3285" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F3285" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G3285" s="4" t="s">
         <v>83</v>
@@ -73074,10 +73180,10 @@
     </row>
     <row r="3286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3286" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="B3286" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="C3286" s="9">
         <v>0.36805555555555558</v>
@@ -73086,10 +73192,10 @@
         <v>53</v>
       </c>
       <c r="E3286" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F3286" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G3286" s="4" t="s">
         <v>83</v>
@@ -73097,10 +73203,10 @@
     </row>
     <row r="3287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3287" s="3">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B3287" s="3">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="C3287" s="9">
         <v>0.36805555555555558</v>
@@ -73109,10 +73215,10 @@
         <v>53</v>
       </c>
       <c r="E3287" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F3287" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G3287" s="4" t="s">
         <v>83</v>
@@ -73120,10 +73226,10 @@
     </row>
     <row r="3288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3288" s="3">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B3288" s="3">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="C3288" s="9">
         <v>0.36805555555555558</v>
@@ -73132,10 +73238,10 @@
         <v>53</v>
       </c>
       <c r="E3288" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F3288" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G3288" s="4" t="s">
         <v>83</v>
@@ -73143,10 +73249,10 @@
     </row>
     <row r="3289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3289" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B3289" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="C3289" s="9">
         <v>0.36805555555555558</v>
@@ -73155,10 +73261,10 @@
         <v>53</v>
       </c>
       <c r="E3289" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F3289" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G3289" s="4" t="s">
         <v>83</v>
@@ -73166,10 +73272,10 @@
     </row>
     <row r="3290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3290" s="3">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B3290" s="3">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="C3290" s="9">
         <v>0.36805555555555558</v>
@@ -73178,10 +73284,10 @@
         <v>53</v>
       </c>
       <c r="E3290" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F3290" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G3290" s="4" t="s">
         <v>83</v>
@@ -73189,10 +73295,10 @@
     </row>
     <row r="3291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3291" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B3291" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="C3291" s="9">
         <v>0.36805555555555558</v>
@@ -73201,10 +73307,10 @@
         <v>53</v>
       </c>
       <c r="E3291" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F3291" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G3291" s="4" t="s">
         <v>83</v>
@@ -73212,10 +73318,10 @@
     </row>
     <row r="3292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3292" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B3292" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C3292" s="9">
         <v>0.36805555555555558</v>
@@ -73224,10 +73330,10 @@
         <v>53</v>
       </c>
       <c r="E3292" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F3292" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G3292" s="4" t="s">
         <v>83</v>
@@ -73235,10 +73341,10 @@
     </row>
     <row r="3293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3293" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B3293" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="C3293" s="9">
         <v>0.36805555555555558</v>
@@ -73247,21 +73353,21 @@
         <v>53</v>
       </c>
       <c r="E3293" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F3293" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G3293" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3294" s="3">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B3294" s="3">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="C3294" s="9">
         <v>0.36805555555555558</v>
@@ -73270,21 +73376,21 @@
         <v>53</v>
       </c>
       <c r="E3294" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F3294" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G3294" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3295" s="3">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B3295" s="3">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="C3295" s="9">
         <v>0.36805555555555558</v>
@@ -73293,10 +73399,10 @@
         <v>53</v>
       </c>
       <c r="E3295" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F3295" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G3295" s="4" t="s">
         <v>71</v>
@@ -73304,10 +73410,10 @@
     </row>
     <row r="3296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3296" s="3">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B3296" s="3">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="C3296" s="9">
         <v>0.36805555555555558</v>
@@ -73316,21 +73422,21 @@
         <v>53</v>
       </c>
       <c r="E3296" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F3296" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G3296" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3297" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3297" s="3">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B3297" s="3">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="C3297" s="9">
         <v>0.36805555555555558</v>
@@ -73339,21 +73445,21 @@
         <v>53</v>
       </c>
       <c r="E3297" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F3297" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3297" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="G3297" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3298" s="3">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B3298" s="3">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="C3298" s="9">
         <v>0.36805555555555558</v>
@@ -73362,21 +73468,21 @@
         <v>53</v>
       </c>
       <c r="E3298" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F3298" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G3298" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3299" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3299" s="3">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B3299" s="3">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="C3299" s="9">
         <v>0.36805555555555558</v>
@@ -73385,21 +73491,21 @@
         <v>53</v>
       </c>
       <c r="E3299" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F3299" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3299" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3300" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="G3299" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3300" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3300" s="3">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B3300" s="3">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="C3300" s="9">
         <v>0.36805555555555558</v>
@@ -73408,21 +73514,21 @@
         <v>53</v>
       </c>
       <c r="E3300" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F3300" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3300" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3300" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3301" s="3">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B3301" s="3">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="C3301" s="9">
         <v>0.36805555555555558</v>
@@ -73431,21 +73537,21 @@
         <v>53</v>
       </c>
       <c r="E3301" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F3301" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3301" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3302" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="3302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3302" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B3302" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="C3302" s="9">
         <v>0.36805555555555558</v>
@@ -73454,21 +73560,21 @@
         <v>53</v>
       </c>
       <c r="E3302" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F3302" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3302" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="G3302" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3303" s="3">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B3303" s="3">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="C3303" s="9">
         <v>0.36805555555555558</v>
@@ -73477,10 +73583,10 @@
         <v>53</v>
       </c>
       <c r="E3303" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F3303" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G3303" s="4" t="s">
         <v>33</v>
@@ -73488,10 +73594,10 @@
     </row>
     <row r="3304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3304" s="3">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B3304" s="3">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="C3304" s="9">
         <v>0.36805555555555558</v>
@@ -73500,10 +73606,10 @@
         <v>53</v>
       </c>
       <c r="E3304" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3304" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="F3304" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G3304" s="4" t="s">
         <v>33</v>
@@ -73511,10 +73617,10 @@
     </row>
     <row r="3305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3305" s="3">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B3305" s="3">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="C3305" s="9">
         <v>0.36805555555555558</v>
@@ -73523,10 +73629,10 @@
         <v>53</v>
       </c>
       <c r="E3305" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F3305" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G3305" s="4" t="s">
         <v>33</v>
@@ -73534,10 +73640,10 @@
     </row>
     <row r="3306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3306" s="3">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B3306" s="3">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="C3306" s="9">
         <v>0.36805555555555558</v>
@@ -73546,10 +73652,10 @@
         <v>53</v>
       </c>
       <c r="E3306" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3306" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="F3306" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G3306" s="4" t="s">
         <v>33</v>
@@ -73557,10 +73663,10 @@
     </row>
     <row r="3307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3307" s="3">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B3307" s="3">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="C3307" s="9">
         <v>0.36805555555555558</v>
@@ -73569,10 +73675,10 @@
         <v>53</v>
       </c>
       <c r="E3307" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F3307" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G3307" s="4" t="s">
         <v>33</v>
@@ -73580,10 +73686,10 @@
     </row>
     <row r="3308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3308" s="3">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B3308" s="3">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C3308" s="9">
         <v>0.36805555555555558</v>
@@ -73592,10 +73698,10 @@
         <v>53</v>
       </c>
       <c r="E3308" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F3308" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G3308" s="4" t="s">
         <v>33</v>
@@ -73603,10 +73709,10 @@
     </row>
     <row r="3309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3309" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B3309" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C3309" s="9">
         <v>0.36805555555555558</v>
@@ -73615,10 +73721,10 @@
         <v>53</v>
       </c>
       <c r="E3309" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3309" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G3309" s="4" t="s">
         <v>33</v>
@@ -73626,10 +73732,10 @@
     </row>
     <row r="3310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3310" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B3310" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="C3310" s="9">
         <v>0.36805555555555558</v>
@@ -73638,21 +73744,21 @@
         <v>53</v>
       </c>
       <c r="E3310" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F3310" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G3310" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3311" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A3311" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="B3311" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3311" s="9">
         <v>0.36805555555555558</v>
@@ -73661,21 +73767,21 @@
         <v>53</v>
       </c>
       <c r="E3311" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F3311" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3311" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3311" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3312" s="3">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="B3312" s="3">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="C3312" s="9">
         <v>0.36805555555555558</v>
@@ -73684,21 +73790,21 @@
         <v>53</v>
       </c>
       <c r="E3312" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3312" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G3312" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3313" spans="1:7" ht="12.75" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3313" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B3313" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="C3313" s="9">
         <v>0.36805555555555558</v>
@@ -73707,21 +73813,21 @@
         <v>53</v>
       </c>
       <c r="E3313" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3313" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3313" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="G3313" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3314" s="3">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B3314" s="3">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3314" s="9">
         <v>0.36805555555555558</v>
@@ -73730,21 +73836,21 @@
         <v>53</v>
       </c>
       <c r="E3314" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3314" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G3314" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3315" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B3315" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C3315" s="9">
         <v>0.36805555555555558</v>
@@ -73753,21 +73859,21 @@
         <v>53</v>
       </c>
       <c r="E3315" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F3315" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G3315" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3316" s="3">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B3316" s="3">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="C3316" s="9">
         <v>0.36805555555555558</v>
@@ -73776,10 +73882,10 @@
         <v>53</v>
       </c>
       <c r="E3316" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F3316" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G3316" s="4" t="s">
         <v>23</v>
@@ -73787,10 +73893,10 @@
     </row>
     <row r="3317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3317" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B3317" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="C3317" s="9">
         <v>0.36805555555555558</v>
@@ -73799,67 +73905,67 @@
         <v>53</v>
       </c>
       <c r="E3317" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3317" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3317" s="4" t="s">
-        <v>23</v>
+        <v>56</v>
+      </c>
+      <c r="F3317" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3317" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3318" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B3318" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="C3318" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3318" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E3318" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3318" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3318" s="4" t="s">
-        <v>23</v>
+        <v>90</v>
+      </c>
+      <c r="F3318" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3318" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3319" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B3319" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C3319" s="9">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3319" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E3319" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F3319" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3319" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
+      </c>
+      <c r="G3319" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3320" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B3320" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="C3320" s="9">
         <v>0.36805555555555602</v>
@@ -73868,21 +73974,21 @@
         <v>79</v>
       </c>
       <c r="E3320" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F3320" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G3320" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3321" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B3321" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="C3321" s="9">
         <v>0.36805555555555602</v>
@@ -73891,21 +73997,21 @@
         <v>79</v>
       </c>
       <c r="E3321" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F3321" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3321" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3321" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3322" s="3">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B3322" s="3">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="C3322" s="9">
         <v>0.36805555555555602</v>
@@ -73914,21 +74020,21 @@
         <v>79</v>
       </c>
       <c r="E3322" s="1" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F3322" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="G3322" s="1" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3323" s="3">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B3323" s="3">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C3323" s="9">
         <v>0.36805555555555602</v>
@@ -73937,21 +74043,21 @@
         <v>79</v>
       </c>
       <c r="E3323" s="1" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F3323" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="G3323" s="1" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3324" s="3">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B3324" s="3">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3324" s="9">
         <v>0.36805555555555602</v>
@@ -73960,21 +74066,21 @@
         <v>79</v>
       </c>
       <c r="E3324" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F3324" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G3324" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3325" s="3">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B3325" s="3">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="C3325" s="9">
         <v>0.36805555555555602</v>
@@ -73983,21 +74089,21 @@
         <v>79</v>
       </c>
       <c r="E3325" s="1" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="F3325" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="G3325" s="1" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3326" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B3326" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C3326" s="9">
         <v>0.36805555555555602</v>
@@ -74006,21 +74112,21 @@
         <v>79</v>
       </c>
       <c r="E3326" s="1" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="F3326" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="G3326" s="1" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3327" s="3">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B3327" s="3">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C3327" s="9">
         <v>0.36805555555555602</v>
@@ -74029,10 +74135,10 @@
         <v>79</v>
       </c>
       <c r="E3327" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F3327" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G3327" s="1" t="s">
         <v>23</v>
@@ -74040,10 +74146,10 @@
     </row>
     <row r="3328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3328" s="3">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B3328" s="3">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C3328" s="9">
         <v>0.36805555555555602</v>
@@ -74052,10 +74158,10 @@
         <v>79</v>
       </c>
       <c r="E3328" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F3328" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G3328" s="1" t="s">
         <v>23</v>
@@ -74063,10 +74169,10 @@
     </row>
     <row r="3329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3329" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B3329" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C3329" s="9">
         <v>0.36805555555555602</v>
@@ -74075,10 +74181,10 @@
         <v>79</v>
       </c>
       <c r="E3329" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F3329" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G3329" s="1" t="s">
         <v>23</v>
@@ -74086,10 +74192,10 @@
     </row>
     <row r="3330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3330" s="3">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B3330" s="3">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C3330" s="9">
         <v>0.36805555555555602</v>
@@ -74098,10 +74204,10 @@
         <v>79</v>
       </c>
       <c r="E3330" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F3330" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G3330" s="1" t="s">
         <v>23</v>
@@ -74109,10 +74215,10 @@
     </row>
     <row r="3331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3331" s="3">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B3331" s="3">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C3331" s="9">
         <v>0.36805555555555602</v>
@@ -74121,10 +74227,10 @@
         <v>79</v>
       </c>
       <c r="E3331" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F3331" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G3331" s="1" t="s">
         <v>23</v>
@@ -74132,10 +74238,10 @@
     </row>
     <row r="3332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3332" s="3">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B3332" s="3">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C3332" s="9">
         <v>0.36805555555555602</v>
@@ -74144,10 +74250,10 @@
         <v>79</v>
       </c>
       <c r="E3332" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F3332" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G3332" s="1" t="s">
         <v>23</v>
@@ -74155,10 +74261,10 @@
     </row>
     <row r="3333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3333" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B3333" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C3333" s="9">
         <v>0.36805555555555602</v>
@@ -74167,10 +74273,10 @@
         <v>79</v>
       </c>
       <c r="E3333" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F3333" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G3333" s="1" t="s">
         <v>23</v>
@@ -74178,10 +74284,10 @@
     </row>
     <row r="3334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3334" s="3">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B3334" s="3">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C3334" s="9">
         <v>0.36805555555555602</v>
@@ -74190,35 +74296,12 @@
         <v>79</v>
       </c>
       <c r="E3334" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F3334" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G3334" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3335" s="3">
-        <v>46114</v>
-      </c>
-      <c r="B3335" s="3">
-        <v>46114</v>
-      </c>
-      <c r="C3335" s="9">
-        <v>0.36805555555555602</v>
-      </c>
-      <c r="D3335" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3335" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3335" t="s">
-        <v>192</v>
-      </c>
-      <c r="G3335" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD80D8CC-56B7-4AE3-9926-1A3EB61A9A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90D339C-F9E7-485C-94A7-92617876956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3668" uniqueCount="236">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27250,6 +27250,25 @@
   <si>
     <t>[달러/원 환율] 대외적 여건은 원화 강세에 우호적, 수급과 심리가 변수 전일 달러/원 환율은 연준 금리인하 기대에 따른 달러 약세 압력에 1,462원으로 하락 개장. 하지만 월말임에도 수출 네고 물량이 더디게 출회되는 가운데, 국내증시에서는 외국인 순매도세가 나타나며 환율도 상승으로 전환. 당국 경계에 1,470원이 상단으로 작용, 전일 종가 대비 5.7원 상승한 1,470.6원에 정규장 마감. 야간장에서는 미일 통화정책 차별화 기대에 따른 달러 약세에 하락하며 1,466.8원으로 마감. 역외 NDF 환율은 3.40원 하락한 1,464.75원에 최종 호가 금일 달러/원 환율은 주말간 달러 약세와 역외 거래를 감안해 1,460원대 하락 개장 예상. 연준 금리인하 기대가 지속되며 약 달러 분위기. 일본 엔화는 BOJ 인상 기대에 강세 전환 시도 중. 더불어 위험선호심리는 뉴욕증시 호조 등에 회복 국면. 약 달러·엔 반등·위험선호 조합은 원화에 긍정적. 다만 여전히 꼬여있는 수급과 잔존한 롱 심리가 하단 지지. 달러/원은 대외적 하락 압력과 대내적 하방 경직 요인 대치하며 등락 예상 [글로벌 동향] 캐나다 성장 호조, 미일 통화정책 차별화 기대에 약 달러 전일 미 달러화는 캐나다 경제성장률 호조와 미일 통화정책 차별화 기대에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.11% 하락한 99.46pt 기록. 캐나다의 3분기 실질 GDP는 전기비 연율 2.6% 증가. 이는 예상치 (+0.5%) 및 전기치 (-1.8%)를 모두 큰 폭으로 상회한 수치. 이에 캐나다 달러는 미 달러 대비 0.41% 절상, 환율은 1.4달러를 하회. 한편 시장에서는 12월 미국 및 일본의 통화정책 차별화를 기대하는 모습. OIS 시장에서 연준 금리인하 확률은 88%, BOJ 금리인상 확률은 61%로 반영. 연준 위원들의 발언이나 경제지표는 없었으나, 시장은 연준의 12월 금리인하 기대. 한편 일본 정부는 경기부양 위한 18조 3천억엔 규모 추경 승인. 이에 따른 국채발행 부담에 10년물 국채금리는 1.8%를 상회. 하지만 달러/엔 환율은 미일 금리차 축소 기대 등에 156엔대 초반까지 하락 [마켓 이슈] 상하단 모두 막힌 달러/원, 역내 수급 상황과 미 고용지표 주시 그동안 급격하게 상승했던 달러/원 환율은 최근 들어 상승세가 다소 진정. 외환당국의 강력한 시장 안정 메시지와 한국은행의 매파적 기조, 국민연금의 전략적 환 헤지 경계 등에 1,480원이 상단으로 인식되는 상황. 하지만 달러/원의 하단 역시 단단한 모습. 여전히 역내 시장에서는 달러 매수 우위 장세가 지속. 수출업체의 래깅 (lagging) 전략으로 역내 달러 공급이 부족. 반면 외국인의 국내 증시 이탈과 거주자의 해외투자 등으로 달러 수요는 증가. 11월 한 달 간 외국인 주식 순매도액은 97억 달러. 같은 기간 거주자 해외주식 순매수액은 55억 달러. 즉, 국내외 증시에서 한 달 동안 약 150억 달러 규모의 순유출 압력에 노출. 당분간 이러한 수급 불균형 상태가 이어지며 달러/원 하방은 제한적. 더불어 FOMC를 일주일 앞두고 발표될 미국 고용지표 (ADP 민간고용, ISM 고용지수) 결과도 주시 필요. 금주는 1,450~1,480원 박스권 예상</t>
   </si>
+  <si>
+    <t>1차로 끝낸 협상의 아쉬움, 2차로 달래기 [금일 달러/원 환율 1,465~1,476원 전망]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이민혁</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험선호 및 유가 급락에 동조, 1,460원대 진입도 가능 전일 달러/원 환율은 미·이란 물밑 협상 등 종전 기대로 인한 유가 하락 및 미 달러화 지수 하락에 연동해 1,478원으로 개장. 이후 저가 매수세 유입되며 낙폭 되돌렸으나, 국내증시 호조 및 외국인의 주식 순매수 등에 하락 흐름 유지. 오후장에서도 1,480원 부근 등락, 전일 종가 대비 8.1원 하락한 1,481.2원에 정규장 마감. 야간장에서는 미 생산자물가의 예상치 하회로 인한 달러 약세에 1,472.7원으로 하락 마감. 역외 NDF 환율은 8.25원 하락한 1,471.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,470원대 하락 개장 예상. 미국의 예상보다 약한 물가압력과 미·이란 2차 협상 기대가 약 달러 자극 중. 더불어 급락한 국제유가 역시 달러/원 하락 요인. 배당 역송금 등 잠재적인 원화 약세 요인은 일부 잔존. 하지만 전반적인 수급 환경은 반도체 수출 호조 및 WGBI 외국인 채권투자 등에 달러 공급 우위 장세. 금일 환율은 수급이 받쳐 준다면 1,460원대 진입도 가능 [글로벌 동향] 미 생산자물가 예상 대폭 하회, 미·이란 2차 협상 기대↑ 전일 미 달러화는 예상보다 낮았던 미 생산자물가와 미·이란의 2차 협상 기대에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.32% 하락한 98.10pt 기록. 미국의 3월 생산자물가지수 (PPI)는 시장 예상을 큰 폭 하회. PPI는 전월대비 0.5% 상승에 그침 (예상치 +1.1%). 식품과 에너지 제외한 근원 PPI는 0.1% 상승하며 예상치 (+0.4%) 하회. 에너지 부문은 이란 전쟁 등 휘발유 가격 급등 여파에 8.5% 상승. 하지만 서비스 부문인 유통 서비스 마진은 0.3% 하락. 한편 트럼프 대통령은 이란과의 2차 협상이 이틀 내에 개최될 수 있다고 밝힘. 소식통에 따르면, 양측은 파키스탄에서 2차 협상을 위한 일정 조율 중인 것으로 확인. 이에 WTI 국제유가는 전일대비 7.87% 급락하며 배럴당 91.28달러에 거래. 미 국채금리는 낮은 생산자물가와 유가 하락을 반영하며 장단기물 대체로 하락. 뉴욕증시는 위험선호 회복에 힘입어 3대 지수 모두 상승 마감 [마켓 이슈] WGBI로 외국인 채권자금 존재감 부각, 평시엔 환율 하락 재료 최근 국제수지 통계를 보면, 전체 달러 공급 원천 가운데 외국인 국내 채권 순투자가 차지하는 비중이 점차 확대. 2026년 1~2월 장기채권 비중은 평균 약 6% 수준. 이는 과거보다 외국인 채권자금이 달러 수급에 미치는 영향력이 커지고 있음 시사. 여기에 더해 4월부터 한국 국채의 WGBI 편입이 시작. 앞으로는 패시브 자금뿐 아니라 WGBI 추종 액티브 자금까지 유입되면서 외국인 채권투자 비중이 한층 더 확대될 전망. 다만 중요한 점은 외국인 채권투자가 본질적으로 '부채성 자금'이라는 점. 들어올 때는 달러 공급원이지만, 시황이 급변하거나 위험회피 심리가 강화될 경우 언제든 유출도 가능. 특히 WGBI 추종 액티브 자금은 시장 환경 변화에 민감하게 반응할 가능성 높음. 즉 WGBI 편입에 따른 외국인 채권자금 유입은 평시에 환율 하락을 유도하는 재료지만, 동시에 스트레스 국면에서는 상방 변동성을 키울 수 있는 잠재적 재료라는 판단</t>
+  </si>
 </sst>
 </file>
 
@@ -27680,7 +27699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3337"/>
+  <dimension ref="A1:G3338"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -75369,6 +75388,29 @@
       </c>
       <c r="G3337" s="1" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3338" s="3">
+        <v>46127</v>
+      </c>
+      <c r="B3338" s="3">
+        <v>46127</v>
+      </c>
+      <c r="C3338" s="7">
+        <v>0.36805555555555602</v>
+      </c>
+      <c r="D3338" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3338" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3338" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3338" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
